--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BDDD3C-B78E-4971-A6FC-2103F6A92FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAFA31B-97F7-4166-B0E2-B7C34572EB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="57840" windowHeight="31920" tabRatio="745" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
+    <workbookView xWindow="53100" yWindow="2370" windowWidth="28905" windowHeight="16320" tabRatio="745" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="509">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -1331,9 +1331,6 @@
     <t>Manuf</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>FTDI</t>
   </si>
   <si>
@@ -1473,6 +1470,141 @@
   </si>
   <si>
     <t>Brass wire tip cleaner</t>
+  </si>
+  <si>
+    <t>Nucleo-L011K4</t>
+  </si>
+  <si>
+    <t>Mates with B06B-PASK-1 (LF) (SN) JST PA series</t>
+  </si>
+  <si>
+    <t>Mates with B04B-PASK-1 (LF) (SN) 4 JST PA series</t>
+  </si>
+  <si>
+    <t>Ordered</t>
+  </si>
+  <si>
+    <t>Mates with 39-31-0020 Molex MiniFit Jnr</t>
+  </si>
+  <si>
+    <t>Molex</t>
+  </si>
+  <si>
+    <t>Mates with B2P-VH(LF)(SN) JST VH Series</t>
+  </si>
+  <si>
+    <t>Already got</t>
+  </si>
+  <si>
+    <t>VHR-2N</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>BVH-21T-P1.1</t>
+  </si>
+  <si>
+    <t>PAP-06V-S</t>
+  </si>
+  <si>
+    <t>Loupes</t>
+  </si>
+  <si>
+    <t>Tag Connect programming header</t>
+  </si>
+  <si>
+    <t>Tag Connect</t>
+  </si>
+  <si>
+    <t>ST Micro</t>
+  </si>
+  <si>
+    <t>Debug Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC2030-CTX-NL-ST14 </t>
+  </si>
+  <si>
+    <t>https://thedebugstore.com/products/tag-connect-tc2030-ctx-nl-st14-stm32-swd-programming-cable?variant=37768445788349</t>
+  </si>
+  <si>
+    <t>Adaptor PCB</t>
+  </si>
+  <si>
+    <t>ARM20-CTX</t>
+  </si>
+  <si>
+    <t>https://thedebugstore.com/products/tag-connect-arm20-ctx-20-pin-to-tc2030-idc-adapter-uk?variant=55729780654455</t>
+  </si>
+  <si>
+    <t>Spelling on Keyfob</t>
+  </si>
+  <si>
+    <t>Should read "Karman Delta"</t>
+  </si>
+  <si>
+    <t>CAN connector</t>
+  </si>
+  <si>
+    <t>Could split out each CAN bus and link in external connector. Thereby breaking the link between the processors as flight starts. Use existing 6 way connector</t>
+  </si>
+  <si>
+    <t>TTL-232RG-VREG3V3-WE</t>
+  </si>
+  <si>
+    <t>https://www.ebay.co.uk/itm/388292280633</t>
+  </si>
+  <si>
+    <t>Ebay</t>
+  </si>
+  <si>
+    <t>Use x3.5 magnification</t>
+  </si>
+  <si>
+    <t>ST-LINK/V2</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/stmicroelectronics/st-link-v2/icd-programmer-for-stm8-stm32/dp/1892523</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/ftdi/ttl-232rg-vreg3v3-we/cable-ttl-usb-conv-wire-end-3v3/dp/2352005</t>
+  </si>
+  <si>
+    <t>NO STOCK</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/stmicroelectronics/nucleo-l011k4/dev-board-nucleo-32-mcu/dp/2535699</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/jst-japan-solderless-terminals/vhr-2n/crimp-housing-2way-3-96mm/dp/630470</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/jst-japan-solderless-terminals/bvh-21t-p1-1/crimp-socket-0-33-0-83mm/dp/630500</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/jst-japan-solderless-terminals/pap-06v-s/connector-housing-pa-6way-2mm/dp/1830730</t>
+  </si>
+  <si>
+    <t>PAP-04V-S</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/jst-japan-solderless-terminals/pap-04v-s/connector-housing-rcpt-4pos-2mm/dp/1830729</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/molex/39-01-2025/connector-housing-rcpt-2pos/dp/2101989</t>
+  </si>
+  <si>
+    <t>45750-1112</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/molex/45750-1112/contact-socket-18awg-crimp/dp/1717550</t>
+  </si>
+  <si>
+    <t>SPHD-002T-P0.5</t>
+  </si>
+  <si>
+    <t>https://uk.farnell.com/jst-japan-solderless-terminals/sphd-002t-p0-5/crimp-socket-24-28awg/dp/1830725?MER=sy-me-pd-mi-acce</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1864,79 +1996,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1948,39 +2087,37 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3643,31 +3780,31 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15" thickBot="1"/>
     <row r="3" spans="2:16" ht="15" thickBot="1">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="54" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="84" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="80" t="s">
         <v>233</v>
       </c>
-      <c r="L3" s="46" t="s">
+      <c r="L3" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="49"/>
+      <c r="N3" s="79"/>
     </row>
     <row r="4" spans="2:16" ht="96.75" customHeight="1" thickBot="1">
       <c r="B4" s="27" t="s">
@@ -3691,10 +3828,10 @@
       <c r="H4" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="47"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="83"/>
       <c r="M4" s="11" t="s">
         <v>81</v>
       </c>
@@ -3706,43 +3843,43 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15" thickTop="1">
-      <c r="B5" s="50">
+      <c r="B5" s="63">
         <v>2</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="63">
         <v>1</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="63">
         <v>2</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="63">
         <v>2</v>
       </c>
-      <c r="F5" s="52">
+      <c r="F5" s="64">
         <v>2</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="63">
         <v>2</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="72" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="50" t="s">
+      <c r="J5" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="50" t="s">
+      <c r="K5" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="56" t="s">
+      <c r="L5" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="62" t="s">
         <v>85</v>
       </c>
       <c r="P5" t="s">
@@ -3750,60 +3887,60 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="15" thickBot="1">
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="59"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="60">
+      <c r="B7" s="50">
         <v>3</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="50">
         <v>2</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="50">
         <v>3</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="50">
         <v>3</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="59">
         <v>3</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="50">
         <v>3</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="H7" s="56" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="60" t="s">
+      <c r="J7" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="68" t="s">
+      <c r="L7" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="47" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
@@ -3811,21 +3948,21 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="59"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="57"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1">
       <c r="B9" s="17">
@@ -3910,37 +4047,37 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="24">
-      <c r="B11" s="60">
+      <c r="B11" s="50">
         <v>5</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="50">
         <v>5</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="50">
         <v>6</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="50">
         <v>6</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="59">
         <v>6</v>
       </c>
-      <c r="G11" s="60">
+      <c r="G11" s="50">
         <v>6</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="71" t="s">
+      <c r="I11" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="68" t="s">
+      <c r="L11" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="29" t="s">
@@ -3954,17 +4091,17 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="24">
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="70"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="48"/>
       <c r="M12" s="14" t="s">
         <v>104</v>
       </c>
@@ -3973,17 +4110,17 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="24">
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="70"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="48"/>
       <c r="M13" s="14" t="s">
         <v>105</v>
       </c>
@@ -3992,17 +4129,17 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="36">
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="70"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="48"/>
       <c r="M14" s="14" t="s">
         <v>106</v>
       </c>
@@ -4011,71 +4148,71 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="24">
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="70"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="48"/>
       <c r="M15" s="29" t="s">
         <v>107</v>
       </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="57"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="49"/>
       <c r="M16" s="21" t="s">
         <v>108</v>
       </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:16" ht="24">
-      <c r="B17" s="60">
+      <c r="B17" s="50">
         <v>6</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="50">
         <v>6</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="50">
         <v>7</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="50">
         <v>7</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="59">
         <v>7</v>
       </c>
-      <c r="G17" s="60">
+      <c r="G17" s="50">
         <v>7</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I17" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="60" t="s">
+      <c r="J17" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="60" t="s">
+      <c r="K17" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="68" t="s">
+      <c r="L17" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -4086,17 +4223,17 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="24">
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="70"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="48"/>
       <c r="M18" s="23" t="s">
         <v>116</v>
       </c>
@@ -4105,122 +4242,122 @@
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="70"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="48"/>
       <c r="M19" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="2:16" ht="24">
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="70"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="48"/>
       <c r="M20" s="23" t="s">
         <v>118</v>
       </c>
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="2:16" ht="24">
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="70"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="48"/>
       <c r="M21" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="2:16" ht="24">
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="70"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="57"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="49"/>
       <c r="M23" s="40" t="s">
         <v>121</v>
       </c>
       <c r="N23" s="24"/>
     </row>
     <row r="24" spans="2:16" ht="36">
-      <c r="B24" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="60">
+      <c r="B24" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="50">
         <v>8</v>
       </c>
-      <c r="E24" s="60">
+      <c r="E24" s="50">
         <v>8</v>
       </c>
-      <c r="F24" s="61">
+      <c r="F24" s="59">
         <v>8</v>
       </c>
-      <c r="G24" s="60">
+      <c r="G24" s="50">
         <v>8</v>
       </c>
-      <c r="H24" s="62" t="s">
+      <c r="H24" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="68" t="s">
+      <c r="I24" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="60" t="s">
+      <c r="J24" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="62" t="s">
+      <c r="K24" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="68" t="s">
+      <c r="L24" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -4231,17 +4368,17 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="24">
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="70"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="48"/>
       <c r="M25" s="29" t="s">
         <v>125</v>
       </c>
@@ -4253,17 +4390,17 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="24">
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="70"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="48"/>
       <c r="M26" s="14" t="s">
         <v>126</v>
       </c>
@@ -4272,17 +4409,17 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="57"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="49"/>
       <c r="M27" s="19" t="s">
         <v>127</v>
       </c>
@@ -4291,37 +4428,37 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="24">
-      <c r="B28" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="60">
+      <c r="B28" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="50">
         <v>9</v>
       </c>
-      <c r="E28" s="60">
+      <c r="E28" s="50">
         <v>9</v>
       </c>
-      <c r="F28" s="61">
+      <c r="F28" s="59">
         <v>9</v>
       </c>
-      <c r="G28" s="60">
+      <c r="G28" s="50">
         <v>9</v>
       </c>
-      <c r="H28" s="62" t="s">
+      <c r="H28" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="I28" s="68" t="s">
+      <c r="I28" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="60" t="s">
+      <c r="J28" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="60" t="s">
+      <c r="K28" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L28" s="68" t="s">
+      <c r="L28" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M28" s="14" t="s">
@@ -4332,17 +4469,17 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="70"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="48"/>
       <c r="M29" s="14" t="s">
         <v>135</v>
       </c>
@@ -4351,71 +4488,71 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="24">
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="70"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="48"/>
       <c r="M30" s="29" t="s">
         <v>103</v>
       </c>
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="57"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="49"/>
       <c r="M31" s="40" t="s">
         <v>136</v>
       </c>
       <c r="N31" s="24"/>
     </row>
     <row r="32" spans="2:16" ht="24">
-      <c r="B32" s="60">
+      <c r="B32" s="50">
         <v>7</v>
       </c>
-      <c r="C32" s="60">
+      <c r="C32" s="50">
         <v>7</v>
       </c>
-      <c r="D32" s="60">
+      <c r="D32" s="50">
         <v>10</v>
       </c>
-      <c r="E32" s="60">
+      <c r="E32" s="50">
         <v>10</v>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="59">
         <v>10</v>
       </c>
-      <c r="G32" s="60">
+      <c r="G32" s="50">
         <v>10</v>
       </c>
-      <c r="H32" s="62" t="s">
+      <c r="H32" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="68" t="s">
+      <c r="I32" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="60" t="s">
+      <c r="J32" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="62" t="s">
+      <c r="K32" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="L32" s="68" t="s">
+      <c r="L32" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M32" s="14" t="s">
@@ -4426,17 +4563,17 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="24">
-      <c r="B33" s="66"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="70"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="48"/>
       <c r="M33" s="14" t="s">
         <v>104</v>
       </c>
@@ -4445,17 +4582,17 @@
       </c>
     </row>
     <row r="34" spans="2:16" ht="36">
-      <c r="B34" s="66"/>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="70"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="48"/>
       <c r="M34" s="14" t="s">
         <v>140</v>
       </c>
@@ -4467,105 +4604,105 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="24">
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="70"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="48"/>
       <c r="M35" s="23" t="s">
         <v>141</v>
       </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="70"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="48"/>
       <c r="M36" s="14" t="s">
         <v>142</v>
       </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" spans="2:16" ht="24">
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="66"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="70"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="48"/>
       <c r="M37" s="37" t="s">
         <v>126</v>
       </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="57"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="49"/>
       <c r="M38" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N38" s="18"/>
     </row>
     <row r="39" spans="2:16" ht="24.75" thickTop="1">
-      <c r="B39" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="50">
+      <c r="B39" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="63">
         <v>8</v>
       </c>
-      <c r="D39" s="50">
+      <c r="D39" s="63">
         <v>11</v>
       </c>
-      <c r="E39" s="50">
+      <c r="E39" s="63">
         <v>11</v>
       </c>
-      <c r="F39" s="52">
+      <c r="F39" s="64">
         <v>11</v>
       </c>
-      <c r="G39" s="50">
+      <c r="G39" s="63">
         <v>11</v>
       </c>
-      <c r="H39" s="58" t="s">
+      <c r="H39" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="56" t="s">
+      <c r="I39" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="J39" s="50" t="s">
+      <c r="J39" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="58" t="s">
+      <c r="K39" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="56" t="s">
+      <c r="L39" s="62" t="s">
         <v>88</v>
       </c>
       <c r="M39" s="14" t="s">
@@ -4576,17 +4713,17 @@
       </c>
     </row>
     <row r="40" spans="2:16" ht="24">
-      <c r="B40" s="70"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="70"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="48"/>
       <c r="M40" s="14" t="s">
         <v>116</v>
       </c>
@@ -4595,17 +4732,17 @@
       </c>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="70"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="70"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="48"/>
       <c r="M41" s="14" t="s">
         <v>142</v>
       </c>
@@ -4617,60 +4754,60 @@
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1">
-      <c r="B42" s="57"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="59"/>
-      <c r="L42" s="57"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="49"/>
       <c r="M42" s="19" t="s">
         <v>147</v>
       </c>
       <c r="N42" s="18"/>
     </row>
     <row r="43" spans="2:16">
-      <c r="B43" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="60">
+      <c r="B43" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="50">
         <v>9</v>
       </c>
-      <c r="D43" s="60">
+      <c r="D43" s="50">
         <v>12</v>
       </c>
-      <c r="E43" s="60">
+      <c r="E43" s="50">
         <v>12</v>
       </c>
-      <c r="F43" s="61">
+      <c r="F43" s="59">
         <v>12</v>
       </c>
-      <c r="G43" s="60">
+      <c r="G43" s="50">
         <v>12</v>
       </c>
-      <c r="H43" s="62" t="s">
+      <c r="H43" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="I43" s="68" t="s">
+      <c r="I43" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="60" t="s">
+      <c r="J43" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="60" t="s">
+      <c r="K43" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L43" s="68" t="s">
+      <c r="L43" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N43" s="74" t="s">
+      <c r="N43" s="71" t="s">
         <v>154</v>
       </c>
       <c r="P43" t="s">
@@ -4678,143 +4815,143 @@
       </c>
     </row>
     <row r="44" spans="2:16" ht="24">
-      <c r="B44" s="70"/>
-      <c r="C44" s="66"/>
-      <c r="D44" s="66"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="70"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+      <c r="L44" s="48"/>
       <c r="M44" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N44" s="75"/>
+      <c r="N44" s="66"/>
     </row>
     <row r="45" spans="2:16" ht="24">
-      <c r="B45" s="70"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="70"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="48"/>
       <c r="M45" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="75"/>
+      <c r="N45" s="66"/>
     </row>
     <row r="46" spans="2:16" ht="24">
-      <c r="B46" s="70"/>
-      <c r="C46" s="66"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="66"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="70"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="51"/>
+      <c r="L46" s="48"/>
       <c r="M46" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N46" s="75"/>
+      <c r="N46" s="66"/>
     </row>
     <row r="47" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B47" s="57"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="51"/>
-      <c r="K47" s="51"/>
-      <c r="L47" s="57"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="49"/>
       <c r="M47" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N47" s="76"/>
+      <c r="N47" s="67"/>
     </row>
     <row r="48" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B48" s="60">
+      <c r="B48" s="50">
         <v>8</v>
       </c>
-      <c r="C48" s="60">
+      <c r="C48" s="50">
         <v>10</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="50">
         <v>13</v>
       </c>
-      <c r="E48" s="60">
+      <c r="E48" s="50">
         <v>13</v>
       </c>
-      <c r="F48" s="61">
+      <c r="F48" s="59">
         <v>13</v>
       </c>
-      <c r="G48" s="60">
+      <c r="G48" s="50">
         <v>13</v>
       </c>
-      <c r="H48" s="62" t="s">
+      <c r="H48" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="68" t="s">
+      <c r="I48" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="60" t="s">
+      <c r="J48" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="60" t="s">
+      <c r="K48" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L48" s="68" t="s">
+      <c r="L48" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M48" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N48" s="68" t="s">
+      <c r="N48" s="47" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24">
-      <c r="B49" s="66"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="66"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="66"/>
-      <c r="K49" s="66"/>
-      <c r="L49" s="70"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+      <c r="L49" s="48"/>
       <c r="M49" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N49" s="70"/>
+      <c r="N49" s="48"/>
     </row>
     <row r="50" spans="2:16" ht="24">
-      <c r="B50" s="66"/>
-      <c r="C50" s="66"/>
-      <c r="D50" s="66"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="66"/>
-      <c r="K50" s="66"/>
-      <c r="L50" s="70"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="48"/>
       <c r="M50" s="14" t="s">
         <v>159</v>
       </c>
@@ -4826,88 +4963,88 @@
       </c>
     </row>
     <row r="51" spans="2:16" ht="24">
-      <c r="B51" s="66"/>
-      <c r="C51" s="66"/>
-      <c r="D51" s="66"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="66"/>
-      <c r="H51" s="69"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="66"/>
-      <c r="K51" s="66"/>
-      <c r="L51" s="70"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="60"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="51"/>
+      <c r="L51" s="48"/>
       <c r="M51" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="2:16" ht="24">
-      <c r="B52" s="66"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="66"/>
-      <c r="K52" s="66"/>
-      <c r="L52" s="70"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+      <c r="L52" s="48"/>
       <c r="M52" s="14" t="s">
         <v>115</v>
       </c>
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="51"/>
-      <c r="K53" s="51"/>
-      <c r="L53" s="57"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="49"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="49"/>
       <c r="M53" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N53" s="24"/>
     </row>
     <row r="54" spans="2:16" ht="24">
-      <c r="B54" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="60">
+      <c r="B54" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="50">
         <v>14</v>
       </c>
-      <c r="F54" s="61">
+      <c r="F54" s="59">
         <v>14</v>
       </c>
-      <c r="G54" s="60">
+      <c r="G54" s="50">
         <v>14</v>
       </c>
-      <c r="H54" s="62" t="s">
+      <c r="H54" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="74" t="s">
+      <c r="I54" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="J54" s="60" t="s">
+      <c r="J54" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="60" t="s">
+      <c r="K54" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="68" t="s">
+      <c r="L54" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M54" s="14" t="s">
@@ -4921,17 +5058,17 @@
       </c>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="75"/>
-      <c r="J55" s="66"/>
-      <c r="K55" s="66"/>
-      <c r="L55" s="70"/>
+      <c r="B55" s="48"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="60"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="48"/>
       <c r="M55" s="14" t="s">
         <v>151</v>
       </c>
@@ -4940,88 +5077,88 @@
       </c>
     </row>
     <row r="56" spans="2:16">
-      <c r="B56" s="70"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="75"/>
-      <c r="J56" s="66"/>
-      <c r="K56" s="66"/>
-      <c r="L56" s="70"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="51"/>
+      <c r="K56" s="51"/>
+      <c r="L56" s="48"/>
       <c r="M56" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" spans="2:16" ht="24">
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="75"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="66"/>
-      <c r="L57" s="70"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="51"/>
+      <c r="K57" s="51"/>
+      <c r="L57" s="48"/>
       <c r="M57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1">
-      <c r="B58" s="57"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="57"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="76"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="51"/>
-      <c r="L58" s="57"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="67"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="49"/>
       <c r="M58" s="19" t="s">
         <v>162</v>
       </c>
       <c r="N58" s="18"/>
     </row>
     <row r="59" spans="2:16" ht="24">
-      <c r="B59" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="60">
+      <c r="B59" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="50">
         <v>11</v>
       </c>
-      <c r="D59" s="60">
+      <c r="D59" s="50">
         <v>14</v>
       </c>
-      <c r="E59" s="60">
+      <c r="E59" s="50">
         <v>15</v>
       </c>
-      <c r="F59" s="61">
+      <c r="F59" s="59">
         <v>15</v>
       </c>
-      <c r="G59" s="60">
+      <c r="G59" s="50">
         <v>15</v>
       </c>
-      <c r="H59" s="62" t="s">
+      <c r="H59" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="74" t="s">
+      <c r="I59" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="60" t="s">
+      <c r="J59" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="60" t="s">
+      <c r="K59" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L59" s="68" t="s">
+      <c r="L59" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M59" s="14" t="s">
@@ -5035,17 +5172,17 @@
       </c>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" s="70"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="75"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="70"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="60"/>
+      <c r="G60" s="51"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="51"/>
+      <c r="K60" s="51"/>
+      <c r="L60" s="48"/>
       <c r="M60" s="14" t="s">
         <v>157</v>
       </c>
@@ -5054,51 +5191,51 @@
       </c>
     </row>
     <row r="61" spans="2:16" ht="24">
-      <c r="B61" s="70"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="75"/>
-      <c r="J61" s="66"/>
-      <c r="K61" s="66"/>
-      <c r="L61" s="70"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="51"/>
+      <c r="E61" s="51"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="51"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="51"/>
+      <c r="K61" s="51"/>
+      <c r="L61" s="48"/>
       <c r="M61" s="14" t="s">
         <v>104</v>
       </c>
       <c r="N61" s="22"/>
     </row>
     <row r="62" spans="2:16" ht="24">
-      <c r="B62" s="70"/>
-      <c r="C62" s="66"/>
-      <c r="D62" s="66"/>
-      <c r="E62" s="66"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="75"/>
-      <c r="J62" s="66"/>
-      <c r="K62" s="66"/>
-      <c r="L62" s="70"/>
+      <c r="B62" s="48"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="51"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="48"/>
       <c r="M62" s="13" t="s">
         <v>167</v>
       </c>
       <c r="N62" s="22"/>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1">
-      <c r="B63" s="57"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="76"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="51"/>
-      <c r="L63" s="57"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="52"/>
+      <c r="K63" s="52"/>
+      <c r="L63" s="49"/>
       <c r="M63" s="19" t="s">
         <v>168</v>
       </c>
@@ -5228,43 +5365,43 @@
       </c>
     </row>
     <row r="67" spans="2:16" ht="36">
-      <c r="B67" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="60">
+      <c r="B67" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="50">
         <v>18</v>
       </c>
-      <c r="F67" s="61">
+      <c r="F67" s="59">
         <v>18</v>
       </c>
-      <c r="G67" s="60">
+      <c r="G67" s="50">
         <v>18</v>
       </c>
-      <c r="H67" s="62" t="s">
+      <c r="H67" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="I67" s="74" t="s">
+      <c r="I67" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="60" t="s">
+      <c r="J67" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="60" t="s">
+      <c r="K67" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="68" t="s">
+      <c r="L67" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M67" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="N67" s="68" t="s">
+      <c r="N67" s="47" t="s">
         <v>88</v>
       </c>
       <c r="P67" t="s">
@@ -5272,860 +5409,860 @@
       </c>
     </row>
     <row r="68" spans="2:16" ht="24">
-      <c r="B68" s="70"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="70"/>
-      <c r="E68" s="66"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="75"/>
-      <c r="J68" s="66"/>
-      <c r="K68" s="66"/>
-      <c r="L68" s="70"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="60"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="51"/>
+      <c r="K68" s="51"/>
+      <c r="L68" s="48"/>
       <c r="M68" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N68" s="70"/>
+      <c r="N68" s="48"/>
     </row>
     <row r="69" spans="2:16" ht="24">
-      <c r="B69" s="70"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="70"/>
-      <c r="E69" s="66"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="75"/>
-      <c r="J69" s="66"/>
-      <c r="K69" s="66"/>
-      <c r="L69" s="70"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="51"/>
+      <c r="L69" s="48"/>
       <c r="M69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="70"/>
+      <c r="N69" s="48"/>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1">
-      <c r="B70" s="57"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="76"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="57"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="61"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="67"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="49"/>
       <c r="M70" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N70" s="57"/>
+      <c r="N70" s="49"/>
     </row>
     <row r="71" spans="2:16" ht="24">
-      <c r="B71" s="60">
+      <c r="B71" s="50">
         <v>11</v>
       </c>
-      <c r="C71" s="60">
+      <c r="C71" s="50">
         <v>14</v>
       </c>
-      <c r="D71" s="60">
+      <c r="D71" s="50">
         <v>17</v>
       </c>
-      <c r="E71" s="60">
+      <c r="E71" s="50">
         <v>19</v>
       </c>
-      <c r="F71" s="61">
+      <c r="F71" s="59">
         <v>19</v>
       </c>
-      <c r="G71" s="60">
+      <c r="G71" s="50">
         <v>19</v>
       </c>
-      <c r="H71" s="62" t="s">
+      <c r="H71" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="68" t="s">
+      <c r="I71" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="J71" s="60" t="s">
+      <c r="J71" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K71" s="60" t="s">
+      <c r="K71" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="L71" s="68" t="s">
+      <c r="L71" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M71" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="N71" s="68" t="s">
+      <c r="N71" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="24">
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="66"/>
-      <c r="E72" s="66"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="70"/>
-      <c r="J72" s="66"/>
-      <c r="K72" s="66"/>
-      <c r="L72" s="70"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="51"/>
+      <c r="K72" s="51"/>
+      <c r="L72" s="48"/>
       <c r="M72" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N72" s="70"/>
+      <c r="N72" s="48"/>
     </row>
     <row r="73" spans="2:16" ht="24">
-      <c r="B73" s="66"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="66"/>
-      <c r="E73" s="66"/>
-      <c r="F73" s="67"/>
-      <c r="G73" s="66"/>
-      <c r="H73" s="69"/>
-      <c r="I73" s="70"/>
-      <c r="J73" s="66"/>
-      <c r="K73" s="66"/>
-      <c r="L73" s="70"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="51"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="51"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="51"/>
+      <c r="K73" s="51"/>
+      <c r="L73" s="48"/>
       <c r="M73" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="N73" s="70"/>
+      <c r="N73" s="48"/>
     </row>
     <row r="74" spans="2:16" ht="48.75" thickBot="1">
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="59"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="51"/>
-      <c r="K74" s="51"/>
-      <c r="L74" s="57"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="61"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="58"/>
+      <c r="I74" s="49"/>
+      <c r="J74" s="52"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="49"/>
       <c r="M74" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N74" s="57"/>
+      <c r="N74" s="49"/>
     </row>
     <row r="75" spans="2:16" ht="36.75" thickTop="1">
-      <c r="B75" s="50">
+      <c r="B75" s="63">
         <v>12</v>
       </c>
-      <c r="C75" s="50">
+      <c r="C75" s="63">
         <v>15</v>
       </c>
-      <c r="D75" s="50">
+      <c r="D75" s="63">
         <v>18</v>
       </c>
-      <c r="E75" s="50">
+      <c r="E75" s="63">
         <v>20</v>
       </c>
-      <c r="F75" s="52">
+      <c r="F75" s="64">
         <v>20</v>
       </c>
-      <c r="G75" s="50">
+      <c r="G75" s="63">
         <v>20</v>
       </c>
-      <c r="H75" s="58" t="s">
+      <c r="H75" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="56" t="s">
+      <c r="I75" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="J75" s="50" t="s">
+      <c r="J75" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="50" t="s">
+      <c r="K75" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="L75" s="77">
+      <c r="L75" s="73">
         <v>-7</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="56" t="s">
+      <c r="N75" s="62" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="24">
-      <c r="B76" s="66"/>
-      <c r="C76" s="66"/>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="69"/>
-      <c r="I76" s="70"/>
-      <c r="J76" s="66"/>
-      <c r="K76" s="66"/>
-      <c r="L76" s="78"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="51"/>
+      <c r="K76" s="51"/>
+      <c r="L76" s="69"/>
       <c r="M76" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="70"/>
+      <c r="N76" s="48"/>
     </row>
     <row r="77" spans="2:16" ht="24">
-      <c r="B77" s="66"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
-      <c r="F77" s="67"/>
-      <c r="G77" s="66"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="66"/>
-      <c r="K77" s="66"/>
-      <c r="L77" s="78"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="51"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+      <c r="L77" s="69"/>
       <c r="M77" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="N77" s="70"/>
+      <c r="N77" s="48"/>
     </row>
     <row r="78" spans="2:16">
-      <c r="B78" s="66"/>
-      <c r="C78" s="66"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="66"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="66"/>
-      <c r="H78" s="69"/>
-      <c r="I78" s="70"/>
-      <c r="J78" s="66"/>
-      <c r="K78" s="66"/>
-      <c r="L78" s="78"/>
+      <c r="B78" s="51"/>
+      <c r="C78" s="51"/>
+      <c r="D78" s="51"/>
+      <c r="E78" s="51"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="51"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="51"/>
+      <c r="K78" s="51"/>
+      <c r="L78" s="69"/>
       <c r="M78" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N78" s="70"/>
+      <c r="N78" s="48"/>
     </row>
     <row r="79" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="59"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="51"/>
-      <c r="K79" s="51"/>
-      <c r="L79" s="79"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="58"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="70"/>
       <c r="M79" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="57"/>
+      <c r="N79" s="49"/>
     </row>
     <row r="80" spans="2:16">
-      <c r="B80" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D80" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="F80" s="61">
+      <c r="B80" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="59">
         <v>21</v>
       </c>
-      <c r="G80" s="60">
+      <c r="G80" s="50">
         <v>21</v>
       </c>
-      <c r="H80" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80" s="68" t="s">
+      <c r="H80" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="J80" s="60" t="s">
+      <c r="J80" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K80" s="60" t="s">
+      <c r="K80" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L80" s="68" t="s">
+      <c r="L80" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M80" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N80" s="68" t="s">
+      <c r="N80" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:19" ht="48">
-      <c r="B81" s="70"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="70"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="66"/>
-      <c r="H81" s="70"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="66"/>
-      <c r="K81" s="66"/>
-      <c r="L81" s="70"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="60"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48"/>
+      <c r="J81" s="51"/>
+      <c r="K81" s="51"/>
+      <c r="L81" s="48"/>
       <c r="M81" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="N81" s="70"/>
+      <c r="N81" s="48"/>
     </row>
     <row r="82" spans="2:19" ht="24">
-      <c r="B82" s="70"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="70"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="66"/>
-      <c r="H82" s="70"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="66"/>
-      <c r="K82" s="66"/>
-      <c r="L82" s="70"/>
+      <c r="B82" s="48"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="51"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="48"/>
       <c r="M82" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="N82" s="70"/>
+      <c r="N82" s="48"/>
     </row>
     <row r="83" spans="2:19" ht="48.75" thickBot="1">
-      <c r="B83" s="57"/>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="57"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="57"/>
-      <c r="I83" s="57"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="51"/>
-      <c r="L83" s="57"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="61"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="49"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="49"/>
       <c r="M83" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N83" s="57"/>
+      <c r="N83" s="49"/>
     </row>
     <row r="84" spans="2:19">
-      <c r="B84" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="61">
+      <c r="B84" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="59">
         <v>22</v>
       </c>
-      <c r="G84" s="60">
+      <c r="G84" s="50">
         <v>22</v>
       </c>
-      <c r="H84" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84" s="68" t="s">
+      <c r="H84" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="J84" s="60" t="s">
+      <c r="J84" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="60" t="s">
+      <c r="K84" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="68" t="s">
+      <c r="L84" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N84" s="68" t="s">
+      <c r="N84" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:19" ht="24">
-      <c r="B85" s="70"/>
-      <c r="C85" s="70"/>
-      <c r="D85" s="70"/>
-      <c r="E85" s="70"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="70"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="66"/>
-      <c r="K85" s="66"/>
-      <c r="L85" s="70"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="48"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="51"/>
+      <c r="K85" s="51"/>
+      <c r="L85" s="48"/>
       <c r="M85" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N85" s="70"/>
+      <c r="N85" s="48"/>
     </row>
     <row r="86" spans="2:19" ht="24">
-      <c r="B86" s="70"/>
-      <c r="C86" s="70"/>
-      <c r="D86" s="70"/>
-      <c r="E86" s="70"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="66"/>
-      <c r="H86" s="70"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="66"/>
-      <c r="K86" s="66"/>
-      <c r="L86" s="70"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="51"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="48"/>
       <c r="M86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N86" s="70"/>
+      <c r="N86" s="48"/>
       <c r="S86" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B87" s="57"/>
-      <c r="C87" s="57"/>
-      <c r="D87" s="57"/>
-      <c r="E87" s="57"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="57"/>
-      <c r="I87" s="57"/>
-      <c r="J87" s="51"/>
-      <c r="K87" s="51"/>
-      <c r="L87" s="57"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="61"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="49"/>
       <c r="M87" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="N87" s="57"/>
+      <c r="N87" s="49"/>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="60">
+      <c r="B88" s="50">
         <v>13</v>
       </c>
-      <c r="C88" s="60">
+      <c r="C88" s="50">
         <v>16</v>
       </c>
-      <c r="D88" s="60">
+      <c r="D88" s="50">
         <v>19</v>
       </c>
-      <c r="E88" s="60">
+      <c r="E88" s="50">
         <v>21</v>
       </c>
-      <c r="F88" s="61">
+      <c r="F88" s="59">
         <v>23</v>
       </c>
-      <c r="G88" s="60">
+      <c r="G88" s="50">
         <v>23</v>
       </c>
-      <c r="H88" s="62" t="s">
+      <c r="H88" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="I88" s="68" t="s">
+      <c r="I88" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="J88" s="60" t="s">
+      <c r="J88" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K88" s="60" t="s">
+      <c r="K88" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="L88" s="68" t="s">
+      <c r="L88" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M88" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="N88" s="68" t="s">
+      <c r="N88" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="2:19" ht="24">
-      <c r="B89" s="66"/>
-      <c r="C89" s="66"/>
-      <c r="D89" s="66"/>
-      <c r="E89" s="66"/>
-      <c r="F89" s="67"/>
-      <c r="G89" s="66"/>
-      <c r="H89" s="69"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="66"/>
-      <c r="K89" s="66"/>
-      <c r="L89" s="70"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="51"/>
+      <c r="D89" s="51"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="60"/>
+      <c r="G89" s="51"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="48"/>
+      <c r="J89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="48"/>
       <c r="M89" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N89" s="70"/>
+      <c r="N89" s="48"/>
     </row>
     <row r="90" spans="2:19">
-      <c r="B90" s="66"/>
-      <c r="C90" s="66"/>
-      <c r="D90" s="66"/>
-      <c r="E90" s="66"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="66"/>
-      <c r="H90" s="69"/>
-      <c r="I90" s="70"/>
-      <c r="J90" s="66"/>
-      <c r="K90" s="66"/>
-      <c r="L90" s="70"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="48"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="48"/>
       <c r="M90" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="N90" s="70"/>
+      <c r="N90" s="48"/>
     </row>
     <row r="91" spans="2:19">
-      <c r="B91" s="66"/>
-      <c r="C91" s="66"/>
-      <c r="D91" s="66"/>
-      <c r="E91" s="66"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="66"/>
-      <c r="H91" s="69"/>
-      <c r="I91" s="70"/>
-      <c r="J91" s="66"/>
-      <c r="K91" s="66"/>
-      <c r="L91" s="70"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="51"/>
+      <c r="D91" s="51"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="60"/>
+      <c r="G91" s="51"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="51"/>
+      <c r="K91" s="51"/>
+      <c r="L91" s="48"/>
       <c r="M91" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N91" s="70"/>
+      <c r="N91" s="48"/>
     </row>
     <row r="92" spans="2:19" ht="24">
-      <c r="B92" s="66"/>
-      <c r="C92" s="66"/>
-      <c r="D92" s="66"/>
-      <c r="E92" s="66"/>
-      <c r="F92" s="67"/>
-      <c r="G92" s="66"/>
-      <c r="H92" s="69"/>
-      <c r="I92" s="70"/>
-      <c r="J92" s="66"/>
-      <c r="K92" s="66"/>
-      <c r="L92" s="70"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="60"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="51"/>
+      <c r="K92" s="51"/>
+      <c r="L92" s="48"/>
       <c r="M92" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="N92" s="70"/>
+      <c r="N92" s="48"/>
     </row>
     <row r="93" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="51"/>
-      <c r="K93" s="51"/>
-      <c r="L93" s="57"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="61"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="58"/>
+      <c r="I93" s="49"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="49"/>
       <c r="M93" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N93" s="57"/>
+      <c r="N93" s="49"/>
     </row>
     <row r="94" spans="2:19">
-      <c r="B94" s="60">
+      <c r="B94" s="50">
         <v>14</v>
       </c>
-      <c r="C94" s="60">
+      <c r="C94" s="50">
         <v>17</v>
       </c>
-      <c r="D94" s="60">
+      <c r="D94" s="50">
         <v>20</v>
       </c>
-      <c r="E94" s="60">
+      <c r="E94" s="50">
         <v>22</v>
       </c>
-      <c r="F94" s="61">
+      <c r="F94" s="59">
         <v>24</v>
       </c>
-      <c r="G94" s="60">
+      <c r="G94" s="50">
         <v>24</v>
       </c>
-      <c r="H94" s="62" t="s">
+      <c r="H94" s="56" t="s">
         <v>196</v>
       </c>
-      <c r="I94" s="68" t="s">
+      <c r="I94" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="J94" s="60" t="s">
+      <c r="J94" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K94" s="60" t="s">
+      <c r="K94" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L94" s="80">
+      <c r="L94" s="68">
         <v>-7</v>
       </c>
       <c r="M94" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N94" s="68" t="s">
+      <c r="N94" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:19" ht="24">
-      <c r="B95" s="66"/>
-      <c r="C95" s="66"/>
-      <c r="D95" s="66"/>
-      <c r="E95" s="66"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="66"/>
-      <c r="H95" s="69"/>
-      <c r="I95" s="70"/>
-      <c r="J95" s="66"/>
-      <c r="K95" s="66"/>
-      <c r="L95" s="78"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="51"/>
+      <c r="D95" s="51"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="60"/>
+      <c r="G95" s="51"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="51"/>
+      <c r="K95" s="51"/>
+      <c r="L95" s="69"/>
       <c r="M95" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="N95" s="70"/>
+      <c r="N95" s="48"/>
     </row>
     <row r="96" spans="2:19" ht="24">
-      <c r="B96" s="66"/>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="66"/>
-      <c r="H96" s="69"/>
-      <c r="I96" s="70"/>
-      <c r="J96" s="66"/>
-      <c r="K96" s="66"/>
-      <c r="L96" s="78"/>
+      <c r="B96" s="51"/>
+      <c r="C96" s="51"/>
+      <c r="D96" s="51"/>
+      <c r="E96" s="51"/>
+      <c r="F96" s="60"/>
+      <c r="G96" s="51"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="51"/>
+      <c r="K96" s="51"/>
+      <c r="L96" s="69"/>
       <c r="M96" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N96" s="70"/>
+      <c r="N96" s="48"/>
     </row>
     <row r="97" spans="2:16" ht="24">
-      <c r="B97" s="66"/>
-      <c r="C97" s="66"/>
-      <c r="D97" s="66"/>
-      <c r="E97" s="66"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="66"/>
-      <c r="H97" s="69"/>
-      <c r="I97" s="70"/>
-      <c r="J97" s="66"/>
-      <c r="K97" s="66"/>
-      <c r="L97" s="78"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51"/>
+      <c r="E97" s="51"/>
+      <c r="F97" s="60"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="51"/>
+      <c r="K97" s="51"/>
+      <c r="L97" s="69"/>
       <c r="M97" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="N97" s="70"/>
+      <c r="N97" s="48"/>
     </row>
     <row r="98" spans="2:16">
-      <c r="B98" s="66"/>
-      <c r="C98" s="66"/>
-      <c r="D98" s="66"/>
-      <c r="E98" s="66"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="66"/>
-      <c r="H98" s="69"/>
-      <c r="I98" s="70"/>
-      <c r="J98" s="66"/>
-      <c r="K98" s="66"/>
-      <c r="L98" s="78"/>
+      <c r="B98" s="51"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="51"/>
+      <c r="E98" s="51"/>
+      <c r="F98" s="60"/>
+      <c r="G98" s="51"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="51"/>
+      <c r="K98" s="51"/>
+      <c r="L98" s="69"/>
       <c r="M98" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N98" s="70"/>
+      <c r="N98" s="48"/>
     </row>
     <row r="99" spans="2:16" ht="24">
-      <c r="B99" s="66"/>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="69"/>
-      <c r="I99" s="70"/>
-      <c r="J99" s="66"/>
-      <c r="K99" s="66"/>
-      <c r="L99" s="78"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="60"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="51"/>
+      <c r="K99" s="51"/>
+      <c r="L99" s="69"/>
       <c r="M99" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="N99" s="70"/>
+      <c r="N99" s="48"/>
     </row>
     <row r="100" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="59"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="51"/>
-      <c r="K100" s="51"/>
-      <c r="L100" s="79"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="58"/>
+      <c r="I100" s="49"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
+      <c r="L100" s="70"/>
       <c r="M100" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N100" s="57"/>
+      <c r="N100" s="49"/>
     </row>
     <row r="101" spans="2:16">
-      <c r="B101" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E101" s="60">
+      <c r="B101" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="50">
         <v>23</v>
       </c>
-      <c r="F101" s="61">
+      <c r="F101" s="59">
         <v>25</v>
       </c>
-      <c r="G101" s="60">
+      <c r="G101" s="50">
         <v>25</v>
       </c>
-      <c r="H101" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="I101" s="68" t="s">
+      <c r="H101" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I101" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J101" s="60" t="s">
+      <c r="J101" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K101" s="60" t="s">
+      <c r="K101" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="68" t="s">
+      <c r="L101" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="N101" s="68" t="s">
+      <c r="N101" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="2:16">
-      <c r="B102" s="70"/>
-      <c r="C102" s="70"/>
-      <c r="D102" s="70"/>
-      <c r="E102" s="66"/>
-      <c r="F102" s="67"/>
-      <c r="G102" s="66"/>
-      <c r="H102" s="70"/>
-      <c r="I102" s="70"/>
-      <c r="J102" s="66"/>
-      <c r="K102" s="66"/>
-      <c r="L102" s="70"/>
+      <c r="B102" s="48"/>
+      <c r="C102" s="48"/>
+      <c r="D102" s="48"/>
+      <c r="E102" s="51"/>
+      <c r="F102" s="60"/>
+      <c r="G102" s="51"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="51"/>
+      <c r="K102" s="51"/>
+      <c r="L102" s="48"/>
       <c r="M102" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N102" s="70"/>
+      <c r="N102" s="48"/>
     </row>
     <row r="103" spans="2:16" ht="24">
-      <c r="B103" s="70"/>
-      <c r="C103" s="70"/>
-      <c r="D103" s="70"/>
-      <c r="E103" s="66"/>
-      <c r="F103" s="67"/>
-      <c r="G103" s="66"/>
-      <c r="H103" s="70"/>
-      <c r="I103" s="70"/>
-      <c r="J103" s="66"/>
-      <c r="K103" s="66"/>
-      <c r="L103" s="70"/>
+      <c r="B103" s="48"/>
+      <c r="C103" s="48"/>
+      <c r="D103" s="48"/>
+      <c r="E103" s="51"/>
+      <c r="F103" s="60"/>
+      <c r="G103" s="51"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="51"/>
+      <c r="K103" s="51"/>
+      <c r="L103" s="48"/>
       <c r="M103" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N103" s="70"/>
+      <c r="N103" s="48"/>
     </row>
     <row r="104" spans="2:16" ht="24">
-      <c r="B104" s="70"/>
-      <c r="C104" s="70"/>
-      <c r="D104" s="70"/>
-      <c r="E104" s="66"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="66"/>
-      <c r="H104" s="70"/>
-      <c r="I104" s="70"/>
-      <c r="J104" s="66"/>
-      <c r="K104" s="66"/>
-      <c r="L104" s="70"/>
+      <c r="B104" s="48"/>
+      <c r="C104" s="48"/>
+      <c r="D104" s="48"/>
+      <c r="E104" s="51"/>
+      <c r="F104" s="60"/>
+      <c r="G104" s="51"/>
+      <c r="H104" s="48"/>
+      <c r="I104" s="48"/>
+      <c r="J104" s="51"/>
+      <c r="K104" s="51"/>
+      <c r="L104" s="48"/>
       <c r="M104" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="N104" s="70"/>
+      <c r="N104" s="48"/>
     </row>
     <row r="105" spans="2:16" ht="15" thickBot="1">
-      <c r="B105" s="57"/>
-      <c r="C105" s="57"/>
-      <c r="D105" s="57"/>
-      <c r="E105" s="51"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="51"/>
-      <c r="H105" s="57"/>
-      <c r="I105" s="57"/>
-      <c r="J105" s="51"/>
-      <c r="K105" s="51"/>
-      <c r="L105" s="57"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="52"/>
+      <c r="F105" s="61"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="49"/>
+      <c r="I105" s="49"/>
+      <c r="J105" s="52"/>
+      <c r="K105" s="52"/>
+      <c r="L105" s="49"/>
       <c r="M105" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="57"/>
+      <c r="N105" s="49"/>
     </row>
     <row r="106" spans="2:16">
-      <c r="B106" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="60">
+      <c r="B106" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="50">
         <v>24</v>
       </c>
-      <c r="F106" s="61">
+      <c r="F106" s="59">
         <v>26</v>
       </c>
-      <c r="G106" s="60">
+      <c r="G106" s="50">
         <v>26</v>
       </c>
-      <c r="H106" s="62" t="s">
+      <c r="H106" s="56" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="74" t="s">
+      <c r="I106" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="J106" s="60" t="s">
+      <c r="J106" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="60" t="s">
+      <c r="K106" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="L106" s="68" t="s">
+      <c r="L106" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M106" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N106" s="68" t="s">
+      <c r="N106" s="47" t="s">
         <v>203</v>
       </c>
       <c r="P106" t="s">
@@ -6133,38 +6270,38 @@
       </c>
     </row>
     <row r="107" spans="2:16">
-      <c r="B107" s="70"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="70"/>
-      <c r="E107" s="66"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="66"/>
-      <c r="H107" s="69"/>
-      <c r="I107" s="75"/>
-      <c r="J107" s="66"/>
-      <c r="K107" s="66"/>
-      <c r="L107" s="70"/>
+      <c r="B107" s="48"/>
+      <c r="C107" s="48"/>
+      <c r="D107" s="48"/>
+      <c r="E107" s="51"/>
+      <c r="F107" s="60"/>
+      <c r="G107" s="51"/>
+      <c r="H107" s="57"/>
+      <c r="I107" s="66"/>
+      <c r="J107" s="51"/>
+      <c r="K107" s="51"/>
+      <c r="L107" s="48"/>
       <c r="M107" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="N107" s="70"/>
+      <c r="N107" s="48"/>
     </row>
     <row r="108" spans="2:16" ht="15" thickBot="1">
-      <c r="B108" s="57"/>
-      <c r="C108" s="57"/>
-      <c r="D108" s="57"/>
-      <c r="E108" s="51"/>
-      <c r="F108" s="53"/>
-      <c r="G108" s="51"/>
-      <c r="H108" s="59"/>
-      <c r="I108" s="76"/>
-      <c r="J108" s="51"/>
-      <c r="K108" s="51"/>
-      <c r="L108" s="57"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="61"/>
+      <c r="G108" s="52"/>
+      <c r="H108" s="58"/>
+      <c r="I108" s="67"/>
+      <c r="J108" s="52"/>
+      <c r="K108" s="52"/>
+      <c r="L108" s="49"/>
       <c r="M108" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="N108" s="57"/>
+      <c r="N108" s="49"/>
     </row>
     <row r="109" spans="2:16" ht="24.75" thickBot="1">
       <c r="B109" s="24" t="s">
@@ -6211,43 +6348,43 @@
       </c>
     </row>
     <row r="110" spans="2:16" ht="15" thickTop="1">
-      <c r="B110" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="50">
+      <c r="B110" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="63">
         <v>26</v>
       </c>
-      <c r="F110" s="52">
+      <c r="F110" s="64">
         <v>28</v>
       </c>
-      <c r="G110" s="50">
+      <c r="G110" s="63">
         <v>28</v>
       </c>
-      <c r="H110" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="I110" s="81" t="s">
+      <c r="H110" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="I110" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="J110" s="50" t="s">
+      <c r="J110" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="K110" s="50" t="s">
+      <c r="K110" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="L110" s="56" t="s">
+      <c r="L110" s="62" t="s">
         <v>88</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N110" s="56" t="s">
+      <c r="N110" s="62" t="s">
         <v>206</v>
       </c>
       <c r="P110" t="s">
@@ -6255,222 +6392,222 @@
       </c>
     </row>
     <row r="111" spans="2:16" ht="24">
-      <c r="B111" s="70"/>
-      <c r="C111" s="70"/>
-      <c r="D111" s="70"/>
-      <c r="E111" s="66"/>
-      <c r="F111" s="67"/>
-      <c r="G111" s="66"/>
-      <c r="H111" s="70"/>
-      <c r="I111" s="75"/>
-      <c r="J111" s="66"/>
-      <c r="K111" s="66"/>
-      <c r="L111" s="70"/>
+      <c r="B111" s="48"/>
+      <c r="C111" s="48"/>
+      <c r="D111" s="48"/>
+      <c r="E111" s="51"/>
+      <c r="F111" s="60"/>
+      <c r="G111" s="51"/>
+      <c r="H111" s="48"/>
+      <c r="I111" s="66"/>
+      <c r="J111" s="51"/>
+      <c r="K111" s="51"/>
+      <c r="L111" s="48"/>
       <c r="M111" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="N111" s="70"/>
+      <c r="N111" s="48"/>
     </row>
     <row r="112" spans="2:16" ht="24">
-      <c r="B112" s="70"/>
-      <c r="C112" s="70"/>
-      <c r="D112" s="70"/>
-      <c r="E112" s="66"/>
-      <c r="F112" s="67"/>
-      <c r="G112" s="66"/>
-      <c r="H112" s="70"/>
-      <c r="I112" s="75"/>
-      <c r="J112" s="66"/>
-      <c r="K112" s="66"/>
-      <c r="L112" s="70"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48"/>
+      <c r="D112" s="48"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="60"/>
+      <c r="G112" s="51"/>
+      <c r="H112" s="48"/>
+      <c r="I112" s="66"/>
+      <c r="J112" s="51"/>
+      <c r="K112" s="51"/>
+      <c r="L112" s="48"/>
       <c r="M112" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="70"/>
+      <c r="N112" s="48"/>
     </row>
     <row r="113" spans="2:14" ht="15" thickBot="1">
-      <c r="B113" s="57"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="53"/>
-      <c r="G113" s="51"/>
-      <c r="H113" s="57"/>
-      <c r="I113" s="76"/>
-      <c r="J113" s="51"/>
-      <c r="K113" s="51"/>
-      <c r="L113" s="57"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="49"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="52"/>
+      <c r="F113" s="61"/>
+      <c r="G113" s="52"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="67"/>
+      <c r="J113" s="52"/>
+      <c r="K113" s="52"/>
+      <c r="L113" s="49"/>
       <c r="M113" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="N113" s="57"/>
+      <c r="N113" s="49"/>
     </row>
     <row r="114" spans="2:14" ht="36">
-      <c r="B114" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="60">
+      <c r="B114" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="50">
         <v>18</v>
       </c>
-      <c r="D114" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E114" s="60">
+      <c r="D114" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E114" s="50">
         <v>27</v>
       </c>
-      <c r="F114" s="61">
+      <c r="F114" s="59">
         <v>29</v>
       </c>
-      <c r="G114" s="60">
+      <c r="G114" s="50">
         <v>29</v>
       </c>
-      <c r="H114" s="62" t="s">
+      <c r="H114" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="I114" s="68" t="s">
+      <c r="I114" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="J114" s="60" t="s">
+      <c r="J114" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K114" s="60" t="s">
+      <c r="K114" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="L114" s="68" t="s">
+      <c r="L114" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M114" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="N114" s="68" t="s">
+      <c r="N114" s="47" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="115" spans="2:14" ht="24">
-      <c r="B115" s="70"/>
-      <c r="C115" s="66"/>
-      <c r="D115" s="70"/>
-      <c r="E115" s="66"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="66"/>
-      <c r="H115" s="69"/>
-      <c r="I115" s="70"/>
-      <c r="J115" s="66"/>
-      <c r="K115" s="66"/>
-      <c r="L115" s="70"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="51"/>
+      <c r="D115" s="48"/>
+      <c r="E115" s="51"/>
+      <c r="F115" s="60"/>
+      <c r="G115" s="51"/>
+      <c r="H115" s="57"/>
+      <c r="I115" s="48"/>
+      <c r="J115" s="51"/>
+      <c r="K115" s="51"/>
+      <c r="L115" s="48"/>
       <c r="M115" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N115" s="70"/>
+      <c r="N115" s="48"/>
     </row>
     <row r="116" spans="2:14">
-      <c r="B116" s="70"/>
-      <c r="C116" s="66"/>
-      <c r="D116" s="70"/>
-      <c r="E116" s="66"/>
-      <c r="F116" s="67"/>
-      <c r="G116" s="66"/>
-      <c r="H116" s="69"/>
-      <c r="I116" s="70"/>
-      <c r="J116" s="66"/>
-      <c r="K116" s="66"/>
-      <c r="L116" s="70"/>
+      <c r="B116" s="48"/>
+      <c r="C116" s="51"/>
+      <c r="D116" s="48"/>
+      <c r="E116" s="51"/>
+      <c r="F116" s="60"/>
+      <c r="G116" s="51"/>
+      <c r="H116" s="57"/>
+      <c r="I116" s="48"/>
+      <c r="J116" s="51"/>
+      <c r="K116" s="51"/>
+      <c r="L116" s="48"/>
       <c r="M116" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N116" s="70"/>
+      <c r="N116" s="48"/>
     </row>
     <row r="117" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B117" s="57"/>
-      <c r="C117" s="51"/>
-      <c r="D117" s="57"/>
-      <c r="E117" s="51"/>
-      <c r="F117" s="53"/>
-      <c r="G117" s="51"/>
-      <c r="H117" s="59"/>
-      <c r="I117" s="57"/>
-      <c r="J117" s="51"/>
-      <c r="K117" s="51"/>
-      <c r="L117" s="57"/>
+      <c r="B117" s="49"/>
+      <c r="C117" s="52"/>
+      <c r="D117" s="49"/>
+      <c r="E117" s="52"/>
+      <c r="F117" s="61"/>
+      <c r="G117" s="52"/>
+      <c r="H117" s="58"/>
+      <c r="I117" s="49"/>
+      <c r="J117" s="52"/>
+      <c r="K117" s="52"/>
+      <c r="L117" s="49"/>
       <c r="M117" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="N117" s="57"/>
+      <c r="N117" s="49"/>
     </row>
     <row r="118" spans="2:14" ht="36">
-      <c r="B118" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="60">
+      <c r="B118" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="50">
         <v>19</v>
       </c>
-      <c r="D118" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E118" s="60">
+      <c r="D118" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="50">
         <v>28</v>
       </c>
-      <c r="F118" s="61">
+      <c r="F118" s="59">
         <v>30</v>
       </c>
-      <c r="G118" s="60">
+      <c r="G118" s="50">
         <v>30</v>
       </c>
-      <c r="H118" s="62" t="s">
+      <c r="H118" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="68" t="s">
+      <c r="I118" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="J118" s="60" t="s">
+      <c r="J118" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K118" s="60" t="s">
+      <c r="K118" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="L118" s="68" t="s">
+      <c r="L118" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M118" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="N118" s="68" t="s">
+      <c r="N118" s="47" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:14" ht="36">
-      <c r="B119" s="70"/>
-      <c r="C119" s="66"/>
-      <c r="D119" s="70"/>
-      <c r="E119" s="66"/>
-      <c r="F119" s="67"/>
-      <c r="G119" s="66"/>
-      <c r="H119" s="69"/>
-      <c r="I119" s="70"/>
-      <c r="J119" s="66"/>
-      <c r="K119" s="66"/>
-      <c r="L119" s="70"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="51"/>
+      <c r="D119" s="48"/>
+      <c r="E119" s="51"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="51"/>
+      <c r="H119" s="57"/>
+      <c r="I119" s="48"/>
+      <c r="J119" s="51"/>
+      <c r="K119" s="51"/>
+      <c r="L119" s="48"/>
       <c r="M119" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="N119" s="70"/>
+      <c r="N119" s="48"/>
     </row>
     <row r="120" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B120" s="57"/>
-      <c r="C120" s="51"/>
-      <c r="D120" s="57"/>
-      <c r="E120" s="51"/>
-      <c r="F120" s="53"/>
-      <c r="G120" s="51"/>
-      <c r="H120" s="59"/>
-      <c r="I120" s="57"/>
-      <c r="J120" s="51"/>
-      <c r="K120" s="51"/>
-      <c r="L120" s="57"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="52"/>
+      <c r="D120" s="49"/>
+      <c r="E120" s="52"/>
+      <c r="F120" s="61"/>
+      <c r="G120" s="52"/>
+      <c r="H120" s="58"/>
+      <c r="I120" s="49"/>
+      <c r="J120" s="52"/>
+      <c r="K120" s="52"/>
+      <c r="L120" s="49"/>
       <c r="M120" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="N120" s="57"/>
+      <c r="N120" s="49"/>
     </row>
     <row r="121" spans="2:14" ht="48.75" thickBot="1">
       <c r="B121" s="17">
@@ -6514,96 +6651,96 @@
       </c>
     </row>
     <row r="122" spans="2:14" ht="24">
-      <c r="B122" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="G122" s="60">
+      <c r="B122" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G122" s="50">
         <v>32</v>
       </c>
-      <c r="H122" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="I122" s="68" t="s">
+      <c r="H122" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I122" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="J122" s="60" t="s">
+      <c r="J122" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K122" s="60" t="s">
+      <c r="K122" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="L122" s="68" t="s">
+      <c r="L122" s="47" t="s">
         <v>88</v>
       </c>
       <c r="M122" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N122" s="68" t="s">
+      <c r="N122" s="47" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="24">
-      <c r="B123" s="70"/>
-      <c r="C123" s="70"/>
-      <c r="D123" s="70"/>
-      <c r="E123" s="70"/>
-      <c r="F123" s="83"/>
-      <c r="G123" s="66"/>
-      <c r="H123" s="70"/>
-      <c r="I123" s="70"/>
-      <c r="J123" s="66"/>
-      <c r="K123" s="66"/>
-      <c r="L123" s="70"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48"/>
+      <c r="D123" s="48"/>
+      <c r="E123" s="48"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="51"/>
+      <c r="H123" s="48"/>
+      <c r="I123" s="48"/>
+      <c r="J123" s="51"/>
+      <c r="K123" s="51"/>
+      <c r="L123" s="48"/>
       <c r="M123" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N123" s="70"/>
+      <c r="N123" s="48"/>
     </row>
     <row r="124" spans="2:14">
-      <c r="B124" s="70"/>
-      <c r="C124" s="70"/>
-      <c r="D124" s="70"/>
-      <c r="E124" s="70"/>
-      <c r="F124" s="83"/>
-      <c r="G124" s="66"/>
-      <c r="H124" s="70"/>
-      <c r="I124" s="70"/>
-      <c r="J124" s="66"/>
-      <c r="K124" s="66"/>
-      <c r="L124" s="70"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="48"/>
+      <c r="D124" s="48"/>
+      <c r="E124" s="48"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="51"/>
+      <c r="H124" s="48"/>
+      <c r="I124" s="48"/>
+      <c r="J124" s="51"/>
+      <c r="K124" s="51"/>
+      <c r="L124" s="48"/>
       <c r="M124" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="70"/>
+      <c r="N124" s="48"/>
     </row>
     <row r="125" spans="2:14" ht="15" thickBot="1">
-      <c r="B125" s="57"/>
-      <c r="C125" s="57"/>
-      <c r="D125" s="57"/>
-      <c r="E125" s="57"/>
-      <c r="F125" s="84"/>
-      <c r="G125" s="51"/>
-      <c r="H125" s="57"/>
-      <c r="I125" s="57"/>
-      <c r="J125" s="51"/>
-      <c r="K125" s="51"/>
-      <c r="L125" s="57"/>
+      <c r="B125" s="49"/>
+      <c r="C125" s="49"/>
+      <c r="D125" s="49"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="55"/>
+      <c r="G125" s="52"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="49"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="49"/>
       <c r="M125" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="57"/>
+      <c r="N125" s="49"/>
     </row>
     <row r="126" spans="2:14" ht="15" thickBot="1">
       <c r="B126" s="24" t="s">
@@ -6689,57 +6826,229 @@
     </row>
   </sheetData>
   <mergeCells count="298">
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="I122:I125"/>
-    <mergeCell ref="J122:J125"/>
-    <mergeCell ref="K122:K125"/>
-    <mergeCell ref="L122:L125"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="G122:G125"/>
-    <mergeCell ref="H118:H120"/>
-    <mergeCell ref="I118:I120"/>
-    <mergeCell ref="J118:J120"/>
-    <mergeCell ref="K118:K120"/>
-    <mergeCell ref="L118:L120"/>
-    <mergeCell ref="N118:N120"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="E118:E120"/>
-    <mergeCell ref="F118:F120"/>
-    <mergeCell ref="G118:G120"/>
-    <mergeCell ref="K114:K117"/>
-    <mergeCell ref="L114:L117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="I114:I117"/>
-    <mergeCell ref="J114:J117"/>
-    <mergeCell ref="K101:K105"/>
-    <mergeCell ref="L101:L105"/>
-    <mergeCell ref="N101:N105"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="J110:J113"/>
-    <mergeCell ref="K110:K113"/>
-    <mergeCell ref="L110:L113"/>
-    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="D17:D23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="E11:E16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="G11:G16"/>
+    <mergeCell ref="H11:H16"/>
+    <mergeCell ref="H17:H23"/>
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="K17:K23"/>
+    <mergeCell ref="L17:L23"/>
+    <mergeCell ref="I11:I16"/>
+    <mergeCell ref="J11:J16"/>
+    <mergeCell ref="K11:K16"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I24:I27"/>
+    <mergeCell ref="J24:J27"/>
+    <mergeCell ref="K24:K27"/>
+    <mergeCell ref="L24:L27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="J28:J31"/>
+    <mergeCell ref="K28:K31"/>
+    <mergeCell ref="L28:L31"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="L32:L38"/>
+    <mergeCell ref="B32:B38"/>
+    <mergeCell ref="C32:C38"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="E32:E38"/>
+    <mergeCell ref="F32:F38"/>
+    <mergeCell ref="G32:G38"/>
+    <mergeCell ref="H32:H38"/>
+    <mergeCell ref="I32:I38"/>
+    <mergeCell ref="J32:J38"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="G48:G53"/>
+    <mergeCell ref="K39:K42"/>
+    <mergeCell ref="L39:L42"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="I48:I53"/>
+    <mergeCell ref="J48:J53"/>
+    <mergeCell ref="K48:K53"/>
+    <mergeCell ref="L48:L53"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="D59:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="F59:F63"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="G59:G63"/>
+    <mergeCell ref="H59:H63"/>
+    <mergeCell ref="I59:I63"/>
+    <mergeCell ref="J59:J63"/>
+    <mergeCell ref="K59:K63"/>
+    <mergeCell ref="L59:L63"/>
+    <mergeCell ref="H54:H58"/>
+    <mergeCell ref="I54:I58"/>
+    <mergeCell ref="J54:J58"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="L54:L58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="K67:K70"/>
+    <mergeCell ref="L67:L70"/>
+    <mergeCell ref="N67:N70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="H71:H74"/>
+    <mergeCell ref="I71:I74"/>
+    <mergeCell ref="J71:J74"/>
+    <mergeCell ref="K71:K74"/>
+    <mergeCell ref="L71:L74"/>
+    <mergeCell ref="N71:N74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="G71:G74"/>
+    <mergeCell ref="N75:N79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="G80:G83"/>
+    <mergeCell ref="H80:H83"/>
+    <mergeCell ref="I80:I83"/>
+    <mergeCell ref="J80:J83"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="H75:H79"/>
+    <mergeCell ref="I75:I79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="K75:K79"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="D75:D79"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="K80:K83"/>
+    <mergeCell ref="L80:L83"/>
+    <mergeCell ref="N80:N83"/>
+    <mergeCell ref="K84:K87"/>
+    <mergeCell ref="L84:L87"/>
+    <mergeCell ref="N84:N87"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="D88:D93"/>
+    <mergeCell ref="E88:E93"/>
+    <mergeCell ref="F88:F93"/>
+    <mergeCell ref="N88:N93"/>
+    <mergeCell ref="G88:G93"/>
+    <mergeCell ref="H88:H93"/>
+    <mergeCell ref="I88:I93"/>
+    <mergeCell ref="J88:J93"/>
+    <mergeCell ref="K88:K93"/>
+    <mergeCell ref="L88:L93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="E84:E87"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="G84:G87"/>
+    <mergeCell ref="H84:H87"/>
+    <mergeCell ref="I84:I87"/>
+    <mergeCell ref="J84:J87"/>
+    <mergeCell ref="B94:B100"/>
+    <mergeCell ref="C94:C100"/>
+    <mergeCell ref="D94:D100"/>
+    <mergeCell ref="E94:E100"/>
+    <mergeCell ref="F94:F100"/>
+    <mergeCell ref="G94:G100"/>
+    <mergeCell ref="H94:H100"/>
+    <mergeCell ref="I94:I100"/>
+    <mergeCell ref="J94:J100"/>
     <mergeCell ref="B106:B108"/>
     <mergeCell ref="C106:C108"/>
     <mergeCell ref="D106:D108"/>
@@ -6764,229 +7073,57 @@
     <mergeCell ref="L106:L108"/>
     <mergeCell ref="I101:I105"/>
     <mergeCell ref="J101:J105"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="C94:C100"/>
-    <mergeCell ref="D94:D100"/>
-    <mergeCell ref="E94:E100"/>
-    <mergeCell ref="F94:F100"/>
-    <mergeCell ref="G94:G100"/>
-    <mergeCell ref="H94:H100"/>
-    <mergeCell ref="I94:I100"/>
-    <mergeCell ref="J94:J100"/>
-    <mergeCell ref="K84:K87"/>
-    <mergeCell ref="L84:L87"/>
-    <mergeCell ref="N84:N87"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="D88:D93"/>
-    <mergeCell ref="E88:E93"/>
-    <mergeCell ref="F88:F93"/>
-    <mergeCell ref="N88:N93"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="H88:H93"/>
-    <mergeCell ref="I88:I93"/>
-    <mergeCell ref="J88:J93"/>
-    <mergeCell ref="K88:K93"/>
-    <mergeCell ref="L88:L93"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E84:E87"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="G84:G87"/>
-    <mergeCell ref="H84:H87"/>
-    <mergeCell ref="I84:I87"/>
-    <mergeCell ref="J84:J87"/>
-    <mergeCell ref="N75:N79"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="G80:G83"/>
-    <mergeCell ref="H80:H83"/>
-    <mergeCell ref="I80:I83"/>
-    <mergeCell ref="J80:J83"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="H75:H79"/>
-    <mergeCell ref="I75:I79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="K75:K79"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="D75:D79"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="K80:K83"/>
-    <mergeCell ref="L80:L83"/>
-    <mergeCell ref="N80:N83"/>
-    <mergeCell ref="H71:H74"/>
-    <mergeCell ref="I71:I74"/>
-    <mergeCell ref="J71:J74"/>
-    <mergeCell ref="K71:K74"/>
-    <mergeCell ref="L71:L74"/>
-    <mergeCell ref="N71:N74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="E71:E74"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="J67:J70"/>
-    <mergeCell ref="K67:K70"/>
-    <mergeCell ref="L67:L70"/>
-    <mergeCell ref="N67:N70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="H59:H63"/>
-    <mergeCell ref="I59:I63"/>
-    <mergeCell ref="J59:J63"/>
-    <mergeCell ref="K59:K63"/>
-    <mergeCell ref="L59:L63"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="J54:J58"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="D59:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="H48:H53"/>
-    <mergeCell ref="I48:I53"/>
-    <mergeCell ref="J48:J53"/>
-    <mergeCell ref="K48:K53"/>
-    <mergeCell ref="L48:L53"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="K43:K47"/>
-    <mergeCell ref="L43:L47"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="G48:G53"/>
-    <mergeCell ref="K39:K42"/>
-    <mergeCell ref="L39:L42"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="D43:D47"/>
-    <mergeCell ref="E43:E47"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="G39:G42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="I39:I42"/>
-    <mergeCell ref="J39:J42"/>
-    <mergeCell ref="K32:K38"/>
-    <mergeCell ref="L32:L38"/>
-    <mergeCell ref="B32:B38"/>
-    <mergeCell ref="C32:C38"/>
-    <mergeCell ref="D32:D38"/>
-    <mergeCell ref="E32:E38"/>
-    <mergeCell ref="F32:F38"/>
-    <mergeCell ref="G32:G38"/>
-    <mergeCell ref="H32:H38"/>
-    <mergeCell ref="I32:I38"/>
-    <mergeCell ref="J32:J38"/>
-    <mergeCell ref="L11:L16"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I24:I27"/>
-    <mergeCell ref="J24:J27"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="L24:L27"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="F24:F27"/>
-    <mergeCell ref="G24:G27"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="H28:H31"/>
-    <mergeCell ref="I28:I31"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="K28:K31"/>
-    <mergeCell ref="L28:L31"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="D17:D23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="E11:E16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="G11:G16"/>
-    <mergeCell ref="H11:H16"/>
-    <mergeCell ref="H17:H23"/>
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="K17:K23"/>
-    <mergeCell ref="L17:L23"/>
-    <mergeCell ref="I11:I16"/>
-    <mergeCell ref="J11:J16"/>
-    <mergeCell ref="K11:K16"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K101:K105"/>
+    <mergeCell ref="L101:L105"/>
+    <mergeCell ref="N101:N105"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="J110:J113"/>
+    <mergeCell ref="K110:K113"/>
+    <mergeCell ref="L110:L113"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="J114:J117"/>
+    <mergeCell ref="K114:K117"/>
+    <mergeCell ref="L114:L117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="H118:H120"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="J118:J120"/>
+    <mergeCell ref="K118:K120"/>
+    <mergeCell ref="L118:L120"/>
+    <mergeCell ref="N118:N120"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="E118:E120"/>
+    <mergeCell ref="F118:F120"/>
+    <mergeCell ref="G118:G120"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="I122:I125"/>
+    <mergeCell ref="J122:J125"/>
+    <mergeCell ref="K122:K125"/>
+    <mergeCell ref="L122:L125"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="G122:G125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7517,6 +7654,9 @@
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
@@ -7615,6 +7755,9 @@
       <c r="A22" s="1" t="s">
         <v>371</v>
       </c>
+      <c r="B22" s="6" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
@@ -7724,6 +7867,9 @@
       <c r="A36" s="1" t="s">
         <v>382</v>
       </c>
+      <c r="B36" s="6" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
@@ -7777,6 +7923,9 @@
       <c r="A43" s="1" t="s">
         <v>389</v>
       </c>
+      <c r="B43" s="6" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="44" spans="1:2" ht="30">
       <c r="A44" s="1" t="s">
@@ -7828,7 +7977,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>32</v>
@@ -7841,19 +7990,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062DA91B-8FB1-42E1-8F78-2FA3A3E1477E}">
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="29.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.5" customWidth="1"/>
-    <col min="8" max="8" width="55.75" customWidth="1"/>
+    <col min="6" max="6" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.5" style="89" customWidth="1"/>
+    <col min="8" max="8" width="55.75" style="89" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="15">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A1" s="5" t="s">
         <v>399</v>
       </c>
@@ -7872,14 +8022,17 @@
       <c r="F1" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="87" t="s">
         <v>400</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="87" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>398</v>
       </c>
@@ -7898,91 +8051,253 @@
       <c r="F2" t="s">
         <v>405</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="88" t="s">
         <v>397</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="89" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="46" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>403</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="C3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D3">
+        <v>39012025</v>
+      </c>
+      <c r="E3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F3">
+        <v>2101989</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>504</v>
+      </c>
+      <c r="H3" s="89" t="s">
+        <v>468</v>
+      </c>
+      <c r="I3" s="86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.25">
       <c r="A4" t="s">
         <v>404</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="C4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4">
+        <v>1717550</v>
+      </c>
+      <c r="G4" s="88" t="s">
+        <v>506</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>407</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="C5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F5">
+        <v>630470</v>
+      </c>
+      <c r="G5" s="88" t="s">
+        <v>499</v>
+      </c>
+      <c r="H5" s="89" t="s">
+        <v>470</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>408</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="C6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E6" t="s">
+        <v>437</v>
+      </c>
+      <c r="F6">
+        <v>630500</v>
+      </c>
+      <c r="G6" s="88" t="s">
+        <v>500</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>410</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D7" t="s">
+        <v>475</v>
+      </c>
+      <c r="E7" t="s">
+        <v>437</v>
+      </c>
+      <c r="F7">
+        <v>1830730</v>
+      </c>
+      <c r="G7" s="88" t="s">
+        <v>501</v>
+      </c>
+      <c r="H7" s="89" t="s">
+        <v>465</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.25">
       <c r="A8" t="s">
         <v>411</v>
       </c>
       <c r="B8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>473</v>
+      </c>
+      <c r="D8" t="s">
+        <v>507</v>
+      </c>
+      <c r="E8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F8">
+        <v>1830725</v>
+      </c>
+      <c r="G8" s="88" t="s">
+        <v>508</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.25">
       <c r="A9" t="s">
         <v>414</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="C9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E9" t="s">
+        <v>437</v>
+      </c>
+      <c r="F9">
+        <v>1830729</v>
+      </c>
+      <c r="G9" s="88" t="s">
+        <v>503</v>
+      </c>
+      <c r="H9" s="89" t="s">
+        <v>466</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.25">
       <c r="A10" t="s">
         <v>415</v>
       </c>
       <c r="B10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="C10" t="s">
+        <v>473</v>
+      </c>
+      <c r="D10" t="s">
+        <v>507</v>
+      </c>
+      <c r="E10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F10">
+        <v>1830725</v>
+      </c>
+      <c r="G10" s="88" t="s">
+        <v>508</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>413</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15">
+      <c r="I11" s="86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>409</v>
       </c>
@@ -7990,239 +8305,360 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" t="s">
+        <v>494</v>
+      </c>
+      <c r="E14" t="s">
+        <v>437</v>
+      </c>
+      <c r="F14">
+        <v>1892523</v>
+      </c>
+      <c r="G14" s="88" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>478</v>
+      </c>
+      <c r="D15" t="s">
+        <v>484</v>
+      </c>
+      <c r="E15" t="s">
+        <v>480</v>
+      </c>
+      <c r="F15" t="s">
+        <v>484</v>
+      </c>
+      <c r="G15" s="88" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>477</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D16" t="s">
+        <v>481</v>
+      </c>
+      <c r="E16" t="s">
+        <v>480</v>
+      </c>
+      <c r="F16" t="s">
+        <v>481</v>
+      </c>
+      <c r="G16" s="88" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>412</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>412</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D17" t="s">
+        <v>490</v>
+      </c>
+      <c r="E17" t="s">
+        <v>437</v>
+      </c>
+      <c r="F17">
+        <v>2352005</v>
+      </c>
+      <c r="G17" s="88" t="s">
+        <v>496</v>
+      </c>
+      <c r="H17" s="89" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>479</v>
+      </c>
+      <c r="D19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E19" t="s">
+        <v>437</v>
+      </c>
+      <c r="F19">
+        <v>2535699</v>
+      </c>
+      <c r="G19" s="88" t="s">
+        <v>498</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="5" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15">
-      <c r="A20" s="5" t="s">
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
+      <c r="C22" t="s">
+        <v>445</v>
+      </c>
+      <c r="D22" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F22">
+        <v>9599568</v>
+      </c>
+      <c r="G22" s="88" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
         <v>421</v>
       </c>
-      <c r="C21" t="s">
-        <v>446</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="H23" s="89" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>422</v>
+      </c>
+      <c r="C24" t="s">
         <v>445</v>
       </c>
-      <c r="E21" t="s">
-        <v>438</v>
-      </c>
-      <c r="F21">
-        <v>9599568</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>422</v>
-      </c>
-      <c r="H22" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>423</v>
-      </c>
-      <c r="C23" t="s">
-        <v>446</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
+        <v>448</v>
+      </c>
+      <c r="E24" t="s">
+        <v>437</v>
+      </c>
+      <c r="F24">
+        <v>860414</v>
+      </c>
+      <c r="G24" s="88" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>425</v>
+      </c>
+      <c r="C25" t="s">
+        <v>451</v>
+      </c>
+      <c r="D25" t="s">
+        <v>450</v>
+      </c>
+      <c r="E25" t="s">
+        <v>437</v>
+      </c>
+      <c r="F25">
+        <v>4668791</v>
+      </c>
+      <c r="G25" s="88" t="s">
         <v>449</v>
       </c>
-      <c r="E23" t="s">
-        <v>438</v>
-      </c>
-      <c r="F23">
-        <v>860414</v>
-      </c>
-      <c r="G23" s="42" t="s">
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>426</v>
-      </c>
-      <c r="C24" t="s">
-        <v>452</v>
-      </c>
-      <c r="D24" t="s">
-        <v>451</v>
-      </c>
-      <c r="E24" t="s">
-        <v>438</v>
-      </c>
-      <c r="F24">
-        <v>4668791</v>
-      </c>
-      <c r="G24" s="42" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
+      <c r="C28" t="s">
+        <v>443</v>
+      </c>
+      <c r="D28" t="s">
+        <v>442</v>
+      </c>
+      <c r="E28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F28">
+        <v>2501338</v>
+      </c>
+      <c r="G28" s="88" t="s">
+        <v>431</v>
+      </c>
+      <c r="H28" s="89" t="s">
         <v>430</v>
       </c>
-      <c r="C27" t="s">
-        <v>444</v>
-      </c>
-      <c r="D27" t="s">
-        <v>443</v>
-      </c>
-      <c r="E27" t="s">
-        <v>438</v>
-      </c>
-      <c r="F27">
-        <v>2501338</v>
-      </c>
-      <c r="G27" s="42" t="s">
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
         <v>432</v>
       </c>
-      <c r="H27" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>433</v>
-      </c>
-      <c r="C28" t="s">
-        <v>442</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C29" t="s">
         <v>441</v>
-      </c>
-      <c r="E28" t="s">
-        <v>438</v>
-      </c>
-      <c r="F28">
-        <v>3026838</v>
-      </c>
-      <c r="G28" s="42" t="s">
-        <v>434</v>
-      </c>
-      <c r="H28" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>436</v>
-      </c>
-      <c r="C29" t="s">
-        <v>439</v>
       </c>
       <c r="D29" t="s">
         <v>440</v>
       </c>
       <c r="E29" t="s">
+        <v>437</v>
+      </c>
+      <c r="F29">
+        <v>3026838</v>
+      </c>
+      <c r="G29" s="88" t="s">
+        <v>433</v>
+      </c>
+      <c r="H29" s="89" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>435</v>
+      </c>
+      <c r="C30" t="s">
         <v>438</v>
       </c>
-      <c r="F29">
+      <c r="D30" t="s">
+        <v>439</v>
+      </c>
+      <c r="E30" t="s">
+        <v>437</v>
+      </c>
+      <c r="F30">
         <v>537056</v>
       </c>
-      <c r="G29" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="H29" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>448</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="G30" s="88" t="s">
+        <v>436</v>
+      </c>
+      <c r="H30" s="89" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>447</v>
+      </c>
+      <c r="H31" s="89" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15">
-      <c r="A35" s="5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>425</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>459</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C37" s="42" t="s">
         <v>458</v>
       </c>
-      <c r="E36" t="s">
-        <v>438</v>
-      </c>
-      <c r="F36">
+      <c r="D37" t="s">
+        <v>457</v>
+      </c>
+      <c r="E37" t="s">
+        <v>437</v>
+      </c>
+      <c r="F37">
         <v>1014356</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="G37" s="88" t="s">
+        <v>455</v>
+      </c>
+      <c r="H37" s="89" t="s">
         <v>456</v>
       </c>
-      <c r="H36" t="s">
-        <v>457</v>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>476</v>
+      </c>
+      <c r="E38" t="s">
+        <v>492</v>
+      </c>
+      <c r="G38" s="88" t="s">
+        <v>491</v>
+      </c>
+      <c r="H38" s="89" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{81F61562-A769-40D5-8796-B69511767642}"/>
-    <hyperlink ref="G23" r:id="rId2" xr:uid="{232BAE3F-A975-4D69-B8C5-5954671752F8}"/>
-    <hyperlink ref="G27" r:id="rId3" xr:uid="{7BEF299E-ADE1-4AE2-84DA-D66885D54700}"/>
-    <hyperlink ref="G28" r:id="rId4" xr:uid="{1EF8ACF8-D561-47BA-963C-C17B2436FD60}"/>
-    <hyperlink ref="G29" r:id="rId5" xr:uid="{941E74FF-2356-4A7D-8B65-A589D7839EB8}"/>
-    <hyperlink ref="G21" r:id="rId6" xr:uid="{86A28CA9-935E-4116-A8B7-E2D4F282CADE}"/>
-    <hyperlink ref="G24" r:id="rId7" xr:uid="{1EF97BBF-089A-430A-8FE3-449902852987}"/>
-    <hyperlink ref="G36" r:id="rId8" xr:uid="{DE4C2826-E46B-4367-AEEB-F0D92150305C}"/>
-    <hyperlink ref="C36" r:id="rId9" display="https://uk.farnell.com/c/tools-production-supplies/tools-hand-workholding/tweezers?brand=weller-erem" xr:uid="{917B40B0-07FF-440B-9D2C-F8AF28993DED}"/>
+    <hyperlink ref="G24" r:id="rId2" xr:uid="{232BAE3F-A975-4D69-B8C5-5954671752F8}"/>
+    <hyperlink ref="G28" r:id="rId3" xr:uid="{7BEF299E-ADE1-4AE2-84DA-D66885D54700}"/>
+    <hyperlink ref="G29" r:id="rId4" xr:uid="{1EF8ACF8-D561-47BA-963C-C17B2436FD60}"/>
+    <hyperlink ref="G30" r:id="rId5" xr:uid="{941E74FF-2356-4A7D-8B65-A589D7839EB8}"/>
+    <hyperlink ref="G22" r:id="rId6" xr:uid="{86A28CA9-935E-4116-A8B7-E2D4F282CADE}"/>
+    <hyperlink ref="G25" r:id="rId7" xr:uid="{1EF97BBF-089A-430A-8FE3-449902852987}"/>
+    <hyperlink ref="G37" r:id="rId8" xr:uid="{DE4C2826-E46B-4367-AEEB-F0D92150305C}"/>
+    <hyperlink ref="C37" r:id="rId9" display="https://uk.farnell.com/c/tools-production-supplies/tools-hand-workholding/tweezers?brand=weller-erem" xr:uid="{917B40B0-07FF-440B-9D2C-F8AF28993DED}"/>
+    <hyperlink ref="G16" r:id="rId10" xr:uid="{373A5412-0A17-4756-A341-D88686C310BA}"/>
+    <hyperlink ref="G15" r:id="rId11" xr:uid="{72DE6257-C00D-42BB-B6D1-77AEBD682242}"/>
+    <hyperlink ref="G38" r:id="rId12" xr:uid="{E49FC62D-B88E-448E-80D3-072B4D7B280E}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{FA23C137-7EB9-45FE-82E6-4F9F1CA8AA00}"/>
+    <hyperlink ref="G17" r:id="rId14" xr:uid="{15ECBC9E-6A2F-4935-9B04-1F32F88C4F4B}"/>
+    <hyperlink ref="G19" r:id="rId15" xr:uid="{91CC90B2-5C73-4009-B98B-B8C12E258ED9}"/>
+    <hyperlink ref="G5" r:id="rId16" xr:uid="{ABD12F70-021C-46BD-B9FC-5F60F3665048}"/>
+    <hyperlink ref="G6" r:id="rId17" xr:uid="{37354371-A569-4927-BFDA-ECE185A7C31D}"/>
+    <hyperlink ref="G7" r:id="rId18" xr:uid="{D22DAF63-E16A-4602-86FB-06B6B540BFAF}"/>
+    <hyperlink ref="G9" r:id="rId19" xr:uid="{D37D6084-73B8-46F8-8866-07FD49CEB2A1}"/>
+    <hyperlink ref="G4" r:id="rId20" xr:uid="{92210B68-E3C2-4088-8C41-2E709D3802DB}"/>
+    <hyperlink ref="G8" r:id="rId21" xr:uid="{8F920A40-6A6E-4BE7-BF13-3C62E8E82B34}"/>
+    <hyperlink ref="G10" r:id="rId22" xr:uid="{AD274C07-47C7-4169-99EC-60E084EF8046}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8230,9 +8666,30 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:B4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="42.75">
+      <c r="A4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAFA31B-97F7-4166-B0E2-B7C34572EB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF9B19B-4226-467E-8D4D-B07375EA571C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53100" yWindow="2370" windowWidth="28905" windowHeight="16320" tabRatio="745" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
+    <workbookView xWindow="34530" yWindow="12600" windowWidth="21600" windowHeight="12645" tabRatio="745" activeTab="6" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="551">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -1606,12 +1606,138 @@
   <si>
     <t>https://uk.farnell.com/jst-japan-solderless-terminals/sphd-002t-p0-5/crimp-socket-24-28awg/dp/1830725?MER=sy-me-pd-mi-acce</t>
   </si>
+  <si>
+    <t>C8B</t>
+  </si>
+  <si>
+    <t>Too close to through hole metal pin of programming header</t>
+  </si>
+  <si>
+    <t>D8B</t>
+  </si>
+  <si>
+    <t>Overlaps connector</t>
+  </si>
+  <si>
+    <t>U3B</t>
+  </si>
+  <si>
+    <t>Designator visible - overlaps pads</t>
+  </si>
+  <si>
+    <t>Via tenting</t>
+  </si>
+  <si>
+    <t>Board edge clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camera connector </t>
+  </si>
+  <si>
+    <t>Add 2 way header</t>
+  </si>
+  <si>
+    <t>Identified by Initials &amp; Date</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Rev A</t>
+  </si>
+  <si>
+    <t>ACB 15 Dec 2025</t>
+  </si>
+  <si>
+    <t>Problem Fixed In</t>
+  </si>
+  <si>
+    <t>Problem Found In</t>
+  </si>
+  <si>
+    <t>CAN peripheral not on current uC</t>
+  </si>
+  <si>
+    <t>Can peripheral on uC would make programming comms easier</t>
+  </si>
+  <si>
+    <t>Silkscreen truncated</t>
+  </si>
+  <si>
+    <t>Not all vias tented</t>
+  </si>
+  <si>
+    <t>Tracks &amp; holes too close to board edge. Create new rule</t>
+  </si>
+  <si>
+    <t>Programming adaptor breakout</t>
+  </si>
+  <si>
+    <t>RX TX crossed - rewire</t>
+  </si>
+  <si>
+    <t>Not going to be re-layed out. Modify Rev A adaptors to use pinout as defined for other serial connections</t>
+  </si>
+  <si>
+    <t>Blob links unnecessary</t>
+  </si>
+  <si>
+    <t>Remove blob links</t>
+  </si>
+  <si>
+    <t>PFETs wrong</t>
+  </si>
+  <si>
+    <t>Drain Source swapped on symbol</t>
+  </si>
+  <si>
+    <t>Boot address</t>
+  </si>
+  <si>
+    <t>Check default boot address so don't have to set option bytes. Possibly invert BOOT</t>
+  </si>
+  <si>
+    <t>Magnitude and direction</t>
+  </si>
+  <si>
+    <t>Should read Direction and Magnitude</t>
+  </si>
+  <si>
+    <t>Can't do without redoing programming adaptor</t>
+  </si>
+  <si>
+    <t>Fixed by Initial &amp; Date</t>
+  </si>
+  <si>
+    <t>Rev B</t>
+  </si>
+  <si>
+    <t>Surge current</t>
+  </si>
+  <si>
+    <t>Check e-match igniton current profile</t>
+  </si>
+  <si>
+    <t>Brown out reset</t>
+  </si>
+  <si>
+    <t>OUT_P1</t>
+  </si>
+  <si>
+    <t>Check uC bulk capacitance needed</t>
+  </si>
+  <si>
+    <t>Cost of multiple designs per PCB</t>
+  </si>
+  <si>
+    <t>Only do main PCB - delete ancillaries &amp; keyfob</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1680,8 +1806,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1721,6 +1853,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1869,7 +2007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1997,6 +2135,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2114,10 +2254,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3780,31 +3919,31 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15" thickBot="1"/>
     <row r="3" spans="2:16" ht="15" thickBot="1">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="84" t="s">
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="K3" s="80" t="s">
+      <c r="K3" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="L3" s="82" t="s">
+      <c r="L3" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="M3" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="79"/>
+      <c r="N3" s="81"/>
     </row>
     <row r="4" spans="2:16" ht="96.75" customHeight="1" thickBot="1">
       <c r="B4" s="27" t="s">
@@ -3828,10 +3967,10 @@
       <c r="H4" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="85"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="83"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="85"/>
       <c r="M4" s="11" t="s">
         <v>81</v>
       </c>
@@ -3843,43 +3982,43 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15" thickTop="1">
-      <c r="B5" s="63">
+      <c r="B5" s="65">
         <v>2</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="65">
         <v>1</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="65">
         <v>2</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="65">
         <v>2</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="66">
         <v>2</v>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="65">
         <v>2</v>
       </c>
-      <c r="H5" s="72" t="s">
+      <c r="H5" s="74" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="63" t="s">
+      <c r="K5" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="62" t="s">
+      <c r="L5" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="64" t="s">
         <v>85</v>
       </c>
       <c r="P5" t="s">
@@ -3887,60 +4026,60 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="15" thickBot="1">
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="58"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="60"/>
       <c r="I6" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="50">
+      <c r="B7" s="52">
         <v>3</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="52">
         <v>2</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="52">
         <v>3</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="52">
         <v>3</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="61">
         <v>3</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="52">
         <v>3</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="58" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="50" t="s">
+      <c r="J7" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="50" t="s">
+      <c r="K7" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="47" t="s">
+      <c r="L7" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="49" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
@@ -3948,21 +4087,21 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="58"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="60"/>
       <c r="I8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1">
       <c r="B9" s="17">
@@ -4047,37 +4186,37 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="24">
-      <c r="B11" s="50">
+      <c r="B11" s="52">
         <v>5</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="52">
         <v>5</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="52">
         <v>6</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="52">
         <v>6</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="61">
         <v>6</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="52">
         <v>6</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="74" t="s">
+      <c r="I11" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="J11" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="56" t="s">
+      <c r="K11" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="29" t="s">
@@ -4091,17 +4230,17 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="24">
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="48"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="50"/>
       <c r="M12" s="14" t="s">
         <v>104</v>
       </c>
@@ -4110,17 +4249,17 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="24">
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="48"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="14" t="s">
         <v>105</v>
       </c>
@@ -4129,17 +4268,17 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="36">
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="48"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="50"/>
       <c r="M14" s="14" t="s">
         <v>106</v>
       </c>
@@ -4148,71 +4287,71 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="24">
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="48"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="50"/>
       <c r="M15" s="29" t="s">
         <v>107</v>
       </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="49"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="51"/>
       <c r="M16" s="21" t="s">
         <v>108</v>
       </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:16" ht="24">
-      <c r="B17" s="50">
+      <c r="B17" s="52">
         <v>6</v>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="52">
         <v>6</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="52">
         <v>7</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <v>7</v>
       </c>
-      <c r="F17" s="59">
+      <c r="F17" s="61">
         <v>7</v>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="52">
         <v>7</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="I17" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="50" t="s">
+      <c r="J17" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="47" t="s">
+      <c r="L17" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -4223,17 +4362,17 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="24">
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="50"/>
       <c r="M18" s="23" t="s">
         <v>116</v>
       </c>
@@ -4242,122 +4381,122 @@
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="48"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="50"/>
       <c r="M19" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="2:16" ht="24">
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="48"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="50"/>
       <c r="M20" s="23" t="s">
         <v>118</v>
       </c>
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="2:16" ht="24">
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="48"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="2:16" ht="24">
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="50"/>
       <c r="M22" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="49"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="51"/>
       <c r="M23" s="40" t="s">
         <v>121</v>
       </c>
       <c r="N23" s="24"/>
     </row>
     <row r="24" spans="2:16" ht="36">
-      <c r="B24" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="50">
+      <c r="B24" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="52">
         <v>8</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <v>8</v>
       </c>
-      <c r="F24" s="59">
+      <c r="F24" s="61">
         <v>8</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="52">
         <v>8</v>
       </c>
-      <c r="H24" s="56" t="s">
+      <c r="H24" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="47" t="s">
+      <c r="I24" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="50" t="s">
+      <c r="J24" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="56" t="s">
+      <c r="K24" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="47" t="s">
+      <c r="L24" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -4368,17 +4507,17 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="24">
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="48"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="29" t="s">
         <v>125</v>
       </c>
@@ -4390,17 +4529,17 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="24">
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="48"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="50"/>
       <c r="M26" s="14" t="s">
         <v>126</v>
       </c>
@@ -4409,17 +4548,17 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="49"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="51"/>
       <c r="M27" s="19" t="s">
         <v>127</v>
       </c>
@@ -4428,37 +4567,37 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="24">
-      <c r="B28" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="50">
+      <c r="B28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="52">
         <v>9</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <v>9</v>
       </c>
-      <c r="F28" s="59">
+      <c r="F28" s="61">
         <v>9</v>
       </c>
-      <c r="G28" s="50">
+      <c r="G28" s="52">
         <v>9</v>
       </c>
-      <c r="H28" s="56" t="s">
+      <c r="H28" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="I28" s="47" t="s">
+      <c r="I28" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="50" t="s">
+      <c r="J28" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="50" t="s">
+      <c r="K28" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L28" s="47" t="s">
+      <c r="L28" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M28" s="14" t="s">
@@ -4469,17 +4608,17 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="48"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="50"/>
       <c r="M29" s="14" t="s">
         <v>135</v>
       </c>
@@ -4488,71 +4627,71 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="24">
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="48"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="50"/>
       <c r="M30" s="29" t="s">
         <v>103</v>
       </c>
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="49"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="51"/>
       <c r="M31" s="40" t="s">
         <v>136</v>
       </c>
       <c r="N31" s="24"/>
     </row>
     <row r="32" spans="2:16" ht="24">
-      <c r="B32" s="50">
+      <c r="B32" s="52">
         <v>7</v>
       </c>
-      <c r="C32" s="50">
+      <c r="C32" s="52">
         <v>7</v>
       </c>
-      <c r="D32" s="50">
+      <c r="D32" s="52">
         <v>10</v>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <v>10</v>
       </c>
-      <c r="F32" s="59">
+      <c r="F32" s="61">
         <v>10</v>
       </c>
-      <c r="G32" s="50">
+      <c r="G32" s="52">
         <v>10</v>
       </c>
-      <c r="H32" s="56" t="s">
+      <c r="H32" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="50" t="s">
+      <c r="J32" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="56" t="s">
+      <c r="K32" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="L32" s="47" t="s">
+      <c r="L32" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M32" s="14" t="s">
@@ -4563,17 +4702,17 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="24">
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="48"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="50"/>
       <c r="M33" s="14" t="s">
         <v>104</v>
       </c>
@@ -4582,17 +4721,17 @@
       </c>
     </row>
     <row r="34" spans="2:16" ht="36">
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="48"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="50"/>
       <c r="M34" s="14" t="s">
         <v>140</v>
       </c>
@@ -4604,105 +4743,105 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="24">
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="48"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="50"/>
       <c r="M35" s="23" t="s">
         <v>141</v>
       </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="48"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="50"/>
       <c r="M36" s="14" t="s">
         <v>142</v>
       </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" spans="2:16" ht="24">
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="48"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="62"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="50"/>
       <c r="M37" s="37" t="s">
         <v>126</v>
       </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="49"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="51"/>
       <c r="M38" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N38" s="18"/>
     </row>
     <row r="39" spans="2:16" ht="24.75" thickTop="1">
-      <c r="B39" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="63">
+      <c r="B39" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="65">
         <v>8</v>
       </c>
-      <c r="D39" s="63">
+      <c r="D39" s="65">
         <v>11</v>
       </c>
-      <c r="E39" s="63">
+      <c r="E39" s="65">
         <v>11</v>
       </c>
-      <c r="F39" s="64">
+      <c r="F39" s="66">
         <v>11</v>
       </c>
-      <c r="G39" s="63">
+      <c r="G39" s="65">
         <v>11</v>
       </c>
-      <c r="H39" s="72" t="s">
+      <c r="H39" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="62" t="s">
+      <c r="I39" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="J39" s="63" t="s">
+      <c r="J39" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="72" t="s">
+      <c r="K39" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="62" t="s">
+      <c r="L39" s="64" t="s">
         <v>88</v>
       </c>
       <c r="M39" s="14" t="s">
@@ -4713,17 +4852,17 @@
       </c>
     </row>
     <row r="40" spans="2:16" ht="24">
-      <c r="B40" s="48"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="48"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="50"/>
       <c r="M40" s="14" t="s">
         <v>116</v>
       </c>
@@ -4732,17 +4871,17 @@
       </c>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="48"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="48"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="50"/>
       <c r="M41" s="14" t="s">
         <v>142</v>
       </c>
@@ -4754,60 +4893,60 @@
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1">
-      <c r="B42" s="49"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="49"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="51"/>
       <c r="M42" s="19" t="s">
         <v>147</v>
       </c>
       <c r="N42" s="18"/>
     </row>
     <row r="43" spans="2:16">
-      <c r="B43" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="50">
+      <c r="B43" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="52">
         <v>9</v>
       </c>
-      <c r="D43" s="50">
+      <c r="D43" s="52">
         <v>12</v>
       </c>
-      <c r="E43" s="50">
+      <c r="E43" s="52">
         <v>12</v>
       </c>
-      <c r="F43" s="59">
+      <c r="F43" s="61">
         <v>12</v>
       </c>
-      <c r="G43" s="50">
+      <c r="G43" s="52">
         <v>12</v>
       </c>
-      <c r="H43" s="56" t="s">
+      <c r="H43" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="50" t="s">
+      <c r="J43" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="50" t="s">
+      <c r="K43" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L43" s="47" t="s">
+      <c r="L43" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N43" s="71" t="s">
+      <c r="N43" s="73" t="s">
         <v>154</v>
       </c>
       <c r="P43" t="s">
@@ -4815,143 +4954,143 @@
       </c>
     </row>
     <row r="44" spans="2:16" ht="24">
-      <c r="B44" s="48"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="51"/>
-      <c r="L44" s="48"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="50"/>
       <c r="M44" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N44" s="66"/>
+      <c r="N44" s="68"/>
     </row>
     <row r="45" spans="2:16" ht="24">
-      <c r="B45" s="48"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="51"/>
-      <c r="L45" s="48"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="62"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="50"/>
       <c r="M45" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="66"/>
+      <c r="N45" s="68"/>
     </row>
     <row r="46" spans="2:16" ht="24">
-      <c r="B46" s="48"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="51"/>
-      <c r="K46" s="51"/>
-      <c r="L46" s="48"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="50"/>
       <c r="M46" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N46" s="66"/>
+      <c r="N46" s="68"/>
     </row>
     <row r="47" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B47" s="49"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="49"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="51"/>
       <c r="M47" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N47" s="67"/>
+      <c r="N47" s="69"/>
     </row>
     <row r="48" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B48" s="50">
+      <c r="B48" s="52">
         <v>8</v>
       </c>
-      <c r="C48" s="50">
+      <c r="C48" s="52">
         <v>10</v>
       </c>
-      <c r="D48" s="50">
+      <c r="D48" s="52">
         <v>13</v>
       </c>
-      <c r="E48" s="50">
+      <c r="E48" s="52">
         <v>13</v>
       </c>
-      <c r="F48" s="59">
+      <c r="F48" s="61">
         <v>13</v>
       </c>
-      <c r="G48" s="50">
+      <c r="G48" s="52">
         <v>13</v>
       </c>
-      <c r="H48" s="56" t="s">
+      <c r="H48" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="47" t="s">
+      <c r="I48" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="50" t="s">
+      <c r="J48" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L48" s="47" t="s">
+      <c r="L48" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M48" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N48" s="47" t="s">
+      <c r="N48" s="49" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24">
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="60"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="51"/>
-      <c r="K49" s="51"/>
-      <c r="L49" s="48"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="50"/>
       <c r="M49" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N49" s="48"/>
+      <c r="N49" s="50"/>
     </row>
     <row r="50" spans="2:16" ht="24">
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="60"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="48"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="50"/>
       <c r="M50" s="14" t="s">
         <v>159</v>
       </c>
@@ -4963,88 +5102,88 @@
       </c>
     </row>
     <row r="51" spans="2:16" ht="24">
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="51"/>
-      <c r="K51" s="51"/>
-      <c r="L51" s="48"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="62"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="50"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="50"/>
       <c r="M51" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="2:16" ht="24">
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="51"/>
-      <c r="K52" s="51"/>
-      <c r="L52" s="48"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="62"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="50"/>
       <c r="M52" s="14" t="s">
         <v>115</v>
       </c>
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="52"/>
-      <c r="K53" s="52"/>
-      <c r="L53" s="49"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="60"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="51"/>
       <c r="M53" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N53" s="24"/>
     </row>
     <row r="54" spans="2:16" ht="24">
-      <c r="B54" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="50">
+      <c r="B54" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="52">
         <v>14</v>
       </c>
-      <c r="F54" s="59">
+      <c r="F54" s="61">
         <v>14</v>
       </c>
-      <c r="G54" s="50">
+      <c r="G54" s="52">
         <v>14</v>
       </c>
-      <c r="H54" s="56" t="s">
+      <c r="H54" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="71" t="s">
+      <c r="I54" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="J54" s="50" t="s">
+      <c r="J54" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="50" t="s">
+      <c r="K54" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="47" t="s">
+      <c r="L54" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M54" s="14" t="s">
@@ -5058,17 +5197,17 @@
       </c>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="48"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="66"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="51"/>
-      <c r="L55" s="48"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="68"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="50"/>
       <c r="M55" s="14" t="s">
         <v>151</v>
       </c>
@@ -5077,88 +5216,88 @@
       </c>
     </row>
     <row r="56" spans="2:16">
-      <c r="B56" s="48"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="51"/>
-      <c r="K56" s="51"/>
-      <c r="L56" s="48"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="68"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="50"/>
       <c r="M56" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" spans="2:16" ht="24">
-      <c r="B57" s="48"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="48"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="68"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="50"/>
       <c r="M57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1">
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="67"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="49"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="69"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="51"/>
       <c r="M58" s="19" t="s">
         <v>162</v>
       </c>
       <c r="N58" s="18"/>
     </row>
     <row r="59" spans="2:16" ht="24">
-      <c r="B59" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="50">
+      <c r="B59" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="52">
         <v>11</v>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="52">
         <v>14</v>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="52">
         <v>15</v>
       </c>
-      <c r="F59" s="59">
+      <c r="F59" s="61">
         <v>15</v>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="52">
         <v>15</v>
       </c>
-      <c r="H59" s="56" t="s">
+      <c r="H59" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="71" t="s">
+      <c r="I59" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="50" t="s">
+      <c r="J59" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="50" t="s">
+      <c r="K59" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L59" s="47" t="s">
+      <c r="L59" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M59" s="14" t="s">
@@ -5172,17 +5311,17 @@
       </c>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" s="48"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="51"/>
-      <c r="E60" s="51"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="51"/>
-      <c r="K60" s="51"/>
-      <c r="L60" s="48"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="68"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="50"/>
       <c r="M60" s="14" t="s">
         <v>157</v>
       </c>
@@ -5191,51 +5330,51 @@
       </c>
     </row>
     <row r="61" spans="2:16" ht="24">
-      <c r="B61" s="48"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="51"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="51"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="66"/>
-      <c r="J61" s="51"/>
-      <c r="K61" s="51"/>
-      <c r="L61" s="48"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="68"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="50"/>
       <c r="M61" s="14" t="s">
         <v>104</v>
       </c>
       <c r="N61" s="22"/>
     </row>
     <row r="62" spans="2:16" ht="24">
-      <c r="B62" s="48"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="51"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="60"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="66"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="48"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="62"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="68"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="50"/>
       <c r="M62" s="13" t="s">
         <v>167</v>
       </c>
       <c r="N62" s="22"/>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1">
-      <c r="B63" s="49"/>
-      <c r="C63" s="52"/>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="67"/>
-      <c r="J63" s="52"/>
-      <c r="K63" s="52"/>
-      <c r="L63" s="49"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="51"/>
       <c r="M63" s="19" t="s">
         <v>168</v>
       </c>
@@ -5365,43 +5504,43 @@
       </c>
     </row>
     <row r="67" spans="2:16" ht="36">
-      <c r="B67" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="50">
+      <c r="B67" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="52">
         <v>18</v>
       </c>
-      <c r="F67" s="59">
+      <c r="F67" s="61">
         <v>18</v>
       </c>
-      <c r="G67" s="50">
+      <c r="G67" s="52">
         <v>18</v>
       </c>
-      <c r="H67" s="56" t="s">
+      <c r="H67" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="I67" s="71" t="s">
+      <c r="I67" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="50" t="s">
+      <c r="J67" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="50" t="s">
+      <c r="K67" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="47" t="s">
+      <c r="L67" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M67" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="N67" s="47" t="s">
+      <c r="N67" s="49" t="s">
         <v>88</v>
       </c>
       <c r="P67" t="s">
@@ -5409,860 +5548,860 @@
       </c>
     </row>
     <row r="68" spans="2:16" ht="24">
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="60"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="66"/>
-      <c r="J68" s="51"/>
-      <c r="K68" s="51"/>
-      <c r="L68" s="48"/>
+      <c r="B68" s="50"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="50"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="62"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="68"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+      <c r="L68" s="50"/>
       <c r="M68" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N68" s="48"/>
+      <c r="N68" s="50"/>
     </row>
     <row r="69" spans="2:16" ht="24">
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="51"/>
-      <c r="L69" s="48"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="62"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="68"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="53"/>
+      <c r="L69" s="50"/>
       <c r="M69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="48"/>
+      <c r="N69" s="50"/>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1">
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="52"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="67"/>
-      <c r="J70" s="52"/>
-      <c r="K70" s="52"/>
-      <c r="L70" s="49"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="69"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="L70" s="51"/>
       <c r="M70" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N70" s="49"/>
+      <c r="N70" s="51"/>
     </row>
     <row r="71" spans="2:16" ht="24">
-      <c r="B71" s="50">
+      <c r="B71" s="52">
         <v>11</v>
       </c>
-      <c r="C71" s="50">
+      <c r="C71" s="52">
         <v>14</v>
       </c>
-      <c r="D71" s="50">
+      <c r="D71" s="52">
         <v>17</v>
       </c>
-      <c r="E71" s="50">
+      <c r="E71" s="52">
         <v>19</v>
       </c>
-      <c r="F71" s="59">
+      <c r="F71" s="61">
         <v>19</v>
       </c>
-      <c r="G71" s="50">
+      <c r="G71" s="52">
         <v>19</v>
       </c>
-      <c r="H71" s="56" t="s">
+      <c r="H71" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="47" t="s">
+      <c r="I71" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="J71" s="50" t="s">
+      <c r="J71" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K71" s="50" t="s">
+      <c r="K71" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="L71" s="47" t="s">
+      <c r="L71" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M71" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="N71" s="47" t="s">
+      <c r="N71" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="24">
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="51"/>
-      <c r="L72" s="48"/>
+      <c r="B72" s="53"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="62"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="50"/>
       <c r="M72" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N72" s="48"/>
+      <c r="N72" s="50"/>
     </row>
     <row r="73" spans="2:16" ht="24">
-      <c r="B73" s="51"/>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="60"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="51"/>
-      <c r="K73" s="51"/>
-      <c r="L73" s="48"/>
+      <c r="B73" s="53"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="62"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="50"/>
       <c r="M73" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="N73" s="48"/>
+      <c r="N73" s="50"/>
     </row>
     <row r="74" spans="2:16" ht="48.75" thickBot="1">
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="49"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="49"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54"/>
+      <c r="L74" s="51"/>
       <c r="M74" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N74" s="49"/>
+      <c r="N74" s="51"/>
     </row>
     <row r="75" spans="2:16" ht="36.75" thickTop="1">
-      <c r="B75" s="63">
+      <c r="B75" s="65">
         <v>12</v>
       </c>
-      <c r="C75" s="63">
+      <c r="C75" s="65">
         <v>15</v>
       </c>
-      <c r="D75" s="63">
+      <c r="D75" s="65">
         <v>18</v>
       </c>
-      <c r="E75" s="63">
+      <c r="E75" s="65">
         <v>20</v>
       </c>
-      <c r="F75" s="64">
+      <c r="F75" s="66">
         <v>20</v>
       </c>
-      <c r="G75" s="63">
+      <c r="G75" s="65">
         <v>20</v>
       </c>
-      <c r="H75" s="72" t="s">
+      <c r="H75" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="62" t="s">
+      <c r="I75" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="J75" s="63" t="s">
+      <c r="J75" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="63" t="s">
+      <c r="K75" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="L75" s="73">
+      <c r="L75" s="75">
         <v>-7</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="62" t="s">
+      <c r="N75" s="64" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="24">
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="51"/>
-      <c r="K76" s="51"/>
-      <c r="L76" s="69"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="62"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="71"/>
       <c r="M76" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="48"/>
+      <c r="N76" s="50"/>
     </row>
     <row r="77" spans="2:16" ht="24">
-      <c r="B77" s="51"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="51"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="51"/>
-      <c r="K77" s="51"/>
-      <c r="L77" s="69"/>
+      <c r="B77" s="53"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="62"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="53"/>
+      <c r="K77" s="53"/>
+      <c r="L77" s="71"/>
       <c r="M77" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="N77" s="48"/>
+      <c r="N77" s="50"/>
     </row>
     <row r="78" spans="2:16">
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="51"/>
-      <c r="K78" s="51"/>
-      <c r="L78" s="69"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="62"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="50"/>
+      <c r="J78" s="53"/>
+      <c r="K78" s="53"/>
+      <c r="L78" s="71"/>
       <c r="M78" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N78" s="48"/>
+      <c r="N78" s="50"/>
     </row>
     <row r="79" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="52"/>
-      <c r="K79" s="52"/>
-      <c r="L79" s="70"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="51"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="54"/>
+      <c r="L79" s="72"/>
       <c r="M79" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="49"/>
+      <c r="N79" s="51"/>
     </row>
     <row r="80" spans="2:16">
-      <c r="B80" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D80" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="F80" s="59">
+      <c r="B80" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="61">
         <v>21</v>
       </c>
-      <c r="G80" s="50">
+      <c r="G80" s="52">
         <v>21</v>
       </c>
-      <c r="H80" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80" s="47" t="s">
+      <c r="H80" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="J80" s="50" t="s">
+      <c r="J80" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K80" s="50" t="s">
+      <c r="K80" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L80" s="47" t="s">
+      <c r="L80" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M80" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N80" s="47" t="s">
+      <c r="N80" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:19" ht="48">
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="60"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="51"/>
-      <c r="L81" s="48"/>
+      <c r="B81" s="50"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="62"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="50"/>
       <c r="M81" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="N81" s="48"/>
+      <c r="N81" s="50"/>
     </row>
     <row r="82" spans="2:19" ht="24">
-      <c r="B82" s="48"/>
-      <c r="C82" s="48"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="60"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="51"/>
-      <c r="L82" s="48"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="N82" s="48"/>
+      <c r="N82" s="50"/>
     </row>
     <row r="83" spans="2:19" ht="48.75" thickBot="1">
-      <c r="B83" s="49"/>
-      <c r="C83" s="49"/>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="61"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
-      <c r="L83" s="49"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="51"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="54"/>
+      <c r="K83" s="54"/>
+      <c r="L83" s="51"/>
       <c r="M83" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N83" s="49"/>
+      <c r="N83" s="51"/>
     </row>
     <row r="84" spans="2:19">
-      <c r="B84" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="59">
+      <c r="B84" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="61">
         <v>22</v>
       </c>
-      <c r="G84" s="50">
+      <c r="G84" s="52">
         <v>22</v>
       </c>
-      <c r="H84" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84" s="47" t="s">
+      <c r="H84" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="J84" s="50" t="s">
+      <c r="J84" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="50" t="s">
+      <c r="K84" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="47" t="s">
+      <c r="L84" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N84" s="47" t="s">
+      <c r="N84" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:19" ht="24">
-      <c r="B85" s="48"/>
-      <c r="C85" s="48"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
-      <c r="J85" s="51"/>
-      <c r="K85" s="51"/>
-      <c r="L85" s="48"/>
+      <c r="B85" s="50"/>
+      <c r="C85" s="50"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="62"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="53"/>
+      <c r="K85" s="53"/>
+      <c r="L85" s="50"/>
       <c r="M85" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N85" s="48"/>
+      <c r="N85" s="50"/>
     </row>
     <row r="86" spans="2:19" ht="24">
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="51"/>
-      <c r="K86" s="51"/>
-      <c r="L86" s="48"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="50"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="50"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="53"/>
+      <c r="L86" s="50"/>
       <c r="M86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N86" s="48"/>
+      <c r="N86" s="50"/>
       <c r="S86" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="61"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="49"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="54"/>
+      <c r="K87" s="54"/>
+      <c r="L87" s="51"/>
       <c r="M87" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="N87" s="49"/>
+      <c r="N87" s="51"/>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="50">
+      <c r="B88" s="52">
         <v>13</v>
       </c>
-      <c r="C88" s="50">
+      <c r="C88" s="52">
         <v>16</v>
       </c>
-      <c r="D88" s="50">
+      <c r="D88" s="52">
         <v>19</v>
       </c>
-      <c r="E88" s="50">
+      <c r="E88" s="52">
         <v>21</v>
       </c>
-      <c r="F88" s="59">
+      <c r="F88" s="61">
         <v>23</v>
       </c>
-      <c r="G88" s="50">
+      <c r="G88" s="52">
         <v>23</v>
       </c>
-      <c r="H88" s="56" t="s">
+      <c r="H88" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="I88" s="47" t="s">
+      <c r="I88" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="J88" s="50" t="s">
+      <c r="J88" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K88" s="50" t="s">
+      <c r="K88" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="L88" s="47" t="s">
+      <c r="L88" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M88" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="N88" s="47" t="s">
+      <c r="N88" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="2:19" ht="24">
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="60"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="57"/>
-      <c r="I89" s="48"/>
-      <c r="J89" s="51"/>
-      <c r="K89" s="51"/>
-      <c r="L89" s="48"/>
+      <c r="B89" s="53"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="62"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="50"/>
       <c r="M89" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N89" s="48"/>
+      <c r="N89" s="50"/>
     </row>
     <row r="90" spans="2:19">
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="57"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="51"/>
-      <c r="K90" s="51"/>
-      <c r="L90" s="48"/>
+      <c r="B90" s="53"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="62"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="59"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="N90" s="48"/>
+      <c r="N90" s="50"/>
     </row>
     <row r="91" spans="2:19">
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="60"/>
-      <c r="G91" s="51"/>
-      <c r="H91" s="57"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="51"/>
-      <c r="K91" s="51"/>
-      <c r="L91" s="48"/>
+      <c r="B91" s="53"/>
+      <c r="C91" s="53"/>
+      <c r="D91" s="53"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="62"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="50"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="50"/>
       <c r="M91" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N91" s="48"/>
+      <c r="N91" s="50"/>
     </row>
     <row r="92" spans="2:19" ht="24">
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="60"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="57"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="51"/>
-      <c r="K92" s="51"/>
-      <c r="L92" s="48"/>
+      <c r="B92" s="53"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="59"/>
+      <c r="I92" s="50"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="50"/>
       <c r="M92" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="N92" s="48"/>
+      <c r="N92" s="50"/>
     </row>
     <row r="93" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B93" s="52"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="49"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="49"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="60"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="54"/>
+      <c r="K93" s="54"/>
+      <c r="L93" s="51"/>
       <c r="M93" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N93" s="49"/>
+      <c r="N93" s="51"/>
     </row>
     <row r="94" spans="2:19">
-      <c r="B94" s="50">
+      <c r="B94" s="52">
         <v>14</v>
       </c>
-      <c r="C94" s="50">
+      <c r="C94" s="52">
         <v>17</v>
       </c>
-      <c r="D94" s="50">
+      <c r="D94" s="52">
         <v>20</v>
       </c>
-      <c r="E94" s="50">
+      <c r="E94" s="52">
         <v>22</v>
       </c>
-      <c r="F94" s="59">
+      <c r="F94" s="61">
         <v>24</v>
       </c>
-      <c r="G94" s="50">
+      <c r="G94" s="52">
         <v>24</v>
       </c>
-      <c r="H94" s="56" t="s">
+      <c r="H94" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="I94" s="47" t="s">
+      <c r="I94" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="J94" s="50" t="s">
+      <c r="J94" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K94" s="50" t="s">
+      <c r="K94" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L94" s="68">
+      <c r="L94" s="70">
         <v>-7</v>
       </c>
       <c r="M94" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N94" s="47" t="s">
+      <c r="N94" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:19" ht="24">
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="60"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="51"/>
-      <c r="K95" s="51"/>
-      <c r="L95" s="69"/>
+      <c r="B95" s="53"/>
+      <c r="C95" s="53"/>
+      <c r="D95" s="53"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="62"/>
+      <c r="G95" s="53"/>
+      <c r="H95" s="59"/>
+      <c r="I95" s="50"/>
+      <c r="J95" s="53"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="71"/>
       <c r="M95" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="N95" s="48"/>
+      <c r="N95" s="50"/>
     </row>
     <row r="96" spans="2:19" ht="24">
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="60"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="57"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="51"/>
-      <c r="K96" s="51"/>
-      <c r="L96" s="69"/>
+      <c r="B96" s="53"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="59"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="71"/>
       <c r="M96" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N96" s="48"/>
+      <c r="N96" s="50"/>
     </row>
     <row r="97" spans="2:16" ht="24">
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="60"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="51"/>
-      <c r="K97" s="51"/>
-      <c r="L97" s="69"/>
+      <c r="B97" s="53"/>
+      <c r="C97" s="53"/>
+      <c r="D97" s="53"/>
+      <c r="E97" s="53"/>
+      <c r="F97" s="62"/>
+      <c r="G97" s="53"/>
+      <c r="H97" s="59"/>
+      <c r="I97" s="50"/>
+      <c r="J97" s="53"/>
+      <c r="K97" s="53"/>
+      <c r="L97" s="71"/>
       <c r="M97" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="N97" s="48"/>
+      <c r="N97" s="50"/>
     </row>
     <row r="98" spans="2:16">
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="60"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="57"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="51"/>
-      <c r="K98" s="51"/>
-      <c r="L98" s="69"/>
+      <c r="B98" s="53"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="59"/>
+      <c r="I98" s="50"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="71"/>
       <c r="M98" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N98" s="48"/>
+      <c r="N98" s="50"/>
     </row>
     <row r="99" spans="2:16" ht="24">
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="60"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="57"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="51"/>
-      <c r="K99" s="51"/>
-      <c r="L99" s="69"/>
+      <c r="B99" s="53"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="62"/>
+      <c r="G99" s="53"/>
+      <c r="H99" s="59"/>
+      <c r="I99" s="50"/>
+      <c r="J99" s="53"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="71"/>
       <c r="M99" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="N99" s="48"/>
+      <c r="N99" s="50"/>
     </row>
     <row r="100" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B100" s="52"/>
-      <c r="C100" s="52"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="52"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="49"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
-      <c r="L100" s="70"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="63"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="60"/>
+      <c r="I100" s="51"/>
+      <c r="J100" s="54"/>
+      <c r="K100" s="54"/>
+      <c r="L100" s="72"/>
       <c r="M100" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N100" s="49"/>
+      <c r="N100" s="51"/>
     </row>
     <row r="101" spans="2:16">
-      <c r="B101" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E101" s="50">
+      <c r="B101" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="52">
         <v>23</v>
       </c>
-      <c r="F101" s="59">
+      <c r="F101" s="61">
         <v>25</v>
       </c>
-      <c r="G101" s="50">
+      <c r="G101" s="52">
         <v>25</v>
       </c>
-      <c r="H101" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="I101" s="47" t="s">
+      <c r="H101" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="I101" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="J101" s="50" t="s">
+      <c r="J101" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K101" s="50" t="s">
+      <c r="K101" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="47" t="s">
+      <c r="L101" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="N101" s="47" t="s">
+      <c r="N101" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="2:16">
-      <c r="B102" s="48"/>
-      <c r="C102" s="48"/>
-      <c r="D102" s="48"/>
-      <c r="E102" s="51"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="51"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
-      <c r="J102" s="51"/>
-      <c r="K102" s="51"/>
-      <c r="L102" s="48"/>
+      <c r="B102" s="50"/>
+      <c r="C102" s="50"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="50"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="50"/>
       <c r="M102" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N102" s="48"/>
+      <c r="N102" s="50"/>
     </row>
     <row r="103" spans="2:16" ht="24">
-      <c r="B103" s="48"/>
-      <c r="C103" s="48"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="60"/>
-      <c r="G103" s="51"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="51"/>
-      <c r="K103" s="51"/>
-      <c r="L103" s="48"/>
+      <c r="B103" s="50"/>
+      <c r="C103" s="50"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="62"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="50"/>
+      <c r="I103" s="50"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="53"/>
+      <c r="L103" s="50"/>
       <c r="M103" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N103" s="48"/>
+      <c r="N103" s="50"/>
     </row>
     <row r="104" spans="2:16" ht="24">
-      <c r="B104" s="48"/>
-      <c r="C104" s="48"/>
-      <c r="D104" s="48"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="60"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="48"/>
-      <c r="I104" s="48"/>
-      <c r="J104" s="51"/>
-      <c r="K104" s="51"/>
-      <c r="L104" s="48"/>
+      <c r="B104" s="50"/>
+      <c r="C104" s="50"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="62"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="50"/>
+      <c r="I104" s="50"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="53"/>
+      <c r="L104" s="50"/>
       <c r="M104" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="N104" s="48"/>
+      <c r="N104" s="50"/>
     </row>
     <row r="105" spans="2:16" ht="15" thickBot="1">
-      <c r="B105" s="49"/>
-      <c r="C105" s="49"/>
-      <c r="D105" s="49"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="61"/>
-      <c r="G105" s="52"/>
-      <c r="H105" s="49"/>
-      <c r="I105" s="49"/>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52"/>
-      <c r="L105" s="49"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51"/>
+      <c r="D105" s="51"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="63"/>
+      <c r="G105" s="54"/>
+      <c r="H105" s="51"/>
+      <c r="I105" s="51"/>
+      <c r="J105" s="54"/>
+      <c r="K105" s="54"/>
+      <c r="L105" s="51"/>
       <c r="M105" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="49"/>
+      <c r="N105" s="51"/>
     </row>
     <row r="106" spans="2:16">
-      <c r="B106" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="50">
+      <c r="B106" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="52">
         <v>24</v>
       </c>
-      <c r="F106" s="59">
+      <c r="F106" s="61">
         <v>26</v>
       </c>
-      <c r="G106" s="50">
+      <c r="G106" s="52">
         <v>26</v>
       </c>
-      <c r="H106" s="56" t="s">
+      <c r="H106" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="71" t="s">
+      <c r="I106" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="J106" s="50" t="s">
+      <c r="J106" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="50" t="s">
+      <c r="K106" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="L106" s="47" t="s">
+      <c r="L106" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M106" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N106" s="47" t="s">
+      <c r="N106" s="49" t="s">
         <v>203</v>
       </c>
       <c r="P106" t="s">
@@ -6270,38 +6409,38 @@
       </c>
     </row>
     <row r="107" spans="2:16">
-      <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="51"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="51"/>
-      <c r="H107" s="57"/>
-      <c r="I107" s="66"/>
-      <c r="J107" s="51"/>
-      <c r="K107" s="51"/>
-      <c r="L107" s="48"/>
+      <c r="B107" s="50"/>
+      <c r="C107" s="50"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="53"/>
+      <c r="F107" s="62"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="59"/>
+      <c r="I107" s="68"/>
+      <c r="J107" s="53"/>
+      <c r="K107" s="53"/>
+      <c r="L107" s="50"/>
       <c r="M107" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="N107" s="48"/>
+      <c r="N107" s="50"/>
     </row>
     <row r="108" spans="2:16" ht="15" thickBot="1">
-      <c r="B108" s="49"/>
-      <c r="C108" s="49"/>
-      <c r="D108" s="49"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="61"/>
-      <c r="G108" s="52"/>
-      <c r="H108" s="58"/>
-      <c r="I108" s="67"/>
-      <c r="J108" s="52"/>
-      <c r="K108" s="52"/>
-      <c r="L108" s="49"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="51"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="63"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="60"/>
+      <c r="I108" s="69"/>
+      <c r="J108" s="54"/>
+      <c r="K108" s="54"/>
+      <c r="L108" s="51"/>
       <c r="M108" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="N108" s="49"/>
+      <c r="N108" s="51"/>
     </row>
     <row r="109" spans="2:16" ht="24.75" thickBot="1">
       <c r="B109" s="24" t="s">
@@ -6348,43 +6487,43 @@
       </c>
     </row>
     <row r="110" spans="2:16" ht="15" thickTop="1">
-      <c r="B110" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="63">
+      <c r="B110" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="65">
         <v>26</v>
       </c>
-      <c r="F110" s="64">
+      <c r="F110" s="66">
         <v>28</v>
       </c>
-      <c r="G110" s="63">
+      <c r="G110" s="65">
         <v>28</v>
       </c>
-      <c r="H110" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="I110" s="65" t="s">
+      <c r="H110" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="I110" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="J110" s="63" t="s">
+      <c r="J110" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K110" s="63" t="s">
+      <c r="K110" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="L110" s="62" t="s">
+      <c r="L110" s="64" t="s">
         <v>88</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N110" s="62" t="s">
+      <c r="N110" s="64" t="s">
         <v>206</v>
       </c>
       <c r="P110" t="s">
@@ -6392,222 +6531,222 @@
       </c>
     </row>
     <row r="111" spans="2:16" ht="24">
-      <c r="B111" s="48"/>
-      <c r="C111" s="48"/>
-      <c r="D111" s="48"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="60"/>
-      <c r="G111" s="51"/>
-      <c r="H111" s="48"/>
-      <c r="I111" s="66"/>
-      <c r="J111" s="51"/>
-      <c r="K111" s="51"/>
-      <c r="L111" s="48"/>
+      <c r="B111" s="50"/>
+      <c r="C111" s="50"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="62"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="68"/>
+      <c r="J111" s="53"/>
+      <c r="K111" s="53"/>
+      <c r="L111" s="50"/>
       <c r="M111" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="N111" s="48"/>
+      <c r="N111" s="50"/>
     </row>
     <row r="112" spans="2:16" ht="24">
-      <c r="B112" s="48"/>
-      <c r="C112" s="48"/>
-      <c r="D112" s="48"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="60"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="48"/>
-      <c r="I112" s="66"/>
-      <c r="J112" s="51"/>
-      <c r="K112" s="51"/>
-      <c r="L112" s="48"/>
+      <c r="B112" s="50"/>
+      <c r="C112" s="50"/>
+      <c r="D112" s="50"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="62"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="50"/>
+      <c r="I112" s="68"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="53"/>
+      <c r="L112" s="50"/>
       <c r="M112" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="48"/>
+      <c r="N112" s="50"/>
     </row>
     <row r="113" spans="2:14" ht="15" thickBot="1">
-      <c r="B113" s="49"/>
-      <c r="C113" s="49"/>
-      <c r="D113" s="49"/>
-      <c r="E113" s="52"/>
-      <c r="F113" s="61"/>
-      <c r="G113" s="52"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="67"/>
-      <c r="J113" s="52"/>
-      <c r="K113" s="52"/>
-      <c r="L113" s="49"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="63"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="51"/>
+      <c r="I113" s="69"/>
+      <c r="J113" s="54"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="51"/>
       <c r="M113" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="N113" s="49"/>
+      <c r="N113" s="51"/>
     </row>
     <row r="114" spans="2:14" ht="36">
-      <c r="B114" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="50">
+      <c r="B114" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="52">
         <v>18</v>
       </c>
-      <c r="D114" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E114" s="50">
+      <c r="D114" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E114" s="52">
         <v>27</v>
       </c>
-      <c r="F114" s="59">
+      <c r="F114" s="61">
         <v>29</v>
       </c>
-      <c r="G114" s="50">
+      <c r="G114" s="52">
         <v>29</v>
       </c>
-      <c r="H114" s="56" t="s">
+      <c r="H114" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="I114" s="47" t="s">
+      <c r="I114" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="J114" s="50" t="s">
+      <c r="J114" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K114" s="50" t="s">
+      <c r="K114" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="L114" s="47" t="s">
+      <c r="L114" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M114" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="N114" s="47" t="s">
+      <c r="N114" s="49" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="115" spans="2:14" ht="24">
-      <c r="B115" s="48"/>
-      <c r="C115" s="51"/>
-      <c r="D115" s="48"/>
-      <c r="E115" s="51"/>
-      <c r="F115" s="60"/>
-      <c r="G115" s="51"/>
-      <c r="H115" s="57"/>
-      <c r="I115" s="48"/>
-      <c r="J115" s="51"/>
-      <c r="K115" s="51"/>
-      <c r="L115" s="48"/>
+      <c r="B115" s="50"/>
+      <c r="C115" s="53"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="53"/>
+      <c r="F115" s="62"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="59"/>
+      <c r="I115" s="50"/>
+      <c r="J115" s="53"/>
+      <c r="K115" s="53"/>
+      <c r="L115" s="50"/>
       <c r="M115" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N115" s="48"/>
+      <c r="N115" s="50"/>
     </row>
     <row r="116" spans="2:14">
-      <c r="B116" s="48"/>
-      <c r="C116" s="51"/>
-      <c r="D116" s="48"/>
-      <c r="E116" s="51"/>
-      <c r="F116" s="60"/>
-      <c r="G116" s="51"/>
-      <c r="H116" s="57"/>
-      <c r="I116" s="48"/>
-      <c r="J116" s="51"/>
-      <c r="K116" s="51"/>
-      <c r="L116" s="48"/>
+      <c r="B116" s="50"/>
+      <c r="C116" s="53"/>
+      <c r="D116" s="50"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="62"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="59"/>
+      <c r="I116" s="50"/>
+      <c r="J116" s="53"/>
+      <c r="K116" s="53"/>
+      <c r="L116" s="50"/>
       <c r="M116" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N116" s="48"/>
+      <c r="N116" s="50"/>
     </row>
     <row r="117" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B117" s="49"/>
-      <c r="C117" s="52"/>
-      <c r="D117" s="49"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="61"/>
-      <c r="G117" s="52"/>
-      <c r="H117" s="58"/>
-      <c r="I117" s="49"/>
-      <c r="J117" s="52"/>
-      <c r="K117" s="52"/>
-      <c r="L117" s="49"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="54"/>
+      <c r="D117" s="51"/>
+      <c r="E117" s="54"/>
+      <c r="F117" s="63"/>
+      <c r="G117" s="54"/>
+      <c r="H117" s="60"/>
+      <c r="I117" s="51"/>
+      <c r="J117" s="54"/>
+      <c r="K117" s="54"/>
+      <c r="L117" s="51"/>
       <c r="M117" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="N117" s="49"/>
+      <c r="N117" s="51"/>
     </row>
     <row r="118" spans="2:14" ht="36">
-      <c r="B118" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="50">
+      <c r="B118" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="52">
         <v>19</v>
       </c>
-      <c r="D118" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E118" s="50">
+      <c r="D118" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="52">
         <v>28</v>
       </c>
-      <c r="F118" s="59">
+      <c r="F118" s="61">
         <v>30</v>
       </c>
-      <c r="G118" s="50">
+      <c r="G118" s="52">
         <v>30</v>
       </c>
-      <c r="H118" s="56" t="s">
+      <c r="H118" s="58" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="47" t="s">
+      <c r="I118" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="J118" s="50" t="s">
+      <c r="J118" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K118" s="50" t="s">
+      <c r="K118" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="L118" s="47" t="s">
+      <c r="L118" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M118" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="N118" s="47" t="s">
+      <c r="N118" s="49" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:14" ht="36">
-      <c r="B119" s="48"/>
-      <c r="C119" s="51"/>
-      <c r="D119" s="48"/>
-      <c r="E119" s="51"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="51"/>
-      <c r="H119" s="57"/>
-      <c r="I119" s="48"/>
-      <c r="J119" s="51"/>
-      <c r="K119" s="51"/>
-      <c r="L119" s="48"/>
+      <c r="B119" s="50"/>
+      <c r="C119" s="53"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="53"/>
+      <c r="F119" s="62"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="59"/>
+      <c r="I119" s="50"/>
+      <c r="J119" s="53"/>
+      <c r="K119" s="53"/>
+      <c r="L119" s="50"/>
       <c r="M119" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="N119" s="48"/>
+      <c r="N119" s="50"/>
     </row>
     <row r="120" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B120" s="49"/>
-      <c r="C120" s="52"/>
-      <c r="D120" s="49"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="61"/>
-      <c r="G120" s="52"/>
-      <c r="H120" s="58"/>
-      <c r="I120" s="49"/>
-      <c r="J120" s="52"/>
-      <c r="K120" s="52"/>
-      <c r="L120" s="49"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="51"/>
+      <c r="E120" s="54"/>
+      <c r="F120" s="63"/>
+      <c r="G120" s="54"/>
+      <c r="H120" s="60"/>
+      <c r="I120" s="51"/>
+      <c r="J120" s="54"/>
+      <c r="K120" s="54"/>
+      <c r="L120" s="51"/>
       <c r="M120" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="N120" s="49"/>
+      <c r="N120" s="51"/>
     </row>
     <row r="121" spans="2:14" ht="48.75" thickBot="1">
       <c r="B121" s="17">
@@ -6651,96 +6790,96 @@
       </c>
     </row>
     <row r="122" spans="2:14" ht="24">
-      <c r="B122" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G122" s="50">
+      <c r="B122" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="G122" s="52">
         <v>32</v>
       </c>
-      <c r="H122" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="I122" s="47" t="s">
+      <c r="H122" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="I122" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="J122" s="50" t="s">
+      <c r="J122" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="K122" s="50" t="s">
+      <c r="K122" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="L122" s="47" t="s">
+      <c r="L122" s="49" t="s">
         <v>88</v>
       </c>
       <c r="M122" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N122" s="47" t="s">
+      <c r="N122" s="49" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="24">
-      <c r="B123" s="48"/>
-      <c r="C123" s="48"/>
-      <c r="D123" s="48"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="54"/>
-      <c r="G123" s="51"/>
-      <c r="H123" s="48"/>
-      <c r="I123" s="48"/>
-      <c r="J123" s="51"/>
-      <c r="K123" s="51"/>
-      <c r="L123" s="48"/>
+      <c r="B123" s="50"/>
+      <c r="C123" s="50"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="56"/>
+      <c r="G123" s="53"/>
+      <c r="H123" s="50"/>
+      <c r="I123" s="50"/>
+      <c r="J123" s="53"/>
+      <c r="K123" s="53"/>
+      <c r="L123" s="50"/>
       <c r="M123" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N123" s="48"/>
+      <c r="N123" s="50"/>
     </row>
     <row r="124" spans="2:14">
-      <c r="B124" s="48"/>
-      <c r="C124" s="48"/>
-      <c r="D124" s="48"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="54"/>
-      <c r="G124" s="51"/>
-      <c r="H124" s="48"/>
-      <c r="I124" s="48"/>
-      <c r="J124" s="51"/>
-      <c r="K124" s="51"/>
-      <c r="L124" s="48"/>
+      <c r="B124" s="50"/>
+      <c r="C124" s="50"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="56"/>
+      <c r="G124" s="53"/>
+      <c r="H124" s="50"/>
+      <c r="I124" s="50"/>
+      <c r="J124" s="53"/>
+      <c r="K124" s="53"/>
+      <c r="L124" s="50"/>
       <c r="M124" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="48"/>
+      <c r="N124" s="50"/>
     </row>
     <row r="125" spans="2:14" ht="15" thickBot="1">
-      <c r="B125" s="49"/>
-      <c r="C125" s="49"/>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="55"/>
-      <c r="G125" s="52"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="49"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="49"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="51"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="51"/>
+      <c r="F125" s="57"/>
+      <c r="G125" s="54"/>
+      <c r="H125" s="51"/>
+      <c r="I125" s="51"/>
+      <c r="J125" s="54"/>
+      <c r="K125" s="54"/>
+      <c r="L125" s="51"/>
       <c r="M125" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="49"/>
+      <c r="N125" s="51"/>
     </row>
     <row r="126" spans="2:14" ht="15" thickBot="1">
       <c r="B126" s="24" t="s">
@@ -7998,8 +8137,8 @@
     <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.375" customWidth="1"/>
     <col min="6" max="6" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.5" style="89" customWidth="1"/>
-    <col min="8" max="8" width="55.75" style="89" customWidth="1"/>
+    <col min="7" max="7" width="57.5" customWidth="1"/>
+    <col min="8" max="8" width="55.75" customWidth="1"/>
     <col min="9" max="9" width="9.875" style="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8022,10 +8161,10 @@
       <c r="F1" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="G1" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="H1" s="87" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -8051,10 +8190,10 @@
       <c r="F2" t="s">
         <v>405</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="48" t="s">
         <v>397</v>
       </c>
-      <c r="H2" s="89" t="s">
+      <c r="H2" t="s">
         <v>401</v>
       </c>
       <c r="I2" s="46" t="s">
@@ -8080,13 +8219,13 @@
       <c r="F3">
         <v>2101989</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="48" t="s">
         <v>504</v>
       </c>
-      <c r="H3" s="89" t="s">
+      <c r="H3" t="s">
         <v>468</v>
       </c>
-      <c r="I3" s="86" t="s">
+      <c r="I3" s="47" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8109,7 +8248,7 @@
       <c r="F4">
         <v>1717550</v>
       </c>
-      <c r="G4" s="88" t="s">
+      <c r="G4" s="48" t="s">
         <v>506</v>
       </c>
       <c r="I4" s="8" t="s">
@@ -8135,10 +8274,10 @@
       <c r="F5">
         <v>630470</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="48" t="s">
         <v>499</v>
       </c>
-      <c r="H5" s="89" t="s">
+      <c r="H5" t="s">
         <v>470</v>
       </c>
       <c r="I5" s="46" t="s">
@@ -8164,7 +8303,7 @@
       <c r="F6">
         <v>630500</v>
       </c>
-      <c r="G6" s="88" t="s">
+      <c r="G6" s="48" t="s">
         <v>500</v>
       </c>
       <c r="I6" s="46" t="s">
@@ -8190,10 +8329,10 @@
       <c r="F7">
         <v>1830730</v>
       </c>
-      <c r="G7" s="88" t="s">
+      <c r="G7" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="H7" s="89" t="s">
+      <c r="H7" t="s">
         <v>465</v>
       </c>
       <c r="I7" s="46" t="s">
@@ -8219,7 +8358,7 @@
       <c r="F8">
         <v>1830725</v>
       </c>
-      <c r="G8" s="88" t="s">
+      <c r="G8" s="48" t="s">
         <v>508</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -8245,10 +8384,10 @@
       <c r="F9">
         <v>1830729</v>
       </c>
-      <c r="G9" s="88" t="s">
+      <c r="G9" s="48" t="s">
         <v>503</v>
       </c>
-      <c r="H9" s="89" t="s">
+      <c r="H9" t="s">
         <v>466</v>
       </c>
       <c r="I9" s="8" t="s">
@@ -8274,7 +8413,7 @@
       <c r="F10">
         <v>1830725</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="G10" s="48" t="s">
         <v>508</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -8288,7 +8427,7 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="I11" s="86" t="s">
+      <c r="I11" s="47" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8316,7 +8455,7 @@
       <c r="F14">
         <v>1892523</v>
       </c>
-      <c r="G14" s="88" t="s">
+      <c r="G14" s="48" t="s">
         <v>495</v>
       </c>
     </row>
@@ -8339,7 +8478,7 @@
       <c r="F15" t="s">
         <v>484</v>
       </c>
-      <c r="G15" s="88" t="s">
+      <c r="G15" s="48" t="s">
         <v>485</v>
       </c>
     </row>
@@ -8362,7 +8501,7 @@
       <c r="F16" t="s">
         <v>481</v>
       </c>
-      <c r="G16" s="88" t="s">
+      <c r="G16" s="48" t="s">
         <v>482</v>
       </c>
     </row>
@@ -8385,10 +8524,10 @@
       <c r="F17">
         <v>2352005</v>
       </c>
-      <c r="G17" s="88" t="s">
+      <c r="G17" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="H17" s="89" t="s">
+      <c r="H17" t="s">
         <v>497</v>
       </c>
     </row>
@@ -8411,7 +8550,7 @@
       <c r="F19">
         <v>2535699</v>
       </c>
-      <c r="G19" s="88" t="s">
+      <c r="G19" s="48" t="s">
         <v>498</v>
       </c>
       <c r="I19" s="46" t="s">
@@ -8439,7 +8578,7 @@
       <c r="F22">
         <v>9599568</v>
       </c>
-      <c r="G22" s="88" t="s">
+      <c r="G22" s="48" t="s">
         <v>446</v>
       </c>
     </row>
@@ -8447,7 +8586,7 @@
       <c r="A23" t="s">
         <v>421</v>
       </c>
-      <c r="H23" s="89" t="s">
+      <c r="H23" t="s">
         <v>454</v>
       </c>
     </row>
@@ -8467,7 +8606,7 @@
       <c r="F24">
         <v>860414</v>
       </c>
-      <c r="G24" s="88" t="s">
+      <c r="G24" s="48" t="s">
         <v>428</v>
       </c>
     </row>
@@ -8487,7 +8626,7 @@
       <c r="F25">
         <v>4668791</v>
       </c>
-      <c r="G25" s="88" t="s">
+      <c r="G25" s="48" t="s">
         <v>449</v>
       </c>
     </row>
@@ -8517,10 +8656,10 @@
       <c r="F28">
         <v>2501338</v>
       </c>
-      <c r="G28" s="88" t="s">
+      <c r="G28" s="48" t="s">
         <v>431</v>
       </c>
-      <c r="H28" s="89" t="s">
+      <c r="H28" t="s">
         <v>430</v>
       </c>
     </row>
@@ -8540,10 +8679,10 @@
       <c r="F29">
         <v>3026838</v>
       </c>
-      <c r="G29" s="88" t="s">
+      <c r="G29" s="48" t="s">
         <v>433</v>
       </c>
-      <c r="H29" s="89" t="s">
+      <c r="H29" t="s">
         <v>434</v>
       </c>
     </row>
@@ -8563,10 +8702,10 @@
       <c r="F30">
         <v>537056</v>
       </c>
-      <c r="G30" s="88" t="s">
+      <c r="G30" s="48" t="s">
         <v>436</v>
       </c>
-      <c r="H30" s="89" t="s">
+      <c r="H30" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8574,7 +8713,7 @@
       <c r="A31" t="s">
         <v>447</v>
       </c>
-      <c r="H31" s="89" t="s">
+      <c r="H31" t="s">
         <v>452</v>
       </c>
     </row>
@@ -8614,10 +8753,10 @@
       <c r="F37">
         <v>1014356</v>
       </c>
-      <c r="G37" s="88" t="s">
+      <c r="G37" s="48" t="s">
         <v>455</v>
       </c>
-      <c r="H37" s="89" t="s">
+      <c r="H37" t="s">
         <v>456</v>
       </c>
     </row>
@@ -8628,10 +8767,10 @@
       <c r="E38" t="s">
         <v>492</v>
       </c>
-      <c r="G38" s="88" t="s">
+      <c r="G38" s="48" t="s">
         <v>491</v>
       </c>
-      <c r="H38" s="89" t="s">
+      <c r="H38" t="s">
         <v>493</v>
       </c>
     </row>
@@ -8666,30 +8805,290 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A2:B4"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="46.625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="45">
+      <c r="A1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>486</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="42.75">
+      <c r="C2" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="42.75">
       <c r="A4" t="s">
         <v>488</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>489</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>511</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>547</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>516</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>517</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.5">
+      <c r="A13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G13" s="88" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>535</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.5">
+      <c r="A16" t="s">
+        <v>537</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G16" s="88" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>549</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>550</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF9B19B-4226-467E-8D4D-B07375EA571C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D643B34C-1D11-4D52-9922-3C6DE76AD0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34530" yWindow="12600" windowWidth="21600" windowHeight="12645" tabRatio="745" activeTab="6" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" tabRatio="745" activeTab="7" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,11 @@
     <sheet name="TO DO" sheetId="5" r:id="rId5"/>
     <sheet name="Bits to purchase" sheetId="11" r:id="rId6"/>
     <sheet name="Problems" sheetId="4" r:id="rId7"/>
-    <sheet name="Lessons Learned" sheetId="6" r:id="rId8"/>
-    <sheet name="Calculations" sheetId="8" r:id="rId9"/>
-    <sheet name="uC pinout" sheetId="9" r:id="rId10"/>
-    <sheet name="New Parts" sheetId="10" r:id="rId11"/>
+    <sheet name="Ignitor current" sheetId="12" r:id="rId8"/>
+    <sheet name="Lessons Learned" sheetId="6" r:id="rId9"/>
+    <sheet name="Calculations" sheetId="8" r:id="rId10"/>
+    <sheet name="uC pinout" sheetId="9" r:id="rId11"/>
+    <sheet name="New Parts" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="567">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -1547,9 +1548,6 @@
     <t>CAN connector</t>
   </si>
   <si>
-    <t>Could split out each CAN bus and link in external connector. Thereby breaking the link between the processors as flight starts. Use existing 6 way connector</t>
-  </si>
-  <si>
     <t>TTL-232RG-VREG3V3-WE</t>
   </si>
   <si>
@@ -1634,9 +1632,6 @@
     <t xml:space="preserve">Camera connector </t>
   </si>
   <si>
-    <t>Add 2 way header</t>
-  </si>
-  <si>
     <t>Identified by Initials &amp; Date</t>
   </si>
   <si>
@@ -1731,13 +1726,89 @@
   </si>
   <si>
     <t>Only do main PCB - delete ancillaries &amp; keyfob</t>
+  </si>
+  <si>
+    <t>ACB 28 Dec 2025</t>
+  </si>
+  <si>
+    <t>3V3 connection on serial debug</t>
+  </si>
+  <si>
+    <t>PCB 3V3 clash with 3V3 from FTDI lead - disconect</t>
+  </si>
+  <si>
+    <t>Add 2 way header via 1k resistor</t>
+  </si>
+  <si>
+    <t>Could split out each CAN bus and link in external connector. Thereby breaking the link between the processors as flight starts. Use existing 6 way connector. NEED TO CHANGE CAN ADAPTOR ALSO</t>
+  </si>
+  <si>
+    <t>Ancillaries schematic template</t>
+  </si>
+  <si>
+    <t>Bottom left logo wrong</t>
+  </si>
+  <si>
+    <t>Add conformal coating mask layers to assembly drawings</t>
+  </si>
+  <si>
+    <t>Status LED brightness</t>
+  </si>
+  <si>
+    <t>Reduce brightness ??</t>
+  </si>
+  <si>
+    <t>Current profile of ignitors</t>
+  </si>
+  <si>
+    <t>#1</t>
+  </si>
+  <si>
+    <t>#2</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <r>
+      <t>DC resistance measured on DVM (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ignitor (Ω)</t>
+  </si>
+  <si>
+    <t>Firing run</t>
+  </si>
+  <si>
+    <t>lead set (Ω) to be subtracted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1811,6 +1882,28 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2007,7 +2100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2137,85 +2230,82 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2227,36 +2317,40 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2702,6 +2796,298 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB33A44F-01BF-A439-73E2-92FDA2FC28C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7486650" y="381000"/>
+          <a:ext cx="4286250" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>155575</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77B513A6-144A-7E44-CBCD-45CCA49BE478}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7486650" y="3429000"/>
+          <a:ext cx="4270375" cy="2562225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14713774-2D29-B35C-126E-2550837FB1BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7486650" y="6286500"/>
+          <a:ext cx="4286250" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE153ADF-F9E0-98B5-2F6E-1D42B43C1BC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="1714500"/>
+          <a:ext cx="4105275" cy="3371850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>DC PSU set to 3.7V 6A current limit</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Current probe clipped to PSU O/P</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" baseline="0"/>
+            <a:t> lead</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Current probe bandwidth 100kHz</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Oscilloscope set to 2mS/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Yellow trace = applied voltage 2V/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Purple trace = current 1A/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1"/>
+            <a:t>RESULTS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1"/>
+            <a:t>2A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t> max current</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>4mS duration</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>High repeatability</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3909,6 +4295,110 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFAF250-9E30-4C8F-8A0D-6D92E94AA6E7}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7.4</v>
+      </c>
+      <c r="D4">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="8">
+        <f>(B4-B3)/(B5/1000)</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="8">
+        <f>(B4-B3)*B5/1000</f>
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="A10" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="9">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="8">
+        <f>B14*B13/(B12+B13)</f>
+        <v>1.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE3FBF9-418F-478C-B431-B3CE13D40659}">
   <dimension ref="B2:S127"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3919,31 +4409,31 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15" thickBot="1"/>
     <row r="3" spans="2:16" ht="15" thickBot="1">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="86" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="68" t="s">
         <v>232</v>
       </c>
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="L3" s="84" t="s">
+      <c r="L3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="79" t="s">
+      <c r="M3" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="81"/>
+      <c r="N3" s="53"/>
     </row>
     <row r="4" spans="2:16" ht="96.75" customHeight="1" thickBot="1">
       <c r="B4" s="27" t="s">
@@ -3967,10 +4457,10 @@
       <c r="H4" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="87"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="85"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="51"/>
       <c r="M4" s="11" t="s">
         <v>81</v>
       </c>
@@ -3982,43 +4472,43 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15" thickTop="1">
-      <c r="B5" s="65">
+      <c r="B5" s="54">
         <v>2</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="54">
         <v>1</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="54">
         <v>2</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="54">
         <v>2</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="56">
         <v>2</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="54">
         <v>2</v>
       </c>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="62" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="64" t="s">
+      <c r="L5" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="60" t="s">
         <v>85</v>
       </c>
       <c r="P5" t="s">
@@ -4026,60 +4516,60 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="15" thickBot="1">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="60"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="63"/>
       <c r="I6" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="52">
+      <c r="B7" s="64">
         <v>3</v>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="64">
         <v>2</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="64">
         <v>3</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="64">
         <v>3</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="65">
         <v>3</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="64">
         <v>3</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="66" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="52" t="s">
+      <c r="K7" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="49" t="s">
+      <c r="L7" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="72" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
@@ -4087,21 +4577,21 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="60"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="63"/>
       <c r="I8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1">
       <c r="B9" s="17">
@@ -4186,37 +4676,37 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="24">
-      <c r="B11" s="52">
+      <c r="B11" s="64">
         <v>5</v>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="64">
         <v>5</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="64">
         <v>6</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="64">
         <v>6</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="65">
         <v>6</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="64">
         <v>6</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="76" t="s">
+      <c r="I11" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="58" t="s">
+      <c r="K11" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="49" t="s">
+      <c r="L11" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="29" t="s">
@@ -4230,17 +4720,17 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="24">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="59"/>
-      <c r="L12" s="50"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="74"/>
       <c r="M12" s="14" t="s">
         <v>104</v>
       </c>
@@ -4249,17 +4739,17 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="24">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="50"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="74"/>
       <c r="M13" s="14" t="s">
         <v>105</v>
       </c>
@@ -4268,17 +4758,17 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="36">
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="50"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="74"/>
       <c r="M14" s="14" t="s">
         <v>106</v>
       </c>
@@ -4287,71 +4777,71 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="24">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="50"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="74"/>
       <c r="M15" s="29" t="s">
         <v>107</v>
       </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="51"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="61"/>
       <c r="M16" s="21" t="s">
         <v>108</v>
       </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:16" ht="24">
-      <c r="B17" s="52">
+      <c r="B17" s="64">
         <v>6</v>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="64">
         <v>6</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="64">
         <v>7</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="64">
         <v>7</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="65">
         <v>7</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="64">
         <v>7</v>
       </c>
-      <c r="H17" s="58" t="s">
+      <c r="H17" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="52" t="s">
+      <c r="J17" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="52" t="s">
+      <c r="K17" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="49" t="s">
+      <c r="L17" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -4362,17 +4852,17 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="24">
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="50"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="74"/>
       <c r="M18" s="23" t="s">
         <v>116</v>
       </c>
@@ -4381,122 +4871,122 @@
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="50"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="74"/>
       <c r="M19" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="2:16" ht="24">
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="50"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="74"/>
       <c r="M20" s="23" t="s">
         <v>118</v>
       </c>
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="2:16" ht="24">
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="50"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="74"/>
       <c r="M21" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="2:16" ht="24">
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="50"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="74"/>
       <c r="M22" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="51"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="61"/>
       <c r="M23" s="40" t="s">
         <v>121</v>
       </c>
       <c r="N23" s="24"/>
     </row>
     <row r="24" spans="2:16" ht="36">
-      <c r="B24" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="52">
+      <c r="B24" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="64">
         <v>8</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="64">
         <v>8</v>
       </c>
-      <c r="F24" s="61">
+      <c r="F24" s="65">
         <v>8</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="64">
         <v>8</v>
       </c>
-      <c r="H24" s="58" t="s">
+      <c r="H24" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="52" t="s">
+      <c r="J24" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="58" t="s">
+      <c r="K24" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="49" t="s">
+      <c r="L24" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -4507,17 +4997,17 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="24">
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="50"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="74"/>
       <c r="M25" s="29" t="s">
         <v>125</v>
       </c>
@@ -4529,17 +5019,17 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="24">
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="74"/>
       <c r="M26" s="14" t="s">
         <v>126</v>
       </c>
@@ -4548,17 +5038,17 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="51"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="61"/>
       <c r="M27" s="19" t="s">
         <v>127</v>
       </c>
@@ -4567,37 +5057,37 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="24">
-      <c r="B28" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="52">
+      <c r="B28" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="64">
         <v>9</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="64">
         <v>9</v>
       </c>
-      <c r="F28" s="61">
+      <c r="F28" s="65">
         <v>9</v>
       </c>
-      <c r="G28" s="52">
+      <c r="G28" s="64">
         <v>9</v>
       </c>
-      <c r="H28" s="58" t="s">
+      <c r="H28" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="I28" s="49" t="s">
+      <c r="I28" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="52" t="s">
+      <c r="J28" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="52" t="s">
+      <c r="K28" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L28" s="49" t="s">
+      <c r="L28" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M28" s="14" t="s">
@@ -4608,17 +5098,17 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="50"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="74"/>
       <c r="M29" s="14" t="s">
         <v>135</v>
       </c>
@@ -4627,71 +5117,71 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="24">
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="50"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="74"/>
       <c r="M30" s="29" t="s">
         <v>103</v>
       </c>
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="51"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="61"/>
       <c r="M31" s="40" t="s">
         <v>136</v>
       </c>
       <c r="N31" s="24"/>
     </row>
     <row r="32" spans="2:16" ht="24">
-      <c r="B32" s="52">
+      <c r="B32" s="64">
         <v>7</v>
       </c>
-      <c r="C32" s="52">
+      <c r="C32" s="64">
         <v>7</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="64">
         <v>10</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="64">
         <v>10</v>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="65">
         <v>10</v>
       </c>
-      <c r="G32" s="52">
+      <c r="G32" s="64">
         <v>10</v>
       </c>
-      <c r="H32" s="58" t="s">
+      <c r="H32" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="52" t="s">
+      <c r="J32" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="58" t="s">
+      <c r="K32" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="L32" s="49" t="s">
+      <c r="L32" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M32" s="14" t="s">
@@ -4702,17 +5192,17 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="24">
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="50"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="74"/>
       <c r="M33" s="14" t="s">
         <v>104</v>
       </c>
@@ -4721,17 +5211,17 @@
       </c>
     </row>
     <row r="34" spans="2:16" ht="36">
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="50"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="74"/>
       <c r="M34" s="14" t="s">
         <v>140</v>
       </c>
@@ -4743,105 +5233,105 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="24">
-      <c r="B35" s="53"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="50"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="74"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="74"/>
       <c r="M35" s="23" t="s">
         <v>141</v>
       </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="50"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="74"/>
       <c r="M36" s="14" t="s">
         <v>142</v>
       </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" spans="2:16" ht="24">
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="50"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="73"/>
+      <c r="L37" s="74"/>
       <c r="M37" s="37" t="s">
         <v>126</v>
       </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="51"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="61"/>
       <c r="M38" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N38" s="18"/>
     </row>
     <row r="39" spans="2:16" ht="24.75" thickTop="1">
-      <c r="B39" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="65">
+      <c r="B39" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="54">
         <v>8</v>
       </c>
-      <c r="D39" s="65">
+      <c r="D39" s="54">
         <v>11</v>
       </c>
-      <c r="E39" s="65">
+      <c r="E39" s="54">
         <v>11</v>
       </c>
-      <c r="F39" s="66">
+      <c r="F39" s="56">
         <v>11</v>
       </c>
-      <c r="G39" s="65">
+      <c r="G39" s="54">
         <v>11</v>
       </c>
-      <c r="H39" s="74" t="s">
+      <c r="H39" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="64" t="s">
+      <c r="I39" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="J39" s="65" t="s">
+      <c r="J39" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="74" t="s">
+      <c r="K39" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="64" t="s">
+      <c r="L39" s="60" t="s">
         <v>88</v>
       </c>
       <c r="M39" s="14" t="s">
@@ -4852,17 +5342,17 @@
       </c>
     </row>
     <row r="40" spans="2:16" ht="24">
-      <c r="B40" s="50"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="50"/>
+      <c r="B40" s="74"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="74"/>
       <c r="M40" s="14" t="s">
         <v>116</v>
       </c>
@@ -4871,17 +5361,17 @@
       </c>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="50"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="50"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="74"/>
       <c r="M41" s="14" t="s">
         <v>142</v>
       </c>
@@ -4893,60 +5383,60 @@
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1">
-      <c r="B42" s="51"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="54"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="51"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="61"/>
       <c r="M42" s="19" t="s">
         <v>147</v>
       </c>
       <c r="N42" s="18"/>
     </row>
     <row r="43" spans="2:16">
-      <c r="B43" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="52">
+      <c r="B43" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="64">
         <v>9</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="64">
         <v>12</v>
       </c>
-      <c r="E43" s="52">
+      <c r="E43" s="64">
         <v>12</v>
       </c>
-      <c r="F43" s="61">
+      <c r="F43" s="65">
         <v>12</v>
       </c>
-      <c r="G43" s="52">
+      <c r="G43" s="64">
         <v>12</v>
       </c>
-      <c r="H43" s="58" t="s">
+      <c r="H43" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="I43" s="49" t="s">
+      <c r="I43" s="72" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="52" t="s">
+      <c r="J43" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="52" t="s">
+      <c r="K43" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L43" s="49" t="s">
+      <c r="L43" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N43" s="73" t="s">
+      <c r="N43" s="78" t="s">
         <v>154</v>
       </c>
       <c r="P43" t="s">
@@ -4954,143 +5444,143 @@
       </c>
     </row>
     <row r="44" spans="2:16" ht="24">
-      <c r="B44" s="50"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="50"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="74"/>
       <c r="M44" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N44" s="68"/>
+      <c r="N44" s="79"/>
     </row>
     <row r="45" spans="2:16" ht="24">
-      <c r="B45" s="50"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="62"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="50"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="74"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="74"/>
       <c r="M45" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="68"/>
+      <c r="N45" s="79"/>
     </row>
     <row r="46" spans="2:16" ht="24">
-      <c r="B46" s="50"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="53"/>
-      <c r="K46" s="53"/>
-      <c r="L46" s="50"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="74"/>
       <c r="M46" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N46" s="68"/>
+      <c r="N46" s="79"/>
     </row>
     <row r="47" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B47" s="51"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="51"/>
+      <c r="B47" s="61"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="61"/>
       <c r="M47" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N47" s="69"/>
+      <c r="N47" s="80"/>
     </row>
     <row r="48" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B48" s="52">
+      <c r="B48" s="64">
         <v>8</v>
       </c>
-      <c r="C48" s="52">
+      <c r="C48" s="64">
         <v>10</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="64">
         <v>13</v>
       </c>
-      <c r="E48" s="52">
+      <c r="E48" s="64">
         <v>13</v>
       </c>
-      <c r="F48" s="61">
+      <c r="F48" s="65">
         <v>13</v>
       </c>
-      <c r="G48" s="52">
+      <c r="G48" s="64">
         <v>13</v>
       </c>
-      <c r="H48" s="58" t="s">
+      <c r="H48" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="49" t="s">
+      <c r="I48" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="52" t="s">
+      <c r="J48" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="52" t="s">
+      <c r="K48" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L48" s="49" t="s">
+      <c r="L48" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M48" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N48" s="49" t="s">
+      <c r="N48" s="72" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24">
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="50"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N49" s="50"/>
+      <c r="N49" s="74"/>
     </row>
     <row r="50" spans="2:16" ht="24">
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="62"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="50"/>
+      <c r="B50" s="70"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="74"/>
+      <c r="J50" s="70"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="74"/>
       <c r="M50" s="14" t="s">
         <v>159</v>
       </c>
@@ -5102,88 +5592,88 @@
       </c>
     </row>
     <row r="51" spans="2:16" ht="24">
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="62"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="50"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="50"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="74"/>
       <c r="M51" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="2:16" ht="24">
-      <c r="B52" s="53"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
-      <c r="F52" s="62"/>
-      <c r="G52" s="53"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="50"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="50"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="74"/>
       <c r="M52" s="14" t="s">
         <v>115</v>
       </c>
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="63"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="51"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="61"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="61"/>
       <c r="M53" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N53" s="24"/>
     </row>
     <row r="54" spans="2:16" ht="24">
-      <c r="B54" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="52">
+      <c r="B54" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="64">
         <v>14</v>
       </c>
-      <c r="F54" s="61">
+      <c r="F54" s="65">
         <v>14</v>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="64">
         <v>14</v>
       </c>
-      <c r="H54" s="58" t="s">
+      <c r="H54" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="73" t="s">
+      <c r="I54" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="J54" s="52" t="s">
+      <c r="J54" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="52" t="s">
+      <c r="K54" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="49" t="s">
+      <c r="L54" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M54" s="14" t="s">
@@ -5197,17 +5687,17 @@
       </c>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="62"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="50"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="79"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="74"/>
       <c r="M55" s="14" t="s">
         <v>151</v>
       </c>
@@ -5216,88 +5706,88 @@
       </c>
     </row>
     <row r="56" spans="2:16">
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="62"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="68"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="50"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="79"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="74"/>
       <c r="M56" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" spans="2:16" ht="24">
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="62"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="68"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="53"/>
-      <c r="L57" s="50"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="79"/>
+      <c r="J57" s="70"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="74"/>
       <c r="M57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1">
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="63"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="54"/>
-      <c r="L58" s="51"/>
+      <c r="B58" s="61"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="55"/>
+      <c r="K58" s="55"/>
+      <c r="L58" s="61"/>
       <c r="M58" s="19" t="s">
         <v>162</v>
       </c>
       <c r="N58" s="18"/>
     </row>
     <row r="59" spans="2:16" ht="24">
-      <c r="B59" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="52">
+      <c r="B59" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="64">
         <v>11</v>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="64">
         <v>14</v>
       </c>
-      <c r="E59" s="52">
+      <c r="E59" s="64">
         <v>15</v>
       </c>
-      <c r="F59" s="61">
+      <c r="F59" s="65">
         <v>15</v>
       </c>
-      <c r="G59" s="52">
+      <c r="G59" s="64">
         <v>15</v>
       </c>
-      <c r="H59" s="58" t="s">
+      <c r="H59" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="73" t="s">
+      <c r="I59" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="52" t="s">
+      <c r="J59" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="52" t="s">
+      <c r="K59" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L59" s="49" t="s">
+      <c r="L59" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M59" s="14" t="s">
@@ -5311,17 +5801,17 @@
       </c>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" s="50"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="53"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="68"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="50"/>
+      <c r="B60" s="74"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="71"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="79"/>
+      <c r="J60" s="70"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="74"/>
       <c r="M60" s="14" t="s">
         <v>157</v>
       </c>
@@ -5330,51 +5820,51 @@
       </c>
     </row>
     <row r="61" spans="2:16" ht="24">
-      <c r="B61" s="50"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="53"/>
-      <c r="E61" s="53"/>
-      <c r="F61" s="62"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="53"/>
-      <c r="L61" s="50"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="79"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="74"/>
       <c r="M61" s="14" t="s">
         <v>104</v>
       </c>
       <c r="N61" s="22"/>
     </row>
     <row r="62" spans="2:16" ht="24">
-      <c r="B62" s="50"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="62"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="68"/>
-      <c r="J62" s="53"/>
-      <c r="K62" s="53"/>
-      <c r="L62" s="50"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="73"/>
+      <c r="I62" s="79"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="74"/>
       <c r="M62" s="13" t="s">
         <v>167</v>
       </c>
       <c r="N62" s="22"/>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1">
-      <c r="B63" s="51"/>
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="54"/>
-      <c r="H63" s="60"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="L63" s="51"/>
+      <c r="B63" s="61"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="80"/>
+      <c r="J63" s="55"/>
+      <c r="K63" s="55"/>
+      <c r="L63" s="61"/>
       <c r="M63" s="19" t="s">
         <v>168</v>
       </c>
@@ -5504,43 +5994,43 @@
       </c>
     </row>
     <row r="67" spans="2:16" ht="36">
-      <c r="B67" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="52">
+      <c r="B67" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="64">
         <v>18</v>
       </c>
-      <c r="F67" s="61">
+      <c r="F67" s="65">
         <v>18</v>
       </c>
-      <c r="G67" s="52">
+      <c r="G67" s="64">
         <v>18</v>
       </c>
-      <c r="H67" s="58" t="s">
+      <c r="H67" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="I67" s="73" t="s">
+      <c r="I67" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="52" t="s">
+      <c r="J67" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="52" t="s">
+      <c r="K67" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="49" t="s">
+      <c r="L67" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M67" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="N67" s="49" t="s">
+      <c r="N67" s="72" t="s">
         <v>88</v>
       </c>
       <c r="P67" t="s">
@@ -5548,860 +6038,860 @@
       </c>
     </row>
     <row r="68" spans="2:16" ht="24">
-      <c r="B68" s="50"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="50"/>
-      <c r="E68" s="53"/>
-      <c r="F68" s="62"/>
-      <c r="G68" s="53"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="68"/>
-      <c r="J68" s="53"/>
-      <c r="K68" s="53"/>
-      <c r="L68" s="50"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="70"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="79"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="74"/>
       <c r="M68" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N68" s="50"/>
+      <c r="N68" s="74"/>
     </row>
     <row r="69" spans="2:16" ht="24">
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="50"/>
-      <c r="E69" s="53"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="53"/>
-      <c r="L69" s="50"/>
+      <c r="B69" s="74"/>
+      <c r="C69" s="74"/>
+      <c r="D69" s="74"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="73"/>
+      <c r="I69" s="79"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="74"/>
       <c r="M69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="50"/>
+      <c r="N69" s="74"/>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1">
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="63"/>
-      <c r="G70" s="54"/>
-      <c r="H70" s="60"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
-      <c r="L70" s="51"/>
+      <c r="B70" s="61"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="61"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="55"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="55"/>
+      <c r="K70" s="55"/>
+      <c r="L70" s="61"/>
       <c r="M70" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N70" s="51"/>
+      <c r="N70" s="61"/>
     </row>
     <row r="71" spans="2:16" ht="24">
-      <c r="B71" s="52">
+      <c r="B71" s="64">
         <v>11</v>
       </c>
-      <c r="C71" s="52">
+      <c r="C71" s="64">
         <v>14</v>
       </c>
-      <c r="D71" s="52">
+      <c r="D71" s="64">
         <v>17</v>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="64">
         <v>19</v>
       </c>
-      <c r="F71" s="61">
+      <c r="F71" s="65">
         <v>19</v>
       </c>
-      <c r="G71" s="52">
+      <c r="G71" s="64">
         <v>19</v>
       </c>
-      <c r="H71" s="58" t="s">
+      <c r="H71" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="49" t="s">
+      <c r="I71" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="J71" s="52" t="s">
+      <c r="J71" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K71" s="52" t="s">
+      <c r="K71" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="L71" s="49" t="s">
+      <c r="L71" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M71" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="N71" s="49" t="s">
+      <c r="N71" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="24">
-      <c r="B72" s="53"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="53"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="62"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-      <c r="L72" s="50"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="70"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="73"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="74"/>
       <c r="M72" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N72" s="50"/>
+      <c r="N72" s="74"/>
     </row>
     <row r="73" spans="2:16" ht="24">
-      <c r="B73" s="53"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="62"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-      <c r="L73" s="50"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="70"/>
+      <c r="D73" s="70"/>
+      <c r="E73" s="70"/>
+      <c r="F73" s="71"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="73"/>
+      <c r="I73" s="74"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="74"/>
       <c r="M73" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="N73" s="50"/>
+      <c r="N73" s="74"/>
     </row>
     <row r="74" spans="2:16" ht="48.75" thickBot="1">
-      <c r="B74" s="54"/>
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="63"/>
-      <c r="G74" s="54"/>
-      <c r="H74" s="60"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="54"/>
-      <c r="K74" s="54"/>
-      <c r="L74" s="51"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="61"/>
+      <c r="J74" s="55"/>
+      <c r="K74" s="55"/>
+      <c r="L74" s="61"/>
       <c r="M74" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N74" s="51"/>
+      <c r="N74" s="61"/>
     </row>
     <row r="75" spans="2:16" ht="36.75" thickTop="1">
-      <c r="B75" s="65">
+      <c r="B75" s="54">
         <v>12</v>
       </c>
-      <c r="C75" s="65">
+      <c r="C75" s="54">
         <v>15</v>
       </c>
-      <c r="D75" s="65">
+      <c r="D75" s="54">
         <v>18</v>
       </c>
-      <c r="E75" s="65">
+      <c r="E75" s="54">
         <v>20</v>
       </c>
-      <c r="F75" s="66">
+      <c r="F75" s="56">
         <v>20</v>
       </c>
-      <c r="G75" s="65">
+      <c r="G75" s="54">
         <v>20</v>
       </c>
-      <c r="H75" s="74" t="s">
+      <c r="H75" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="64" t="s">
+      <c r="I75" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="J75" s="65" t="s">
+      <c r="J75" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="65" t="s">
+      <c r="K75" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L75" s="75">
+      <c r="L75" s="81">
         <v>-7</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="64" t="s">
+      <c r="N75" s="60" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="24">
-      <c r="B76" s="53"/>
-      <c r="C76" s="53"/>
-      <c r="D76" s="53"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="62"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="59"/>
-      <c r="I76" s="50"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
-      <c r="L76" s="71"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
+      <c r="F76" s="71"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="74"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="82"/>
       <c r="M76" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="50"/>
+      <c r="N76" s="74"/>
     </row>
     <row r="77" spans="2:16" ht="24">
-      <c r="B77" s="53"/>
-      <c r="C77" s="53"/>
-      <c r="D77" s="53"/>
-      <c r="E77" s="53"/>
-      <c r="F77" s="62"/>
-      <c r="G77" s="53"/>
-      <c r="H77" s="59"/>
-      <c r="I77" s="50"/>
-      <c r="J77" s="53"/>
-      <c r="K77" s="53"/>
-      <c r="L77" s="71"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="71"/>
+      <c r="G77" s="70"/>
+      <c r="H77" s="73"/>
+      <c r="I77" s="74"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="82"/>
       <c r="M77" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="N77" s="50"/>
+      <c r="N77" s="74"/>
     </row>
     <row r="78" spans="2:16">
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="62"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="59"/>
-      <c r="I78" s="50"/>
-      <c r="J78" s="53"/>
-      <c r="K78" s="53"/>
-      <c r="L78" s="71"/>
+      <c r="B78" s="70"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="71"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="73"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="70"/>
+      <c r="K78" s="70"/>
+      <c r="L78" s="82"/>
       <c r="M78" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N78" s="50"/>
+      <c r="N78" s="74"/>
     </row>
     <row r="79" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B79" s="54"/>
-      <c r="C79" s="54"/>
-      <c r="D79" s="54"/>
-      <c r="E79" s="54"/>
-      <c r="F79" s="63"/>
-      <c r="G79" s="54"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="54"/>
-      <c r="K79" s="54"/>
-      <c r="L79" s="72"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="55"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="61"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+      <c r="L79" s="83"/>
       <c r="M79" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="51"/>
+      <c r="N79" s="61"/>
     </row>
     <row r="80" spans="2:16">
-      <c r="B80" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D80" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="F80" s="61">
+      <c r="B80" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="65">
         <v>21</v>
       </c>
-      <c r="G80" s="52">
+      <c r="G80" s="64">
         <v>21</v>
       </c>
-      <c r="H80" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80" s="49" t="s">
+      <c r="H80" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="72" t="s">
         <v>189</v>
       </c>
-      <c r="J80" s="52" t="s">
+      <c r="J80" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K80" s="52" t="s">
+      <c r="K80" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L80" s="49" t="s">
+      <c r="L80" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M80" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N80" s="49" t="s">
+      <c r="N80" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:19" ht="48">
-      <c r="B81" s="50"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="62"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
-      <c r="L81" s="50"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="70"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="70"/>
+      <c r="K81" s="70"/>
+      <c r="L81" s="74"/>
       <c r="M81" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="N81" s="50"/>
+      <c r="N81" s="74"/>
     </row>
     <row r="82" spans="2:19" ht="24">
-      <c r="B82" s="50"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="62"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="50"/>
-      <c r="J82" s="53"/>
-      <c r="K82" s="53"/>
-      <c r="L82" s="50"/>
+      <c r="B82" s="74"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="74"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="74"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="74"/>
       <c r="M82" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="N82" s="50"/>
+      <c r="N82" s="74"/>
     </row>
     <row r="83" spans="2:19" ht="48.75" thickBot="1">
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="54"/>
-      <c r="H83" s="51"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="54"/>
-      <c r="K83" s="54"/>
-      <c r="L83" s="51"/>
+      <c r="B83" s="61"/>
+      <c r="C83" s="61"/>
+      <c r="D83" s="61"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="55"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61"/>
+      <c r="J83" s="55"/>
+      <c r="K83" s="55"/>
+      <c r="L83" s="61"/>
       <c r="M83" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N83" s="51"/>
+      <c r="N83" s="61"/>
     </row>
     <row r="84" spans="2:19">
-      <c r="B84" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="61">
+      <c r="B84" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="65">
         <v>22</v>
       </c>
-      <c r="G84" s="52">
+      <c r="G84" s="64">
         <v>22</v>
       </c>
-      <c r="H84" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84" s="49" t="s">
+      <c r="H84" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" s="72" t="s">
         <v>191</v>
       </c>
-      <c r="J84" s="52" t="s">
+      <c r="J84" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="52" t="s">
+      <c r="K84" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="49" t="s">
+      <c r="L84" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N84" s="49" t="s">
+      <c r="N84" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:19" ht="24">
-      <c r="B85" s="50"/>
-      <c r="C85" s="50"/>
-      <c r="D85" s="50"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="50"/>
-      <c r="I85" s="50"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="53"/>
-      <c r="L85" s="50"/>
+      <c r="B85" s="74"/>
+      <c r="C85" s="74"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="74"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="70"/>
+      <c r="H85" s="74"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="74"/>
       <c r="M85" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N85" s="50"/>
+      <c r="N85" s="74"/>
     </row>
     <row r="86" spans="2:19" ht="24">
-      <c r="B86" s="50"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="50"/>
-      <c r="I86" s="50"/>
-      <c r="J86" s="53"/>
-      <c r="K86" s="53"/>
-      <c r="L86" s="50"/>
+      <c r="B86" s="74"/>
+      <c r="C86" s="74"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="74"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="70"/>
+      <c r="H86" s="74"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="74"/>
       <c r="M86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N86" s="50"/>
+      <c r="N86" s="74"/>
       <c r="S86" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="54"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="54"/>
-      <c r="K87" s="54"/>
-      <c r="L87" s="51"/>
+      <c r="B87" s="61"/>
+      <c r="C87" s="61"/>
+      <c r="D87" s="61"/>
+      <c r="E87" s="61"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="55"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61"/>
+      <c r="J87" s="55"/>
+      <c r="K87" s="55"/>
+      <c r="L87" s="61"/>
       <c r="M87" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="N87" s="51"/>
+      <c r="N87" s="61"/>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="52">
+      <c r="B88" s="64">
         <v>13</v>
       </c>
-      <c r="C88" s="52">
+      <c r="C88" s="64">
         <v>16</v>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="64">
         <v>19</v>
       </c>
-      <c r="E88" s="52">
+      <c r="E88" s="64">
         <v>21</v>
       </c>
-      <c r="F88" s="61">
+      <c r="F88" s="65">
         <v>23</v>
       </c>
-      <c r="G88" s="52">
+      <c r="G88" s="64">
         <v>23</v>
       </c>
-      <c r="H88" s="58" t="s">
+      <c r="H88" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="I88" s="49" t="s">
+      <c r="I88" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="J88" s="52" t="s">
+      <c r="J88" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K88" s="52" t="s">
+      <c r="K88" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="L88" s="49" t="s">
+      <c r="L88" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M88" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="N88" s="49" t="s">
+      <c r="N88" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="2:19" ht="24">
-      <c r="B89" s="53"/>
-      <c r="C89" s="53"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="62"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="50"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="53"/>
-      <c r="L89" s="50"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="70"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="70"/>
+      <c r="H89" s="73"/>
+      <c r="I89" s="74"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="74"/>
       <c r="M89" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N89" s="50"/>
+      <c r="N89" s="74"/>
     </row>
     <row r="90" spans="2:19">
-      <c r="B90" s="53"/>
-      <c r="C90" s="53"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="62"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="50"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="50"/>
+      <c r="B90" s="70"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="73"/>
+      <c r="I90" s="74"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="74"/>
       <c r="M90" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="N90" s="50"/>
+      <c r="N90" s="74"/>
     </row>
     <row r="91" spans="2:19">
-      <c r="B91" s="53"/>
-      <c r="C91" s="53"/>
-      <c r="D91" s="53"/>
-      <c r="E91" s="53"/>
-      <c r="F91" s="62"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="50"/>
-      <c r="J91" s="53"/>
-      <c r="K91" s="53"/>
-      <c r="L91" s="50"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="73"/>
+      <c r="I91" s="74"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="74"/>
       <c r="M91" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N91" s="50"/>
+      <c r="N91" s="74"/>
     </row>
     <row r="92" spans="2:19" ht="24">
-      <c r="B92" s="53"/>
-      <c r="C92" s="53"/>
-      <c r="D92" s="53"/>
-      <c r="E92" s="53"/>
-      <c r="F92" s="62"/>
-      <c r="G92" s="53"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="50"/>
-      <c r="J92" s="53"/>
-      <c r="K92" s="53"/>
-      <c r="L92" s="50"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="71"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="73"/>
+      <c r="I92" s="74"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="74"/>
       <c r="M92" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="N92" s="50"/>
+      <c r="N92" s="74"/>
     </row>
     <row r="93" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B93" s="54"/>
-      <c r="C93" s="54"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="54"/>
-      <c r="F93" s="63"/>
-      <c r="G93" s="54"/>
-      <c r="H93" s="60"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="54"/>
-      <c r="K93" s="54"/>
-      <c r="L93" s="51"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="61"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
+      <c r="L93" s="61"/>
       <c r="M93" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N93" s="51"/>
+      <c r="N93" s="61"/>
     </row>
     <row r="94" spans="2:19">
-      <c r="B94" s="52">
+      <c r="B94" s="64">
         <v>14</v>
       </c>
-      <c r="C94" s="52">
+      <c r="C94" s="64">
         <v>17</v>
       </c>
-      <c r="D94" s="52">
+      <c r="D94" s="64">
         <v>20</v>
       </c>
-      <c r="E94" s="52">
+      <c r="E94" s="64">
         <v>22</v>
       </c>
-      <c r="F94" s="61">
+      <c r="F94" s="65">
         <v>24</v>
       </c>
-      <c r="G94" s="52">
+      <c r="G94" s="64">
         <v>24</v>
       </c>
-      <c r="H94" s="58" t="s">
+      <c r="H94" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="I94" s="49" t="s">
+      <c r="I94" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="J94" s="52" t="s">
+      <c r="J94" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K94" s="52" t="s">
+      <c r="K94" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L94" s="70">
+      <c r="L94" s="84">
         <v>-7</v>
       </c>
       <c r="M94" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N94" s="49" t="s">
+      <c r="N94" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:19" ht="24">
-      <c r="B95" s="53"/>
-      <c r="C95" s="53"/>
-      <c r="D95" s="53"/>
-      <c r="E95" s="53"/>
-      <c r="F95" s="62"/>
-      <c r="G95" s="53"/>
-      <c r="H95" s="59"/>
-      <c r="I95" s="50"/>
-      <c r="J95" s="53"/>
-      <c r="K95" s="53"/>
-      <c r="L95" s="71"/>
+      <c r="B95" s="70"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
+      <c r="F95" s="71"/>
+      <c r="G95" s="70"/>
+      <c r="H95" s="73"/>
+      <c r="I95" s="74"/>
+      <c r="J95" s="70"/>
+      <c r="K95" s="70"/>
+      <c r="L95" s="82"/>
       <c r="M95" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="N95" s="50"/>
+      <c r="N95" s="74"/>
     </row>
     <row r="96" spans="2:19" ht="24">
-      <c r="B96" s="53"/>
-      <c r="C96" s="53"/>
-      <c r="D96" s="53"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="62"/>
-      <c r="G96" s="53"/>
-      <c r="H96" s="59"/>
-      <c r="I96" s="50"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="71"/>
+      <c r="B96" s="70"/>
+      <c r="C96" s="70"/>
+      <c r="D96" s="70"/>
+      <c r="E96" s="70"/>
+      <c r="F96" s="71"/>
+      <c r="G96" s="70"/>
+      <c r="H96" s="73"/>
+      <c r="I96" s="74"/>
+      <c r="J96" s="70"/>
+      <c r="K96" s="70"/>
+      <c r="L96" s="82"/>
       <c r="M96" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N96" s="50"/>
+      <c r="N96" s="74"/>
     </row>
     <row r="97" spans="2:16" ht="24">
-      <c r="B97" s="53"/>
-      <c r="C97" s="53"/>
-      <c r="D97" s="53"/>
-      <c r="E97" s="53"/>
-      <c r="F97" s="62"/>
-      <c r="G97" s="53"/>
-      <c r="H97" s="59"/>
-      <c r="I97" s="50"/>
-      <c r="J97" s="53"/>
-      <c r="K97" s="53"/>
-      <c r="L97" s="71"/>
+      <c r="B97" s="70"/>
+      <c r="C97" s="70"/>
+      <c r="D97" s="70"/>
+      <c r="E97" s="70"/>
+      <c r="F97" s="71"/>
+      <c r="G97" s="70"/>
+      <c r="H97" s="73"/>
+      <c r="I97" s="74"/>
+      <c r="J97" s="70"/>
+      <c r="K97" s="70"/>
+      <c r="L97" s="82"/>
       <c r="M97" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="N97" s="50"/>
+      <c r="N97" s="74"/>
     </row>
     <row r="98" spans="2:16">
-      <c r="B98" s="53"/>
-      <c r="C98" s="53"/>
-      <c r="D98" s="53"/>
-      <c r="E98" s="53"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="53"/>
-      <c r="H98" s="59"/>
-      <c r="I98" s="50"/>
-      <c r="J98" s="53"/>
-      <c r="K98" s="53"/>
-      <c r="L98" s="71"/>
+      <c r="B98" s="70"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
+      <c r="F98" s="71"/>
+      <c r="G98" s="70"/>
+      <c r="H98" s="73"/>
+      <c r="I98" s="74"/>
+      <c r="J98" s="70"/>
+      <c r="K98" s="70"/>
+      <c r="L98" s="82"/>
       <c r="M98" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N98" s="50"/>
+      <c r="N98" s="74"/>
     </row>
     <row r="99" spans="2:16" ht="24">
-      <c r="B99" s="53"/>
-      <c r="C99" s="53"/>
-      <c r="D99" s="53"/>
-      <c r="E99" s="53"/>
-      <c r="F99" s="62"/>
-      <c r="G99" s="53"/>
-      <c r="H99" s="59"/>
-      <c r="I99" s="50"/>
-      <c r="J99" s="53"/>
-      <c r="K99" s="53"/>
-      <c r="L99" s="71"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="74"/>
+      <c r="J99" s="70"/>
+      <c r="K99" s="70"/>
+      <c r="L99" s="82"/>
       <c r="M99" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="N99" s="50"/>
+      <c r="N99" s="74"/>
     </row>
     <row r="100" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B100" s="54"/>
-      <c r="C100" s="54"/>
-      <c r="D100" s="54"/>
-      <c r="E100" s="54"/>
-      <c r="F100" s="63"/>
-      <c r="G100" s="54"/>
-      <c r="H100" s="60"/>
-      <c r="I100" s="51"/>
-      <c r="J100" s="54"/>
-      <c r="K100" s="54"/>
-      <c r="L100" s="72"/>
+      <c r="B100" s="55"/>
+      <c r="C100" s="55"/>
+      <c r="D100" s="55"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="63"/>
+      <c r="I100" s="61"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="55"/>
+      <c r="L100" s="83"/>
       <c r="M100" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N100" s="51"/>
+      <c r="N100" s="61"/>
     </row>
     <row r="101" spans="2:16">
-      <c r="B101" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E101" s="52">
+      <c r="B101" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="64">
         <v>23</v>
       </c>
-      <c r="F101" s="61">
+      <c r="F101" s="65">
         <v>25</v>
       </c>
-      <c r="G101" s="52">
+      <c r="G101" s="64">
         <v>25</v>
       </c>
-      <c r="H101" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I101" s="49" t="s">
+      <c r="H101" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="I101" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="J101" s="52" t="s">
+      <c r="J101" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K101" s="52" t="s">
+      <c r="K101" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="49" t="s">
+      <c r="L101" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="N101" s="49" t="s">
+      <c r="N101" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="2:16">
-      <c r="B102" s="50"/>
-      <c r="C102" s="50"/>
-      <c r="D102" s="50"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="50"/>
-      <c r="I102" s="50"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="50"/>
+      <c r="B102" s="74"/>
+      <c r="C102" s="74"/>
+      <c r="D102" s="74"/>
+      <c r="E102" s="70"/>
+      <c r="F102" s="71"/>
+      <c r="G102" s="70"/>
+      <c r="H102" s="74"/>
+      <c r="I102" s="74"/>
+      <c r="J102" s="70"/>
+      <c r="K102" s="70"/>
+      <c r="L102" s="74"/>
       <c r="M102" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N102" s="50"/>
+      <c r="N102" s="74"/>
     </row>
     <row r="103" spans="2:16" ht="24">
-      <c r="B103" s="50"/>
-      <c r="C103" s="50"/>
-      <c r="D103" s="50"/>
-      <c r="E103" s="53"/>
-      <c r="F103" s="62"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="50"/>
-      <c r="I103" s="50"/>
-      <c r="J103" s="53"/>
-      <c r="K103" s="53"/>
-      <c r="L103" s="50"/>
+      <c r="B103" s="74"/>
+      <c r="C103" s="74"/>
+      <c r="D103" s="74"/>
+      <c r="E103" s="70"/>
+      <c r="F103" s="71"/>
+      <c r="G103" s="70"/>
+      <c r="H103" s="74"/>
+      <c r="I103" s="74"/>
+      <c r="J103" s="70"/>
+      <c r="K103" s="70"/>
+      <c r="L103" s="74"/>
       <c r="M103" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N103" s="50"/>
+      <c r="N103" s="74"/>
     </row>
     <row r="104" spans="2:16" ht="24">
-      <c r="B104" s="50"/>
-      <c r="C104" s="50"/>
-      <c r="D104" s="50"/>
-      <c r="E104" s="53"/>
-      <c r="F104" s="62"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="50"/>
-      <c r="I104" s="50"/>
-      <c r="J104" s="53"/>
-      <c r="K104" s="53"/>
-      <c r="L104" s="50"/>
+      <c r="B104" s="74"/>
+      <c r="C104" s="74"/>
+      <c r="D104" s="74"/>
+      <c r="E104" s="70"/>
+      <c r="F104" s="71"/>
+      <c r="G104" s="70"/>
+      <c r="H104" s="74"/>
+      <c r="I104" s="74"/>
+      <c r="J104" s="70"/>
+      <c r="K104" s="70"/>
+      <c r="L104" s="74"/>
       <c r="M104" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="N104" s="50"/>
+      <c r="N104" s="74"/>
     </row>
     <row r="105" spans="2:16" ht="15" thickBot="1">
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
-      <c r="D105" s="51"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="63"/>
-      <c r="G105" s="54"/>
-      <c r="H105" s="51"/>
-      <c r="I105" s="51"/>
-      <c r="J105" s="54"/>
-      <c r="K105" s="54"/>
-      <c r="L105" s="51"/>
+      <c r="B105" s="61"/>
+      <c r="C105" s="61"/>
+      <c r="D105" s="61"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="57"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="61"/>
+      <c r="I105" s="61"/>
+      <c r="J105" s="55"/>
+      <c r="K105" s="55"/>
+      <c r="L105" s="61"/>
       <c r="M105" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="51"/>
+      <c r="N105" s="61"/>
     </row>
     <row r="106" spans="2:16">
-      <c r="B106" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="52">
+      <c r="B106" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="64">
         <v>24</v>
       </c>
-      <c r="F106" s="61">
+      <c r="F106" s="65">
         <v>26</v>
       </c>
-      <c r="G106" s="52">
+      <c r="G106" s="64">
         <v>26</v>
       </c>
-      <c r="H106" s="58" t="s">
+      <c r="H106" s="66" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="73" t="s">
+      <c r="I106" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="J106" s="52" t="s">
+      <c r="J106" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="52" t="s">
+      <c r="K106" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="L106" s="49" t="s">
+      <c r="L106" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M106" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N106" s="49" t="s">
+      <c r="N106" s="72" t="s">
         <v>203</v>
       </c>
       <c r="P106" t="s">
@@ -6409,38 +6899,38 @@
       </c>
     </row>
     <row r="107" spans="2:16">
-      <c r="B107" s="50"/>
-      <c r="C107" s="50"/>
-      <c r="D107" s="50"/>
-      <c r="E107" s="53"/>
-      <c r="F107" s="62"/>
-      <c r="G107" s="53"/>
-      <c r="H107" s="59"/>
-      <c r="I107" s="68"/>
-      <c r="J107" s="53"/>
-      <c r="K107" s="53"/>
-      <c r="L107" s="50"/>
+      <c r="B107" s="74"/>
+      <c r="C107" s="74"/>
+      <c r="D107" s="74"/>
+      <c r="E107" s="70"/>
+      <c r="F107" s="71"/>
+      <c r="G107" s="70"/>
+      <c r="H107" s="73"/>
+      <c r="I107" s="79"/>
+      <c r="J107" s="70"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="74"/>
       <c r="M107" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="N107" s="50"/>
+      <c r="N107" s="74"/>
     </row>
     <row r="108" spans="2:16" ht="15" thickBot="1">
-      <c r="B108" s="51"/>
-      <c r="C108" s="51"/>
-      <c r="D108" s="51"/>
-      <c r="E108" s="54"/>
-      <c r="F108" s="63"/>
-      <c r="G108" s="54"/>
-      <c r="H108" s="60"/>
-      <c r="I108" s="69"/>
-      <c r="J108" s="54"/>
-      <c r="K108" s="54"/>
-      <c r="L108" s="51"/>
+      <c r="B108" s="61"/>
+      <c r="C108" s="61"/>
+      <c r="D108" s="61"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="57"/>
+      <c r="G108" s="55"/>
+      <c r="H108" s="63"/>
+      <c r="I108" s="80"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="55"/>
+      <c r="L108" s="61"/>
       <c r="M108" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="N108" s="51"/>
+      <c r="N108" s="61"/>
     </row>
     <row r="109" spans="2:16" ht="24.75" thickBot="1">
       <c r="B109" s="24" t="s">
@@ -6487,43 +6977,43 @@
       </c>
     </row>
     <row r="110" spans="2:16" ht="15" thickTop="1">
-      <c r="B110" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="65">
+      <c r="B110" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="54">
         <v>26</v>
       </c>
-      <c r="F110" s="66">
+      <c r="F110" s="56">
         <v>28</v>
       </c>
-      <c r="G110" s="65">
+      <c r="G110" s="54">
         <v>28</v>
       </c>
-      <c r="H110" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="I110" s="67" t="s">
+      <c r="H110" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="I110" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="J110" s="65" t="s">
+      <c r="J110" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K110" s="65" t="s">
+      <c r="K110" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L110" s="64" t="s">
+      <c r="L110" s="60" t="s">
         <v>88</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N110" s="64" t="s">
+      <c r="N110" s="60" t="s">
         <v>206</v>
       </c>
       <c r="P110" t="s">
@@ -6531,222 +7021,222 @@
       </c>
     </row>
     <row r="111" spans="2:16" ht="24">
-      <c r="B111" s="50"/>
-      <c r="C111" s="50"/>
-      <c r="D111" s="50"/>
-      <c r="E111" s="53"/>
-      <c r="F111" s="62"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="50"/>
-      <c r="I111" s="68"/>
-      <c r="J111" s="53"/>
-      <c r="K111" s="53"/>
-      <c r="L111" s="50"/>
+      <c r="B111" s="74"/>
+      <c r="C111" s="74"/>
+      <c r="D111" s="74"/>
+      <c r="E111" s="70"/>
+      <c r="F111" s="71"/>
+      <c r="G111" s="70"/>
+      <c r="H111" s="74"/>
+      <c r="I111" s="79"/>
+      <c r="J111" s="70"/>
+      <c r="K111" s="70"/>
+      <c r="L111" s="74"/>
       <c r="M111" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="N111" s="50"/>
+      <c r="N111" s="74"/>
     </row>
     <row r="112" spans="2:16" ht="24">
-      <c r="B112" s="50"/>
-      <c r="C112" s="50"/>
-      <c r="D112" s="50"/>
-      <c r="E112" s="53"/>
-      <c r="F112" s="62"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="50"/>
-      <c r="I112" s="68"/>
-      <c r="J112" s="53"/>
-      <c r="K112" s="53"/>
-      <c r="L112" s="50"/>
+      <c r="B112" s="74"/>
+      <c r="C112" s="74"/>
+      <c r="D112" s="74"/>
+      <c r="E112" s="70"/>
+      <c r="F112" s="71"/>
+      <c r="G112" s="70"/>
+      <c r="H112" s="74"/>
+      <c r="I112" s="79"/>
+      <c r="J112" s="70"/>
+      <c r="K112" s="70"/>
+      <c r="L112" s="74"/>
       <c r="M112" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="50"/>
+      <c r="N112" s="74"/>
     </row>
     <row r="113" spans="2:14" ht="15" thickBot="1">
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="51"/>
-      <c r="E113" s="54"/>
-      <c r="F113" s="63"/>
-      <c r="G113" s="54"/>
-      <c r="H113" s="51"/>
-      <c r="I113" s="69"/>
-      <c r="J113" s="54"/>
-      <c r="K113" s="54"/>
-      <c r="L113" s="51"/>
+      <c r="B113" s="61"/>
+      <c r="C113" s="61"/>
+      <c r="D113" s="61"/>
+      <c r="E113" s="55"/>
+      <c r="F113" s="57"/>
+      <c r="G113" s="55"/>
+      <c r="H113" s="61"/>
+      <c r="I113" s="80"/>
+      <c r="J113" s="55"/>
+      <c r="K113" s="55"/>
+      <c r="L113" s="61"/>
       <c r="M113" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="N113" s="51"/>
+      <c r="N113" s="61"/>
     </row>
     <row r="114" spans="2:14" ht="36">
-      <c r="B114" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="52">
+      <c r="B114" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="64">
         <v>18</v>
       </c>
-      <c r="D114" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E114" s="52">
+      <c r="D114" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E114" s="64">
         <v>27</v>
       </c>
-      <c r="F114" s="61">
+      <c r="F114" s="65">
         <v>29</v>
       </c>
-      <c r="G114" s="52">
+      <c r="G114" s="64">
         <v>29</v>
       </c>
-      <c r="H114" s="58" t="s">
+      <c r="H114" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="I114" s="49" t="s">
+      <c r="I114" s="72" t="s">
         <v>210</v>
       </c>
-      <c r="J114" s="52" t="s">
+      <c r="J114" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K114" s="52" t="s">
+      <c r="K114" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="L114" s="49" t="s">
+      <c r="L114" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M114" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="N114" s="49" t="s">
+      <c r="N114" s="72" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="115" spans="2:14" ht="24">
-      <c r="B115" s="50"/>
-      <c r="C115" s="53"/>
-      <c r="D115" s="50"/>
-      <c r="E115" s="53"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="53"/>
-      <c r="H115" s="59"/>
-      <c r="I115" s="50"/>
-      <c r="J115" s="53"/>
-      <c r="K115" s="53"/>
-      <c r="L115" s="50"/>
+      <c r="B115" s="74"/>
+      <c r="C115" s="70"/>
+      <c r="D115" s="74"/>
+      <c r="E115" s="70"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="70"/>
+      <c r="H115" s="73"/>
+      <c r="I115" s="74"/>
+      <c r="J115" s="70"/>
+      <c r="K115" s="70"/>
+      <c r="L115" s="74"/>
       <c r="M115" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N115" s="50"/>
+      <c r="N115" s="74"/>
     </row>
     <row r="116" spans="2:14">
-      <c r="B116" s="50"/>
-      <c r="C116" s="53"/>
-      <c r="D116" s="50"/>
-      <c r="E116" s="53"/>
-      <c r="F116" s="62"/>
-      <c r="G116" s="53"/>
-      <c r="H116" s="59"/>
-      <c r="I116" s="50"/>
-      <c r="J116" s="53"/>
-      <c r="K116" s="53"/>
-      <c r="L116" s="50"/>
+      <c r="B116" s="74"/>
+      <c r="C116" s="70"/>
+      <c r="D116" s="74"/>
+      <c r="E116" s="70"/>
+      <c r="F116" s="71"/>
+      <c r="G116" s="70"/>
+      <c r="H116" s="73"/>
+      <c r="I116" s="74"/>
+      <c r="J116" s="70"/>
+      <c r="K116" s="70"/>
+      <c r="L116" s="74"/>
       <c r="M116" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N116" s="50"/>
+      <c r="N116" s="74"/>
     </row>
     <row r="117" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B117" s="51"/>
-      <c r="C117" s="54"/>
-      <c r="D117" s="51"/>
-      <c r="E117" s="54"/>
-      <c r="F117" s="63"/>
-      <c r="G117" s="54"/>
-      <c r="H117" s="60"/>
-      <c r="I117" s="51"/>
-      <c r="J117" s="54"/>
-      <c r="K117" s="54"/>
-      <c r="L117" s="51"/>
+      <c r="B117" s="61"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="61"/>
+      <c r="E117" s="55"/>
+      <c r="F117" s="57"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="63"/>
+      <c r="I117" s="61"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="55"/>
+      <c r="L117" s="61"/>
       <c r="M117" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="N117" s="51"/>
+      <c r="N117" s="61"/>
     </row>
     <row r="118" spans="2:14" ht="36">
-      <c r="B118" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="52">
+      <c r="B118" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="64">
         <v>19</v>
       </c>
-      <c r="D118" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E118" s="52">
+      <c r="D118" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="64">
         <v>28</v>
       </c>
-      <c r="F118" s="61">
+      <c r="F118" s="65">
         <v>30</v>
       </c>
-      <c r="G118" s="52">
+      <c r="G118" s="64">
         <v>30</v>
       </c>
-      <c r="H118" s="58" t="s">
+      <c r="H118" s="66" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="49" t="s">
+      <c r="I118" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="J118" s="52" t="s">
+      <c r="J118" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K118" s="52" t="s">
+      <c r="K118" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="L118" s="49" t="s">
+      <c r="L118" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M118" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="N118" s="49" t="s">
+      <c r="N118" s="72" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:14" ht="36">
-      <c r="B119" s="50"/>
-      <c r="C119" s="53"/>
-      <c r="D119" s="50"/>
-      <c r="E119" s="53"/>
-      <c r="F119" s="62"/>
-      <c r="G119" s="53"/>
-      <c r="H119" s="59"/>
-      <c r="I119" s="50"/>
-      <c r="J119" s="53"/>
-      <c r="K119" s="53"/>
-      <c r="L119" s="50"/>
+      <c r="B119" s="74"/>
+      <c r="C119" s="70"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="70"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="70"/>
+      <c r="H119" s="73"/>
+      <c r="I119" s="74"/>
+      <c r="J119" s="70"/>
+      <c r="K119" s="70"/>
+      <c r="L119" s="74"/>
       <c r="M119" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="N119" s="50"/>
+      <c r="N119" s="74"/>
     </row>
     <row r="120" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B120" s="51"/>
-      <c r="C120" s="54"/>
-      <c r="D120" s="51"/>
-      <c r="E120" s="54"/>
-      <c r="F120" s="63"/>
-      <c r="G120" s="54"/>
-      <c r="H120" s="60"/>
-      <c r="I120" s="51"/>
-      <c r="J120" s="54"/>
-      <c r="K120" s="54"/>
-      <c r="L120" s="51"/>
+      <c r="B120" s="61"/>
+      <c r="C120" s="55"/>
+      <c r="D120" s="61"/>
+      <c r="E120" s="55"/>
+      <c r="F120" s="57"/>
+      <c r="G120" s="55"/>
+      <c r="H120" s="63"/>
+      <c r="I120" s="61"/>
+      <c r="J120" s="55"/>
+      <c r="K120" s="55"/>
+      <c r="L120" s="61"/>
       <c r="M120" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="N120" s="51"/>
+      <c r="N120" s="61"/>
     </row>
     <row r="121" spans="2:14" ht="48.75" thickBot="1">
       <c r="B121" s="17">
@@ -6790,96 +7280,96 @@
       </c>
     </row>
     <row r="122" spans="2:14" ht="24">
-      <c r="B122" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="G122" s="52">
+      <c r="B122" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="G122" s="64">
         <v>32</v>
       </c>
-      <c r="H122" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I122" s="49" t="s">
+      <c r="H122" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="I122" s="72" t="s">
         <v>222</v>
       </c>
-      <c r="J122" s="52" t="s">
+      <c r="J122" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="K122" s="52" t="s">
+      <c r="K122" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="L122" s="49" t="s">
+      <c r="L122" s="72" t="s">
         <v>88</v>
       </c>
       <c r="M122" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N122" s="49" t="s">
+      <c r="N122" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="24">
-      <c r="B123" s="50"/>
-      <c r="C123" s="50"/>
-      <c r="D123" s="50"/>
-      <c r="E123" s="50"/>
-      <c r="F123" s="56"/>
-      <c r="G123" s="53"/>
-      <c r="H123" s="50"/>
-      <c r="I123" s="50"/>
-      <c r="J123" s="53"/>
-      <c r="K123" s="53"/>
-      <c r="L123" s="50"/>
+      <c r="B123" s="74"/>
+      <c r="C123" s="74"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="70"/>
+      <c r="H123" s="74"/>
+      <c r="I123" s="74"/>
+      <c r="J123" s="70"/>
+      <c r="K123" s="70"/>
+      <c r="L123" s="74"/>
       <c r="M123" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N123" s="50"/>
+      <c r="N123" s="74"/>
     </row>
     <row r="124" spans="2:14">
-      <c r="B124" s="50"/>
-      <c r="C124" s="50"/>
-      <c r="D124" s="50"/>
-      <c r="E124" s="50"/>
-      <c r="F124" s="56"/>
-      <c r="G124" s="53"/>
-      <c r="H124" s="50"/>
-      <c r="I124" s="50"/>
-      <c r="J124" s="53"/>
-      <c r="K124" s="53"/>
-      <c r="L124" s="50"/>
+      <c r="B124" s="74"/>
+      <c r="C124" s="74"/>
+      <c r="D124" s="74"/>
+      <c r="E124" s="74"/>
+      <c r="F124" s="87"/>
+      <c r="G124" s="70"/>
+      <c r="H124" s="74"/>
+      <c r="I124" s="74"/>
+      <c r="J124" s="70"/>
+      <c r="K124" s="70"/>
+      <c r="L124" s="74"/>
       <c r="M124" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="50"/>
+      <c r="N124" s="74"/>
     </row>
     <row r="125" spans="2:14" ht="15" thickBot="1">
-      <c r="B125" s="51"/>
-      <c r="C125" s="51"/>
-      <c r="D125" s="51"/>
-      <c r="E125" s="51"/>
-      <c r="F125" s="57"/>
-      <c r="G125" s="54"/>
-      <c r="H125" s="51"/>
-      <c r="I125" s="51"/>
-      <c r="J125" s="54"/>
-      <c r="K125" s="54"/>
-      <c r="L125" s="51"/>
+      <c r="B125" s="61"/>
+      <c r="C125" s="61"/>
+      <c r="D125" s="61"/>
+      <c r="E125" s="61"/>
+      <c r="F125" s="88"/>
+      <c r="G125" s="55"/>
+      <c r="H125" s="61"/>
+      <c r="I125" s="61"/>
+      <c r="J125" s="55"/>
+      <c r="K125" s="55"/>
+      <c r="L125" s="61"/>
       <c r="M125" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="51"/>
+      <c r="N125" s="61"/>
     </row>
     <row r="126" spans="2:14" ht="15" thickBot="1">
       <c r="B126" s="24" t="s">
@@ -6965,32 +7455,254 @@
     </row>
   </sheetData>
   <mergeCells count="298">
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="I122:I125"/>
+    <mergeCell ref="J122:J125"/>
+    <mergeCell ref="K122:K125"/>
+    <mergeCell ref="L122:L125"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="H118:H120"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="J118:J120"/>
+    <mergeCell ref="K118:K120"/>
+    <mergeCell ref="L118:L120"/>
+    <mergeCell ref="N118:N120"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="E118:E120"/>
+    <mergeCell ref="F118:F120"/>
+    <mergeCell ref="G118:G120"/>
+    <mergeCell ref="K114:K117"/>
+    <mergeCell ref="L114:L117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="J114:J117"/>
+    <mergeCell ref="K101:K105"/>
+    <mergeCell ref="L101:L105"/>
+    <mergeCell ref="N101:N105"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="J110:J113"/>
+    <mergeCell ref="K110:K113"/>
+    <mergeCell ref="L110:L113"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="D106:D108"/>
+    <mergeCell ref="E106:E108"/>
+    <mergeCell ref="F106:F108"/>
+    <mergeCell ref="K94:K100"/>
+    <mergeCell ref="L94:L100"/>
+    <mergeCell ref="N94:N100"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="C101:C105"/>
+    <mergeCell ref="D101:D105"/>
+    <mergeCell ref="E101:E105"/>
+    <mergeCell ref="F101:F105"/>
+    <mergeCell ref="G101:G105"/>
+    <mergeCell ref="H101:H105"/>
+    <mergeCell ref="N106:N108"/>
+    <mergeCell ref="G106:G108"/>
+    <mergeCell ref="H106:H108"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="K106:K108"/>
+    <mergeCell ref="L106:L108"/>
+    <mergeCell ref="I101:I105"/>
+    <mergeCell ref="J101:J105"/>
+    <mergeCell ref="B94:B100"/>
+    <mergeCell ref="C94:C100"/>
+    <mergeCell ref="D94:D100"/>
+    <mergeCell ref="E94:E100"/>
+    <mergeCell ref="F94:F100"/>
+    <mergeCell ref="G94:G100"/>
+    <mergeCell ref="H94:H100"/>
+    <mergeCell ref="I94:I100"/>
+    <mergeCell ref="J94:J100"/>
+    <mergeCell ref="K84:K87"/>
+    <mergeCell ref="L84:L87"/>
+    <mergeCell ref="N84:N87"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="D88:D93"/>
+    <mergeCell ref="E88:E93"/>
+    <mergeCell ref="F88:F93"/>
+    <mergeCell ref="N88:N93"/>
+    <mergeCell ref="G88:G93"/>
+    <mergeCell ref="H88:H93"/>
+    <mergeCell ref="I88:I93"/>
+    <mergeCell ref="J88:J93"/>
+    <mergeCell ref="K88:K93"/>
+    <mergeCell ref="L88:L93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="E84:E87"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="G84:G87"/>
+    <mergeCell ref="H84:H87"/>
+    <mergeCell ref="I84:I87"/>
+    <mergeCell ref="J84:J87"/>
+    <mergeCell ref="N75:N79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="G80:G83"/>
+    <mergeCell ref="H80:H83"/>
+    <mergeCell ref="I80:I83"/>
+    <mergeCell ref="J80:J83"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="H75:H79"/>
+    <mergeCell ref="I75:I79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="K75:K79"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="D75:D79"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="K80:K83"/>
+    <mergeCell ref="L80:L83"/>
+    <mergeCell ref="N80:N83"/>
+    <mergeCell ref="H71:H74"/>
+    <mergeCell ref="I71:I74"/>
+    <mergeCell ref="J71:J74"/>
+    <mergeCell ref="K71:K74"/>
+    <mergeCell ref="L71:L74"/>
+    <mergeCell ref="N71:N74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="G71:G74"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="K67:K70"/>
+    <mergeCell ref="L67:L70"/>
+    <mergeCell ref="N67:N70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="G59:G63"/>
+    <mergeCell ref="H59:H63"/>
+    <mergeCell ref="I59:I63"/>
+    <mergeCell ref="J59:J63"/>
+    <mergeCell ref="K59:K63"/>
+    <mergeCell ref="L59:L63"/>
+    <mergeCell ref="H54:H58"/>
+    <mergeCell ref="I54:I58"/>
+    <mergeCell ref="J54:J58"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="L54:L58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="D59:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="F59:F63"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="I48:I53"/>
+    <mergeCell ref="J48:J53"/>
+    <mergeCell ref="K48:K53"/>
+    <mergeCell ref="L48:L53"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="G48:G53"/>
+    <mergeCell ref="K39:K42"/>
+    <mergeCell ref="L39:L42"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="L32:L38"/>
+    <mergeCell ref="B32:B38"/>
+    <mergeCell ref="C32:C38"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="E32:E38"/>
+    <mergeCell ref="F32:F38"/>
+    <mergeCell ref="G32:G38"/>
+    <mergeCell ref="H32:H38"/>
+    <mergeCell ref="I32:I38"/>
+    <mergeCell ref="J32:J38"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I24:I27"/>
+    <mergeCell ref="J24:J27"/>
+    <mergeCell ref="K24:K27"/>
+    <mergeCell ref="L24:L27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="J28:J31"/>
+    <mergeCell ref="K28:K31"/>
+    <mergeCell ref="L28:L31"/>
+    <mergeCell ref="B17:B23"/>
     <mergeCell ref="C17:C23"/>
     <mergeCell ref="D17:D23"/>
     <mergeCell ref="E17:E23"/>
@@ -7015,261 +7727,39 @@
     <mergeCell ref="J11:J16"/>
     <mergeCell ref="K11:K16"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="L11:L16"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I24:I27"/>
-    <mergeCell ref="J24:J27"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="L24:L27"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="F24:F27"/>
-    <mergeCell ref="G24:G27"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="H28:H31"/>
-    <mergeCell ref="I28:I31"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="K28:K31"/>
-    <mergeCell ref="L28:L31"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="J39:J42"/>
-    <mergeCell ref="K32:K38"/>
-    <mergeCell ref="L32:L38"/>
-    <mergeCell ref="B32:B38"/>
-    <mergeCell ref="C32:C38"/>
-    <mergeCell ref="D32:D38"/>
-    <mergeCell ref="E32:E38"/>
-    <mergeCell ref="F32:F38"/>
-    <mergeCell ref="G32:G38"/>
-    <mergeCell ref="H32:H38"/>
-    <mergeCell ref="I32:I38"/>
-    <mergeCell ref="J32:J38"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="G48:G53"/>
-    <mergeCell ref="K39:K42"/>
-    <mergeCell ref="L39:L42"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="D43:D47"/>
-    <mergeCell ref="E43:E47"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="G39:G42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="I39:I42"/>
-    <mergeCell ref="H48:H53"/>
-    <mergeCell ref="I48:I53"/>
-    <mergeCell ref="J48:J53"/>
-    <mergeCell ref="K48:K53"/>
-    <mergeCell ref="L48:L53"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="K43:K47"/>
-    <mergeCell ref="L43:L47"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="D59:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="H59:H63"/>
-    <mergeCell ref="I59:I63"/>
-    <mergeCell ref="J59:J63"/>
-    <mergeCell ref="K59:K63"/>
-    <mergeCell ref="L59:L63"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="J54:J58"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="J67:J70"/>
-    <mergeCell ref="K67:K70"/>
-    <mergeCell ref="L67:L70"/>
-    <mergeCell ref="N67:N70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="H71:H74"/>
-    <mergeCell ref="I71:I74"/>
-    <mergeCell ref="J71:J74"/>
-    <mergeCell ref="K71:K74"/>
-    <mergeCell ref="L71:L74"/>
-    <mergeCell ref="N71:N74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="E71:E74"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="N75:N79"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="G80:G83"/>
-    <mergeCell ref="H80:H83"/>
-    <mergeCell ref="I80:I83"/>
-    <mergeCell ref="J80:J83"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="H75:H79"/>
-    <mergeCell ref="I75:I79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="K75:K79"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="D75:D79"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="K80:K83"/>
-    <mergeCell ref="L80:L83"/>
-    <mergeCell ref="N80:N83"/>
-    <mergeCell ref="K84:K87"/>
-    <mergeCell ref="L84:L87"/>
-    <mergeCell ref="N84:N87"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="D88:D93"/>
-    <mergeCell ref="E88:E93"/>
-    <mergeCell ref="F88:F93"/>
-    <mergeCell ref="N88:N93"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="H88:H93"/>
-    <mergeCell ref="I88:I93"/>
-    <mergeCell ref="J88:J93"/>
-    <mergeCell ref="K88:K93"/>
-    <mergeCell ref="L88:L93"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E84:E87"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="G84:G87"/>
-    <mergeCell ref="H84:H87"/>
-    <mergeCell ref="I84:I87"/>
-    <mergeCell ref="J84:J87"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="C94:C100"/>
-    <mergeCell ref="D94:D100"/>
-    <mergeCell ref="E94:E100"/>
-    <mergeCell ref="F94:F100"/>
-    <mergeCell ref="G94:G100"/>
-    <mergeCell ref="H94:H100"/>
-    <mergeCell ref="I94:I100"/>
-    <mergeCell ref="J94:J100"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="D106:D108"/>
-    <mergeCell ref="E106:E108"/>
-    <mergeCell ref="F106:F108"/>
-    <mergeCell ref="K94:K100"/>
-    <mergeCell ref="L94:L100"/>
-    <mergeCell ref="N94:N100"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="C101:C105"/>
-    <mergeCell ref="D101:D105"/>
-    <mergeCell ref="E101:E105"/>
-    <mergeCell ref="F101:F105"/>
-    <mergeCell ref="G101:G105"/>
-    <mergeCell ref="H101:H105"/>
-    <mergeCell ref="N106:N108"/>
-    <mergeCell ref="G106:G108"/>
-    <mergeCell ref="H106:H108"/>
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="J106:J108"/>
-    <mergeCell ref="K106:K108"/>
-    <mergeCell ref="L106:L108"/>
-    <mergeCell ref="I101:I105"/>
-    <mergeCell ref="J101:J105"/>
-    <mergeCell ref="K101:K105"/>
-    <mergeCell ref="L101:L105"/>
-    <mergeCell ref="N101:N105"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="J110:J113"/>
-    <mergeCell ref="K110:K113"/>
-    <mergeCell ref="L110:L113"/>
-    <mergeCell ref="N110:N113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="I114:I117"/>
-    <mergeCell ref="J114:J117"/>
-    <mergeCell ref="K114:K117"/>
-    <mergeCell ref="L114:L117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="H118:H120"/>
-    <mergeCell ref="I118:I120"/>
-    <mergeCell ref="J118:J120"/>
-    <mergeCell ref="K118:K120"/>
-    <mergeCell ref="L118:L120"/>
-    <mergeCell ref="N118:N120"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="E118:E120"/>
-    <mergeCell ref="F118:F120"/>
-    <mergeCell ref="G118:G120"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="I122:I125"/>
-    <mergeCell ref="J122:J125"/>
-    <mergeCell ref="K122:K125"/>
-    <mergeCell ref="L122:L125"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE67EDC-82AC-429D-88AC-E2E8E455B911}">
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -8220,7 +8710,7 @@
         <v>2101989</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H3" t="s">
         <v>468</v>
@@ -8240,7 +8730,7 @@
         <v>469</v>
       </c>
       <c r="D4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E4" t="s">
         <v>437</v>
@@ -8249,7 +8739,7 @@
         <v>1717550</v>
       </c>
       <c r="G4" s="48" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>471</v>
@@ -8275,7 +8765,7 @@
         <v>630470</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H5" t="s">
         <v>470</v>
@@ -8304,7 +8794,7 @@
         <v>630500</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I6" s="46" t="s">
         <v>32</v>
@@ -8330,7 +8820,7 @@
         <v>1830730</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H7" t="s">
         <v>465</v>
@@ -8350,7 +8840,7 @@
         <v>473</v>
       </c>
       <c r="D8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E8" t="s">
         <v>437</v>
@@ -8359,7 +8849,7 @@
         <v>1830725</v>
       </c>
       <c r="G8" s="48" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>471</v>
@@ -8376,7 +8866,7 @@
         <v>473</v>
       </c>
       <c r="D9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E9" t="s">
         <v>437</v>
@@ -8385,7 +8875,7 @@
         <v>1830729</v>
       </c>
       <c r="G9" s="48" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H9" t="s">
         <v>466</v>
@@ -8405,7 +8895,7 @@
         <v>473</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E10" t="s">
         <v>437</v>
@@ -8414,7 +8904,7 @@
         <v>1830725</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>471</v>
@@ -8447,7 +8937,7 @@
         <v>479</v>
       </c>
       <c r="D14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E14" t="s">
         <v>437</v>
@@ -8456,7 +8946,7 @@
         <v>1892523</v>
       </c>
       <c r="G14" s="48" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8516,7 +9006,7 @@
         <v>417</v>
       </c>
       <c r="D17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E17" t="s">
         <v>437</v>
@@ -8525,10 +9015,10 @@
         <v>2352005</v>
       </c>
       <c r="G17" s="48" t="s">
+        <v>495</v>
+      </c>
+      <c r="H17" t="s">
         <v>496</v>
-      </c>
-      <c r="H17" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -8551,7 +9041,7 @@
         <v>2535699</v>
       </c>
       <c r="G19" s="48" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I19" s="46" t="s">
         <v>32</v>
@@ -8765,13 +9255,13 @@
         <v>476</v>
       </c>
       <c r="E38" t="s">
+        <v>491</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="H38" t="s">
         <v>492</v>
-      </c>
-      <c r="G38" s="48" t="s">
-        <v>491</v>
-      </c>
-      <c r="H38" t="s">
-        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -8805,37 +9295,37 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
     <col min="7" max="7" width="46.625" style="1" customWidth="1"/>
     <col min="8" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" ht="45">
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="30">
       <c r="A1" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>7</v>
@@ -8852,111 +9342,150 @@
         <v>487</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>549</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="42.75">
+        <v>519</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8964,13 +9493,13 @@
         <v>515</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -8978,44 +9507,44 @@
         <v>516</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5">
+      <c r="A12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>517</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.5">
+        <v>519</v>
+      </c>
+      <c r="G12" s="49" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G13" s="88" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9026,13 +9555,13 @@
         <v>534</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.5">
       <c r="A15" t="s">
         <v>535</v>
       </c>
@@ -9040,51 +9569,125 @@
         <v>536</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.5">
+        <v>519</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="G16" s="88" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>544</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>546</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="57">
+      <c r="A20" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>523</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>432</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>557</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -9094,6 +9697,99 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F4E72C-2ACE-4813-A14A-59C7689800F0}">
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="35.25" style="89" customWidth="1"/>
+    <col min="7" max="7" width="2.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="89" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="5" customFormat="1">
+      <c r="B2" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="89" t="s">
+        <v>563</v>
+      </c>
+      <c r="B3">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="C3">
+        <v>2.13</v>
+      </c>
+      <c r="D3">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="89" t="s">
+        <v>566</v>
+      </c>
+      <c r="B4">
+        <v>0.75</v>
+      </c>
+      <c r="C4">
+        <v>0.75</v>
+      </c>
+      <c r="D4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="89" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="5">
+        <f>B3-B4</f>
+        <v>1.5299999999999998</v>
+      </c>
+      <c r="C5" s="5">
+        <f t="shared" ref="C5:D5" si="0">C3-C4</f>
+        <v>1.38</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4700000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6">
+      <c r="F19" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6">
+      <c r="F34" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3088DDB1-6775-4E99-BEAA-2B2DCCF23E2B}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -9121,108 +9817,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFAF250-9E30-4C8F-8A0D-6D92E94AA6E7}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15">
-      <c r="A1" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" s="9">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="9">
-        <v>7.4</v>
-      </c>
-      <c r="D4">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="8">
-        <f>(B4-B3)/(B5/1000)</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="8">
-        <f>(B4-B3)*B5/1000</f>
-        <v>5.3999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="9">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="8">
-        <f>B14*B13/(B12+B13)</f>
-        <v>1.85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D643B34C-1D11-4D52-9922-3C6DE76AD0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1976A523-0F15-41D7-85CA-2150A432BFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" tabRatio="745" activeTab="7" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" tabRatio="783" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="FMEA" sheetId="2" r:id="rId3"/>
     <sheet name="Power State Diagram" sheetId="3" r:id="rId4"/>
     <sheet name="TO DO" sheetId="5" r:id="rId5"/>
-    <sheet name="Bits to purchase" sheetId="11" r:id="rId6"/>
-    <sheet name="Problems" sheetId="4" r:id="rId7"/>
+    <sheet name="Problems" sheetId="4" r:id="rId6"/>
+    <sheet name="Bits to purchase" sheetId="11" r:id="rId7"/>
     <sheet name="Ignitor current" sheetId="12" r:id="rId8"/>
     <sheet name="Lessons Learned" sheetId="6" r:id="rId9"/>
     <sheet name="Calculations" sheetId="8" r:id="rId10"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="568">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -1802,6 +1802,9 @@
   </si>
   <si>
     <t>lead set (Ω) to be subtracted</t>
+  </si>
+  <si>
+    <t>ACB 1 Jan 2026</t>
   </si>
 </sst>
 </file>
@@ -2233,79 +2236,86 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2317,40 +2327,33 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4409,31 +4412,31 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15" thickBot="1"/>
     <row r="3" spans="2:16" ht="15" thickBot="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="58" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="88" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="84" t="s">
         <v>232</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="53"/>
+      <c r="N3" s="83"/>
     </row>
     <row r="4" spans="2:16" ht="96.75" customHeight="1" thickBot="1">
       <c r="B4" s="27" t="s">
@@ -4457,10 +4460,10 @@
       <c r="H4" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="59"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="51"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="87"/>
       <c r="M4" s="11" t="s">
         <v>81</v>
       </c>
@@ -4472,43 +4475,43 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15" thickTop="1">
-      <c r="B5" s="54">
+      <c r="B5" s="67">
         <v>2</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="67">
         <v>1</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="67">
         <v>2</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="67">
         <v>2</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="68">
         <v>2</v>
       </c>
-      <c r="G5" s="54">
+      <c r="G5" s="67">
         <v>2</v>
       </c>
-      <c r="H5" s="62" t="s">
+      <c r="H5" s="76" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="60" t="s">
+      <c r="L5" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="66" t="s">
         <v>85</v>
       </c>
       <c r="P5" t="s">
@@ -4516,60 +4519,60 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="15" thickBot="1">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="63"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="62"/>
       <c r="I6" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="64">
+      <c r="B7" s="54">
         <v>3</v>
       </c>
-      <c r="C7" s="64">
+      <c r="C7" s="54">
         <v>2</v>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="54">
         <v>3</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="54">
         <v>3</v>
       </c>
-      <c r="F7" s="65">
+      <c r="F7" s="63">
         <v>3</v>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="54">
         <v>3</v>
       </c>
-      <c r="H7" s="66" t="s">
+      <c r="H7" s="60" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="64" t="s">
+      <c r="K7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="72" t="s">
+      <c r="L7" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="51" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
@@ -4577,21 +4580,21 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="63"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1">
       <c r="B9" s="17">
@@ -4676,37 +4679,37 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="24">
-      <c r="B11" s="64">
+      <c r="B11" s="54">
         <v>5</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="54">
         <v>5</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="54">
         <v>6</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="54">
         <v>6</v>
       </c>
-      <c r="F11" s="65">
+      <c r="F11" s="63">
         <v>6</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="54">
         <v>6</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="75" t="s">
+      <c r="I11" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="64" t="s">
+      <c r="J11" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="66" t="s">
+      <c r="K11" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="72" t="s">
+      <c r="L11" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="29" t="s">
@@ -4720,17 +4723,17 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="24">
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="74"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="52"/>
       <c r="M12" s="14" t="s">
         <v>104</v>
       </c>
@@ -4739,17 +4742,17 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="24">
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="73"/>
-      <c r="L13" s="74"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="52"/>
       <c r="M13" s="14" t="s">
         <v>105</v>
       </c>
@@ -4758,17 +4761,17 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="36">
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="74"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="52"/>
       <c r="M14" s="14" t="s">
         <v>106</v>
       </c>
@@ -4777,71 +4780,71 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="24">
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="74"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="52"/>
       <c r="M15" s="29" t="s">
         <v>107</v>
       </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="61"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="21" t="s">
         <v>108</v>
       </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:16" ht="24">
-      <c r="B17" s="64">
+      <c r="B17" s="54">
         <v>6</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="54">
         <v>6</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="54">
         <v>7</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="54">
         <v>7</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="63">
         <v>7</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="54">
         <v>7</v>
       </c>
-      <c r="H17" s="66" t="s">
+      <c r="H17" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="72" t="s">
+      <c r="I17" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="64" t="s">
+      <c r="J17" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="64" t="s">
+      <c r="K17" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="72" t="s">
+      <c r="L17" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -4852,17 +4855,17 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="24">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="74"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="52"/>
       <c r="M18" s="23" t="s">
         <v>116</v>
       </c>
@@ -4871,122 +4874,122 @@
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="74"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="52"/>
       <c r="M19" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="2:16" ht="24">
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="74"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="52"/>
       <c r="M20" s="23" t="s">
         <v>118</v>
       </c>
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="2:16" ht="24">
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="74"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="52"/>
       <c r="M21" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="2:16" ht="24">
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="74"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="52"/>
       <c r="M22" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="61"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="53"/>
       <c r="M23" s="40" t="s">
         <v>121</v>
       </c>
       <c r="N23" s="24"/>
     </row>
     <row r="24" spans="2:16" ht="36">
-      <c r="B24" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="64">
+      <c r="B24" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="54">
         <v>8</v>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="54">
         <v>8</v>
       </c>
-      <c r="F24" s="65">
+      <c r="F24" s="63">
         <v>8</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G24" s="54">
         <v>8</v>
       </c>
-      <c r="H24" s="66" t="s">
+      <c r="H24" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="72" t="s">
+      <c r="I24" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="64" t="s">
+      <c r="J24" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="66" t="s">
+      <c r="K24" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="72" t="s">
+      <c r="L24" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -4997,17 +5000,17 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="24">
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="74"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="52"/>
       <c r="M25" s="29" t="s">
         <v>125</v>
       </c>
@@ -5019,17 +5022,17 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="24">
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="74"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="52"/>
       <c r="M26" s="14" t="s">
         <v>126</v>
       </c>
@@ -5038,17 +5041,17 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="61"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="53"/>
       <c r="M27" s="19" t="s">
         <v>127</v>
       </c>
@@ -5057,37 +5060,37 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="24">
-      <c r="B28" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="64">
+      <c r="B28" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="54">
         <v>9</v>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="54">
         <v>9</v>
       </c>
-      <c r="F28" s="65">
+      <c r="F28" s="63">
         <v>9</v>
       </c>
-      <c r="G28" s="64">
+      <c r="G28" s="54">
         <v>9</v>
       </c>
-      <c r="H28" s="66" t="s">
+      <c r="H28" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="I28" s="72" t="s">
+      <c r="I28" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="64" t="s">
+      <c r="J28" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="64" t="s">
+      <c r="K28" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L28" s="72" t="s">
+      <c r="L28" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M28" s="14" t="s">
@@ -5098,17 +5101,17 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="74"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="52"/>
       <c r="M29" s="14" t="s">
         <v>135</v>
       </c>
@@ -5117,71 +5120,71 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="24">
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="74"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="52"/>
       <c r="M30" s="29" t="s">
         <v>103</v>
       </c>
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="61"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="53"/>
       <c r="M31" s="40" t="s">
         <v>136</v>
       </c>
       <c r="N31" s="24"/>
     </row>
     <row r="32" spans="2:16" ht="24">
-      <c r="B32" s="64">
+      <c r="B32" s="54">
         <v>7</v>
       </c>
-      <c r="C32" s="64">
+      <c r="C32" s="54">
         <v>7</v>
       </c>
-      <c r="D32" s="64">
+      <c r="D32" s="54">
         <v>10</v>
       </c>
-      <c r="E32" s="64">
+      <c r="E32" s="54">
         <v>10</v>
       </c>
-      <c r="F32" s="65">
+      <c r="F32" s="63">
         <v>10</v>
       </c>
-      <c r="G32" s="64">
+      <c r="G32" s="54">
         <v>10</v>
       </c>
-      <c r="H32" s="66" t="s">
+      <c r="H32" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="72" t="s">
+      <c r="I32" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="64" t="s">
+      <c r="J32" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="66" t="s">
+      <c r="K32" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="L32" s="72" t="s">
+      <c r="L32" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M32" s="14" t="s">
@@ -5192,17 +5195,17 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="24">
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="73"/>
-      <c r="L33" s="74"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="52"/>
       <c r="M33" s="14" t="s">
         <v>104</v>
       </c>
@@ -5211,17 +5214,17 @@
       </c>
     </row>
     <row r="34" spans="2:16" ht="36">
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="73"/>
-      <c r="L34" s="74"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="52"/>
       <c r="M34" s="14" t="s">
         <v>140</v>
       </c>
@@ -5233,105 +5236,105 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="24">
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="74"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="52"/>
       <c r="M35" s="23" t="s">
         <v>141</v>
       </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="74"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="74"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="52"/>
       <c r="M36" s="14" t="s">
         <v>142</v>
       </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" spans="2:16" ht="24">
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="74"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="73"/>
-      <c r="L37" s="74"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="52"/>
       <c r="M37" s="37" t="s">
         <v>126</v>
       </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="63"/>
-      <c r="L38" s="61"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="53"/>
       <c r="M38" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N38" s="18"/>
     </row>
     <row r="39" spans="2:16" ht="24.75" thickTop="1">
-      <c r="B39" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="54">
+      <c r="B39" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="67">
         <v>8</v>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="67">
         <v>11</v>
       </c>
-      <c r="E39" s="54">
+      <c r="E39" s="67">
         <v>11</v>
       </c>
-      <c r="F39" s="56">
+      <c r="F39" s="68">
         <v>11</v>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="67">
         <v>11</v>
       </c>
-      <c r="H39" s="62" t="s">
+      <c r="H39" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="60" t="s">
+      <c r="I39" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="J39" s="54" t="s">
+      <c r="J39" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="62" t="s">
+      <c r="K39" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="60" t="s">
+      <c r="L39" s="66" t="s">
         <v>88</v>
       </c>
       <c r="M39" s="14" t="s">
@@ -5342,17 +5345,17 @@
       </c>
     </row>
     <row r="40" spans="2:16" ht="24">
-      <c r="B40" s="74"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="74"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="74"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="52"/>
       <c r="M40" s="14" t="s">
         <v>116</v>
       </c>
@@ -5361,17 +5364,17 @@
       </c>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="74"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="73"/>
-      <c r="L41" s="74"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="52"/>
       <c r="M41" s="14" t="s">
         <v>142</v>
       </c>
@@ -5383,60 +5386,60 @@
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1">
-      <c r="B42" s="61"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="61"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="53"/>
       <c r="M42" s="19" t="s">
         <v>147</v>
       </c>
       <c r="N42" s="18"/>
     </row>
     <row r="43" spans="2:16">
-      <c r="B43" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="64">
+      <c r="B43" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="54">
         <v>9</v>
       </c>
-      <c r="D43" s="64">
+      <c r="D43" s="54">
         <v>12</v>
       </c>
-      <c r="E43" s="64">
+      <c r="E43" s="54">
         <v>12</v>
       </c>
-      <c r="F43" s="65">
+      <c r="F43" s="63">
         <v>12</v>
       </c>
-      <c r="G43" s="64">
+      <c r="G43" s="54">
         <v>12</v>
       </c>
-      <c r="H43" s="66" t="s">
+      <c r="H43" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="I43" s="72" t="s">
+      <c r="I43" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="64" t="s">
+      <c r="K43" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L43" s="72" t="s">
+      <c r="L43" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M43" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N43" s="78" t="s">
+      <c r="N43" s="75" t="s">
         <v>154</v>
       </c>
       <c r="P43" t="s">
@@ -5444,143 +5447,143 @@
       </c>
     </row>
     <row r="44" spans="2:16" ht="24">
-      <c r="B44" s="74"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="74"/>
-      <c r="J44" s="70"/>
-      <c r="K44" s="70"/>
-      <c r="L44" s="74"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="52"/>
       <c r="M44" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N44" s="79"/>
+      <c r="N44" s="70"/>
     </row>
     <row r="45" spans="2:16" ht="24">
-      <c r="B45" s="74"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="74"/>
-      <c r="J45" s="70"/>
-      <c r="K45" s="70"/>
-      <c r="L45" s="74"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="52"/>
       <c r="M45" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="79"/>
+      <c r="N45" s="70"/>
     </row>
     <row r="46" spans="2:16" ht="24">
-      <c r="B46" s="74"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="74"/>
-      <c r="J46" s="70"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="74"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="52"/>
       <c r="M46" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N46" s="79"/>
+      <c r="N46" s="70"/>
     </row>
     <row r="47" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B47" s="61"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="55"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="61"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="55"/>
-      <c r="L47" s="61"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
+      <c r="L47" s="53"/>
       <c r="M47" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N47" s="80"/>
+      <c r="N47" s="71"/>
     </row>
     <row r="48" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B48" s="64">
+      <c r="B48" s="54">
         <v>8</v>
       </c>
-      <c r="C48" s="64">
+      <c r="C48" s="54">
         <v>10</v>
       </c>
-      <c r="D48" s="64">
+      <c r="D48" s="54">
         <v>13</v>
       </c>
-      <c r="E48" s="64">
+      <c r="E48" s="54">
         <v>13</v>
       </c>
-      <c r="F48" s="65">
+      <c r="F48" s="63">
         <v>13</v>
       </c>
-      <c r="G48" s="64">
+      <c r="G48" s="54">
         <v>13</v>
       </c>
-      <c r="H48" s="66" t="s">
+      <c r="H48" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="72" t="s">
+      <c r="I48" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="64" t="s">
+      <c r="J48" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="64" t="s">
+      <c r="K48" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L48" s="72" t="s">
+      <c r="L48" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M48" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N48" s="72" t="s">
+      <c r="N48" s="51" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24">
-      <c r="B49" s="70"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="70"/>
-      <c r="K49" s="70"/>
-      <c r="L49" s="74"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="52"/>
       <c r="M49" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N49" s="74"/>
+      <c r="N49" s="52"/>
     </row>
     <row r="50" spans="2:16" ht="24">
-      <c r="B50" s="70"/>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="71"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="74"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="74"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="52"/>
       <c r="M50" s="14" t="s">
         <v>159</v>
       </c>
@@ -5592,88 +5595,88 @@
       </c>
     </row>
     <row r="51" spans="2:16" ht="24">
-      <c r="B51" s="70"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="74"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="74"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="64"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="L51" s="52"/>
       <c r="M51" s="14" t="s">
         <v>120</v>
       </c>
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="2:16" ht="24">
-      <c r="B52" s="70"/>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="73"/>
-      <c r="I52" s="74"/>
-      <c r="J52" s="70"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="74"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="52"/>
       <c r="M52" s="14" t="s">
         <v>115</v>
       </c>
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B53" s="55"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="55"/>
-      <c r="H53" s="63"/>
-      <c r="I53" s="61"/>
-      <c r="J53" s="55"/>
-      <c r="K53" s="55"/>
-      <c r="L53" s="61"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="L53" s="53"/>
       <c r="M53" s="21" t="s">
         <v>127</v>
       </c>
       <c r="N53" s="24"/>
     </row>
     <row r="54" spans="2:16" ht="24">
-      <c r="B54" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="64">
+      <c r="B54" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="54">
         <v>14</v>
       </c>
-      <c r="F54" s="65">
+      <c r="F54" s="63">
         <v>14</v>
       </c>
-      <c r="G54" s="64">
+      <c r="G54" s="54">
         <v>14</v>
       </c>
-      <c r="H54" s="66" t="s">
+      <c r="H54" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="78" t="s">
+      <c r="I54" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="J54" s="64" t="s">
+      <c r="J54" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="64" t="s">
+      <c r="K54" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="72" t="s">
+      <c r="L54" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M54" s="14" t="s">
@@ -5687,17 +5690,17 @@
       </c>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="71"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="79"/>
-      <c r="J55" s="70"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="74"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="55"/>
+      <c r="L55" s="52"/>
       <c r="M55" s="14" t="s">
         <v>151</v>
       </c>
@@ -5706,88 +5709,88 @@
       </c>
     </row>
     <row r="56" spans="2:16">
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="70"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="74"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="55"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="55"/>
+      <c r="L56" s="52"/>
       <c r="M56" s="14" t="s">
         <v>117</v>
       </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" spans="2:16" ht="24">
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="71"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="74"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="55"/>
+      <c r="L57" s="52"/>
       <c r="M57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1">
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="55"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="55"/>
-      <c r="H58" s="63"/>
-      <c r="I58" s="80"/>
-      <c r="J58" s="55"/>
-      <c r="K58" s="55"/>
-      <c r="L58" s="61"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="62"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="19" t="s">
         <v>162</v>
       </c>
       <c r="N58" s="18"/>
     </row>
     <row r="59" spans="2:16" ht="24">
-      <c r="B59" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="64">
+      <c r="B59" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="54">
         <v>11</v>
       </c>
-      <c r="D59" s="64">
+      <c r="D59" s="54">
         <v>14</v>
       </c>
-      <c r="E59" s="64">
+      <c r="E59" s="54">
         <v>15</v>
       </c>
-      <c r="F59" s="65">
+      <c r="F59" s="63">
         <v>15</v>
       </c>
-      <c r="G59" s="64">
+      <c r="G59" s="54">
         <v>15</v>
       </c>
-      <c r="H59" s="66" t="s">
+      <c r="H59" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="78" t="s">
+      <c r="I59" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="64" t="s">
+      <c r="J59" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="64" t="s">
+      <c r="K59" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L59" s="72" t="s">
+      <c r="L59" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M59" s="14" t="s">
@@ -5801,17 +5804,17 @@
       </c>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" s="74"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="71"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="73"/>
-      <c r="I60" s="79"/>
-      <c r="J60" s="70"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="74"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="55"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="55"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="52"/>
       <c r="M60" s="14" t="s">
         <v>157</v>
       </c>
@@ -5820,51 +5823,51 @@
       </c>
     </row>
     <row r="61" spans="2:16" ht="24">
-      <c r="B61" s="74"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="70"/>
-      <c r="K61" s="70"/>
-      <c r="L61" s="74"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="55"/>
+      <c r="L61" s="52"/>
       <c r="M61" s="14" t="s">
         <v>104</v>
       </c>
       <c r="N61" s="22"/>
     </row>
     <row r="62" spans="2:16" ht="24">
-      <c r="B62" s="74"/>
-      <c r="C62" s="70"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="71"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="79"/>
-      <c r="J62" s="70"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="74"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="55"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="70"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="55"/>
+      <c r="L62" s="52"/>
       <c r="M62" s="13" t="s">
         <v>167</v>
       </c>
       <c r="N62" s="22"/>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1">
-      <c r="B63" s="61"/>
-      <c r="C63" s="55"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="55"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="55"/>
-      <c r="H63" s="63"/>
-      <c r="I63" s="80"/>
-      <c r="J63" s="55"/>
-      <c r="K63" s="55"/>
-      <c r="L63" s="61"/>
+      <c r="B63" s="53"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="62"/>
+      <c r="I63" s="71"/>
+      <c r="J63" s="56"/>
+      <c r="K63" s="56"/>
+      <c r="L63" s="53"/>
       <c r="M63" s="19" t="s">
         <v>168</v>
       </c>
@@ -5994,43 +5997,43 @@
       </c>
     </row>
     <row r="67" spans="2:16" ht="36">
-      <c r="B67" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="64">
+      <c r="B67" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="54">
         <v>18</v>
       </c>
-      <c r="F67" s="65">
+      <c r="F67" s="63">
         <v>18</v>
       </c>
-      <c r="G67" s="64">
+      <c r="G67" s="54">
         <v>18</v>
       </c>
-      <c r="H67" s="66" t="s">
+      <c r="H67" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="I67" s="78" t="s">
+      <c r="I67" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="64" t="s">
+      <c r="J67" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="64" t="s">
+      <c r="K67" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="72" t="s">
+      <c r="L67" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M67" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="N67" s="72" t="s">
+      <c r="N67" s="51" t="s">
         <v>88</v>
       </c>
       <c r="P67" t="s">
@@ -6038,860 +6041,860 @@
       </c>
     </row>
     <row r="68" spans="2:16" ht="24">
-      <c r="B68" s="74"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="70"/>
-      <c r="F68" s="71"/>
-      <c r="G68" s="70"/>
-      <c r="H68" s="73"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="70"/>
-      <c r="K68" s="70"/>
-      <c r="L68" s="74"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="64"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="61"/>
+      <c r="I68" s="70"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+      <c r="L68" s="52"/>
       <c r="M68" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N68" s="74"/>
+      <c r="N68" s="52"/>
     </row>
     <row r="69" spans="2:16" ht="24">
-      <c r="B69" s="74"/>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="70"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="79"/>
-      <c r="J69" s="70"/>
-      <c r="K69" s="70"/>
-      <c r="L69" s="74"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="55"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="55"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="70"/>
+      <c r="J69" s="55"/>
+      <c r="K69" s="55"/>
+      <c r="L69" s="52"/>
       <c r="M69" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="74"/>
+      <c r="N69" s="52"/>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1">
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="61"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="55"/>
-      <c r="H70" s="63"/>
-      <c r="I70" s="80"/>
-      <c r="J70" s="55"/>
-      <c r="K70" s="55"/>
-      <c r="L70" s="61"/>
+      <c r="B70" s="53"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="53"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="62"/>
+      <c r="I70" s="71"/>
+      <c r="J70" s="56"/>
+      <c r="K70" s="56"/>
+      <c r="L70" s="53"/>
       <c r="M70" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N70" s="61"/>
+      <c r="N70" s="53"/>
     </row>
     <row r="71" spans="2:16" ht="24">
-      <c r="B71" s="64">
+      <c r="B71" s="54">
         <v>11</v>
       </c>
-      <c r="C71" s="64">
+      <c r="C71" s="54">
         <v>14</v>
       </c>
-      <c r="D71" s="64">
+      <c r="D71" s="54">
         <v>17</v>
       </c>
-      <c r="E71" s="64">
+      <c r="E71" s="54">
         <v>19</v>
       </c>
-      <c r="F71" s="65">
+      <c r="F71" s="63">
         <v>19</v>
       </c>
-      <c r="G71" s="64">
+      <c r="G71" s="54">
         <v>19</v>
       </c>
-      <c r="H71" s="66" t="s">
+      <c r="H71" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="72" t="s">
+      <c r="I71" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="J71" s="64" t="s">
+      <c r="J71" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K71" s="64" t="s">
+      <c r="K71" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L71" s="72" t="s">
+      <c r="L71" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M71" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="N71" s="72" t="s">
+      <c r="N71" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="24">
-      <c r="B72" s="70"/>
-      <c r="C72" s="70"/>
-      <c r="D72" s="70"/>
-      <c r="E72" s="70"/>
-      <c r="F72" s="71"/>
-      <c r="G72" s="70"/>
-      <c r="H72" s="73"/>
-      <c r="I72" s="74"/>
-      <c r="J72" s="70"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="74"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="64"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="52"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="L72" s="52"/>
       <c r="M72" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="N72" s="74"/>
+      <c r="N72" s="52"/>
     </row>
     <row r="73" spans="2:16" ht="24">
-      <c r="B73" s="70"/>
-      <c r="C73" s="70"/>
-      <c r="D73" s="70"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="71"/>
-      <c r="G73" s="70"/>
-      <c r="H73" s="73"/>
-      <c r="I73" s="74"/>
-      <c r="J73" s="70"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="74"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="64"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="61"/>
+      <c r="I73" s="52"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="55"/>
+      <c r="L73" s="52"/>
       <c r="M73" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="N73" s="74"/>
+      <c r="N73" s="52"/>
     </row>
     <row r="74" spans="2:16" ht="48.75" thickBot="1">
-      <c r="B74" s="55"/>
-      <c r="C74" s="55"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="55"/>
-      <c r="H74" s="63"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="55"/>
-      <c r="K74" s="55"/>
-      <c r="L74" s="61"/>
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="62"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="56"/>
+      <c r="K74" s="56"/>
+      <c r="L74" s="53"/>
       <c r="M74" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N74" s="61"/>
+      <c r="N74" s="53"/>
     </row>
     <row r="75" spans="2:16" ht="36.75" thickTop="1">
-      <c r="B75" s="54">
+      <c r="B75" s="67">
         <v>12</v>
       </c>
-      <c r="C75" s="54">
+      <c r="C75" s="67">
         <v>15</v>
       </c>
-      <c r="D75" s="54">
+      <c r="D75" s="67">
         <v>18</v>
       </c>
-      <c r="E75" s="54">
+      <c r="E75" s="67">
         <v>20</v>
       </c>
-      <c r="F75" s="56">
+      <c r="F75" s="68">
         <v>20</v>
       </c>
-      <c r="G75" s="54">
+      <c r="G75" s="67">
         <v>20</v>
       </c>
-      <c r="H75" s="62" t="s">
+      <c r="H75" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="60" t="s">
+      <c r="I75" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="J75" s="54" t="s">
+      <c r="J75" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="54" t="s">
+      <c r="K75" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="L75" s="81">
+      <c r="L75" s="77">
         <v>-7</v>
       </c>
       <c r="M75" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="60" t="s">
+      <c r="N75" s="66" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="24">
-      <c r="B76" s="70"/>
-      <c r="C76" s="70"/>
-      <c r="D76" s="70"/>
-      <c r="E76" s="70"/>
-      <c r="F76" s="71"/>
-      <c r="G76" s="70"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="70"/>
-      <c r="K76" s="70"/>
-      <c r="L76" s="82"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="64"/>
+      <c r="G76" s="55"/>
+      <c r="H76" s="61"/>
+      <c r="I76" s="52"/>
+      <c r="J76" s="55"/>
+      <c r="K76" s="55"/>
+      <c r="L76" s="73"/>
       <c r="M76" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="74"/>
+      <c r="N76" s="52"/>
     </row>
     <row r="77" spans="2:16" ht="24">
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="71"/>
-      <c r="G77" s="70"/>
-      <c r="H77" s="73"/>
-      <c r="I77" s="74"/>
-      <c r="J77" s="70"/>
-      <c r="K77" s="70"/>
-      <c r="L77" s="82"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="55"/>
+      <c r="D77" s="55"/>
+      <c r="E77" s="55"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="55"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="55"/>
+      <c r="L77" s="73"/>
       <c r="M77" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="N77" s="74"/>
+      <c r="N77" s="52"/>
     </row>
     <row r="78" spans="2:16">
-      <c r="B78" s="70"/>
-      <c r="C78" s="70"/>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="71"/>
-      <c r="G78" s="70"/>
-      <c r="H78" s="73"/>
-      <c r="I78" s="74"/>
-      <c r="J78" s="70"/>
-      <c r="K78" s="70"/>
-      <c r="L78" s="82"/>
+      <c r="B78" s="55"/>
+      <c r="C78" s="55"/>
+      <c r="D78" s="55"/>
+      <c r="E78" s="55"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="55"/>
+      <c r="H78" s="61"/>
+      <c r="I78" s="52"/>
+      <c r="J78" s="55"/>
+      <c r="K78" s="55"/>
+      <c r="L78" s="73"/>
       <c r="M78" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N78" s="74"/>
+      <c r="N78" s="52"/>
     </row>
     <row r="79" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B79" s="55"/>
-      <c r="C79" s="55"/>
-      <c r="D79" s="55"/>
-      <c r="E79" s="55"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="63"/>
-      <c r="I79" s="61"/>
-      <c r="J79" s="55"/>
-      <c r="K79" s="55"/>
-      <c r="L79" s="83"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="62"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="56"/>
+      <c r="K79" s="56"/>
+      <c r="L79" s="74"/>
       <c r="M79" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="61"/>
+      <c r="N79" s="53"/>
     </row>
     <row r="80" spans="2:16">
-      <c r="B80" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D80" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="F80" s="65">
+      <c r="B80" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="63">
         <v>21</v>
       </c>
-      <c r="G80" s="64">
+      <c r="G80" s="54">
         <v>21</v>
       </c>
-      <c r="H80" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80" s="72" t="s">
+      <c r="H80" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="J80" s="64" t="s">
+      <c r="J80" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K80" s="64" t="s">
+      <c r="K80" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L80" s="72" t="s">
+      <c r="L80" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M80" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N80" s="72" t="s">
+      <c r="N80" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:19" ht="48">
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="70"/>
-      <c r="H81" s="74"/>
-      <c r="I81" s="74"/>
-      <c r="J81" s="70"/>
-      <c r="K81" s="70"/>
-      <c r="L81" s="74"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="64"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="52"/>
+      <c r="I81" s="52"/>
+      <c r="J81" s="55"/>
+      <c r="K81" s="55"/>
+      <c r="L81" s="52"/>
       <c r="M81" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="N81" s="74"/>
+      <c r="N81" s="52"/>
     </row>
     <row r="82" spans="2:19" ht="24">
-      <c r="B82" s="74"/>
-      <c r="C82" s="74"/>
-      <c r="D82" s="74"/>
-      <c r="E82" s="74"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="70"/>
-      <c r="H82" s="74"/>
-      <c r="I82" s="74"/>
-      <c r="J82" s="70"/>
-      <c r="K82" s="70"/>
-      <c r="L82" s="74"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="64"/>
+      <c r="G82" s="55"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="52"/>
+      <c r="J82" s="55"/>
+      <c r="K82" s="55"/>
+      <c r="L82" s="52"/>
       <c r="M82" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="N82" s="74"/>
+      <c r="N82" s="52"/>
     </row>
     <row r="83" spans="2:19" ht="48.75" thickBot="1">
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
-      <c r="J83" s="55"/>
-      <c r="K83" s="55"/>
-      <c r="L83" s="61"/>
+      <c r="B83" s="53"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="53"/>
+      <c r="I83" s="53"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
+      <c r="L83" s="53"/>
       <c r="M83" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="N83" s="61"/>
+      <c r="N83" s="53"/>
     </row>
     <row r="84" spans="2:19">
-      <c r="B84" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="65">
+      <c r="B84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="63">
         <v>22</v>
       </c>
-      <c r="G84" s="64">
+      <c r="G84" s="54">
         <v>22</v>
       </c>
-      <c r="H84" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84" s="72" t="s">
+      <c r="H84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="J84" s="64" t="s">
+      <c r="J84" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="64" t="s">
+      <c r="K84" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="72" t="s">
+      <c r="L84" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N84" s="72" t="s">
+      <c r="N84" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:19" ht="24">
-      <c r="B85" s="74"/>
-      <c r="C85" s="74"/>
-      <c r="D85" s="74"/>
-      <c r="E85" s="74"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="70"/>
-      <c r="H85" s="74"/>
-      <c r="I85" s="74"/>
-      <c r="J85" s="70"/>
-      <c r="K85" s="70"/>
-      <c r="L85" s="74"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="64"/>
+      <c r="G85" s="55"/>
+      <c r="H85" s="52"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="55"/>
+      <c r="K85" s="55"/>
+      <c r="L85" s="52"/>
       <c r="M85" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N85" s="74"/>
+      <c r="N85" s="52"/>
     </row>
     <row r="86" spans="2:19" ht="24">
-      <c r="B86" s="74"/>
-      <c r="C86" s="74"/>
-      <c r="D86" s="74"/>
-      <c r="E86" s="74"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="70"/>
-      <c r="H86" s="74"/>
-      <c r="I86" s="74"/>
-      <c r="J86" s="70"/>
-      <c r="K86" s="70"/>
-      <c r="L86" s="74"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="64"/>
+      <c r="G86" s="55"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="55"/>
+      <c r="K86" s="55"/>
+      <c r="L86" s="52"/>
       <c r="M86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N86" s="74"/>
+      <c r="N86" s="52"/>
       <c r="S86" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="57"/>
-      <c r="G87" s="55"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61"/>
-      <c r="J87" s="55"/>
-      <c r="K87" s="55"/>
-      <c r="L87" s="61"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="56"/>
+      <c r="K87" s="56"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="N87" s="61"/>
+      <c r="N87" s="53"/>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="64">
+      <c r="B88" s="54">
         <v>13</v>
       </c>
-      <c r="C88" s="64">
+      <c r="C88" s="54">
         <v>16</v>
       </c>
-      <c r="D88" s="64">
+      <c r="D88" s="54">
         <v>19</v>
       </c>
-      <c r="E88" s="64">
+      <c r="E88" s="54">
         <v>21</v>
       </c>
-      <c r="F88" s="65">
+      <c r="F88" s="63">
         <v>23</v>
       </c>
-      <c r="G88" s="64">
+      <c r="G88" s="54">
         <v>23</v>
       </c>
-      <c r="H88" s="66" t="s">
+      <c r="H88" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="I88" s="72" t="s">
+      <c r="I88" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="J88" s="64" t="s">
+      <c r="J88" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K88" s="64" t="s">
+      <c r="K88" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L88" s="72" t="s">
+      <c r="L88" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M88" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="N88" s="72" t="s">
+      <c r="N88" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="2:19" ht="24">
-      <c r="B89" s="70"/>
-      <c r="C89" s="70"/>
-      <c r="D89" s="70"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="70"/>
-      <c r="H89" s="73"/>
-      <c r="I89" s="74"/>
-      <c r="J89" s="70"/>
-      <c r="K89" s="70"/>
-      <c r="L89" s="74"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="55"/>
+      <c r="D89" s="55"/>
+      <c r="E89" s="55"/>
+      <c r="F89" s="64"/>
+      <c r="G89" s="55"/>
+      <c r="H89" s="61"/>
+      <c r="I89" s="52"/>
+      <c r="J89" s="55"/>
+      <c r="K89" s="55"/>
+      <c r="L89" s="52"/>
       <c r="M89" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N89" s="74"/>
+      <c r="N89" s="52"/>
     </row>
     <row r="90" spans="2:19">
-      <c r="B90" s="70"/>
-      <c r="C90" s="70"/>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="70"/>
-      <c r="H90" s="73"/>
-      <c r="I90" s="74"/>
-      <c r="J90" s="70"/>
-      <c r="K90" s="70"/>
-      <c r="L90" s="74"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
+      <c r="F90" s="64"/>
+      <c r="G90" s="55"/>
+      <c r="H90" s="61"/>
+      <c r="I90" s="52"/>
+      <c r="J90" s="55"/>
+      <c r="K90" s="55"/>
+      <c r="L90" s="52"/>
       <c r="M90" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="N90" s="74"/>
+      <c r="N90" s="52"/>
     </row>
     <row r="91" spans="2:19">
-      <c r="B91" s="70"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="70"/>
-      <c r="E91" s="70"/>
-      <c r="F91" s="71"/>
-      <c r="G91" s="70"/>
-      <c r="H91" s="73"/>
-      <c r="I91" s="74"/>
-      <c r="J91" s="70"/>
-      <c r="K91" s="70"/>
-      <c r="L91" s="74"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="64"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="61"/>
+      <c r="I91" s="52"/>
+      <c r="J91" s="55"/>
+      <c r="K91" s="55"/>
+      <c r="L91" s="52"/>
       <c r="M91" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N91" s="74"/>
+      <c r="N91" s="52"/>
     </row>
     <row r="92" spans="2:19" ht="24">
-      <c r="B92" s="70"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="70"/>
-      <c r="E92" s="70"/>
-      <c r="F92" s="71"/>
-      <c r="G92" s="70"/>
-      <c r="H92" s="73"/>
-      <c r="I92" s="74"/>
-      <c r="J92" s="70"/>
-      <c r="K92" s="70"/>
-      <c r="L92" s="74"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="64"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="61"/>
+      <c r="I92" s="52"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
+      <c r="L92" s="52"/>
       <c r="M92" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="N92" s="74"/>
+      <c r="N92" s="52"/>
     </row>
     <row r="93" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B93" s="55"/>
-      <c r="C93" s="55"/>
-      <c r="D93" s="55"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="63"/>
-      <c r="I93" s="61"/>
-      <c r="J93" s="55"/>
-      <c r="K93" s="55"/>
-      <c r="L93" s="61"/>
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="62"/>
+      <c r="I93" s="53"/>
+      <c r="J93" s="56"/>
+      <c r="K93" s="56"/>
+      <c r="L93" s="53"/>
       <c r="M93" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N93" s="61"/>
+      <c r="N93" s="53"/>
     </row>
     <row r="94" spans="2:19">
-      <c r="B94" s="64">
+      <c r="B94" s="54">
         <v>14</v>
       </c>
-      <c r="C94" s="64">
+      <c r="C94" s="54">
         <v>17</v>
       </c>
-      <c r="D94" s="64">
+      <c r="D94" s="54">
         <v>20</v>
       </c>
-      <c r="E94" s="64">
+      <c r="E94" s="54">
         <v>22</v>
       </c>
-      <c r="F94" s="65">
+      <c r="F94" s="63">
         <v>24</v>
       </c>
-      <c r="G94" s="64">
+      <c r="G94" s="54">
         <v>24</v>
       </c>
-      <c r="H94" s="66" t="s">
+      <c r="H94" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="I94" s="72" t="s">
+      <c r="I94" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="J94" s="64" t="s">
+      <c r="J94" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K94" s="64" t="s">
+      <c r="K94" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L94" s="84">
+      <c r="L94" s="72">
         <v>-7</v>
       </c>
       <c r="M94" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N94" s="72" t="s">
+      <c r="N94" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:19" ht="24">
-      <c r="B95" s="70"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
-      <c r="F95" s="71"/>
-      <c r="G95" s="70"/>
-      <c r="H95" s="73"/>
-      <c r="I95" s="74"/>
-      <c r="J95" s="70"/>
-      <c r="K95" s="70"/>
-      <c r="L95" s="82"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="64"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="61"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
+      <c r="L95" s="73"/>
       <c r="M95" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="N95" s="74"/>
+      <c r="N95" s="52"/>
     </row>
     <row r="96" spans="2:19" ht="24">
-      <c r="B96" s="70"/>
-      <c r="C96" s="70"/>
-      <c r="D96" s="70"/>
-      <c r="E96" s="70"/>
-      <c r="F96" s="71"/>
-      <c r="G96" s="70"/>
-      <c r="H96" s="73"/>
-      <c r="I96" s="74"/>
-      <c r="J96" s="70"/>
-      <c r="K96" s="70"/>
-      <c r="L96" s="82"/>
+      <c r="B96" s="55"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="64"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="61"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
+      <c r="L96" s="73"/>
       <c r="M96" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N96" s="74"/>
+      <c r="N96" s="52"/>
     </row>
     <row r="97" spans="2:16" ht="24">
-      <c r="B97" s="70"/>
-      <c r="C97" s="70"/>
-      <c r="D97" s="70"/>
-      <c r="E97" s="70"/>
-      <c r="F97" s="71"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="73"/>
-      <c r="I97" s="74"/>
-      <c r="J97" s="70"/>
-      <c r="K97" s="70"/>
-      <c r="L97" s="82"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="64"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="61"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
+      <c r="L97" s="73"/>
       <c r="M97" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="N97" s="74"/>
+      <c r="N97" s="52"/>
     </row>
     <row r="98" spans="2:16">
-      <c r="B98" s="70"/>
-      <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
-      <c r="E98" s="70"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="70"/>
-      <c r="H98" s="73"/>
-      <c r="I98" s="74"/>
-      <c r="J98" s="70"/>
-      <c r="K98" s="70"/>
-      <c r="L98" s="82"/>
+      <c r="B98" s="55"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="61"/>
+      <c r="I98" s="52"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
+      <c r="L98" s="73"/>
       <c r="M98" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N98" s="74"/>
+      <c r="N98" s="52"/>
     </row>
     <row r="99" spans="2:16" ht="24">
-      <c r="B99" s="70"/>
-      <c r="C99" s="70"/>
-      <c r="D99" s="70"/>
-      <c r="E99" s="70"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="70"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="74"/>
-      <c r="J99" s="70"/>
-      <c r="K99" s="70"/>
-      <c r="L99" s="82"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="55"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="64"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="52"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="55"/>
+      <c r="L99" s="73"/>
       <c r="M99" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="N99" s="74"/>
+      <c r="N99" s="52"/>
     </row>
     <row r="100" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B100" s="55"/>
-      <c r="C100" s="55"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="55"/>
-      <c r="H100" s="63"/>
-      <c r="I100" s="61"/>
-      <c r="J100" s="55"/>
-      <c r="K100" s="55"/>
-      <c r="L100" s="83"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="56"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="56"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="56"/>
+      <c r="H100" s="62"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="56"/>
+      <c r="K100" s="56"/>
+      <c r="L100" s="74"/>
       <c r="M100" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N100" s="61"/>
+      <c r="N100" s="53"/>
     </row>
     <row r="101" spans="2:16">
-      <c r="B101" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E101" s="64">
+      <c r="B101" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="54">
         <v>23</v>
       </c>
-      <c r="F101" s="65">
+      <c r="F101" s="63">
         <v>25</v>
       </c>
-      <c r="G101" s="64">
+      <c r="G101" s="54">
         <v>25</v>
       </c>
-      <c r="H101" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="I101" s="72" t="s">
+      <c r="H101" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="I101" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="J101" s="64" t="s">
+      <c r="J101" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K101" s="64" t="s">
+      <c r="K101" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="72" t="s">
+      <c r="L101" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="N101" s="72" t="s">
+      <c r="N101" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="2:16">
-      <c r="B102" s="74"/>
-      <c r="C102" s="74"/>
-      <c r="D102" s="74"/>
-      <c r="E102" s="70"/>
-      <c r="F102" s="71"/>
-      <c r="G102" s="70"/>
-      <c r="H102" s="74"/>
-      <c r="I102" s="74"/>
-      <c r="J102" s="70"/>
-      <c r="K102" s="70"/>
-      <c r="L102" s="74"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="55"/>
+      <c r="F102" s="64"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="52"/>
+      <c r="I102" s="52"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="55"/>
+      <c r="L102" s="52"/>
       <c r="M102" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="N102" s="74"/>
+      <c r="N102" s="52"/>
     </row>
     <row r="103" spans="2:16" ht="24">
-      <c r="B103" s="74"/>
-      <c r="C103" s="74"/>
-      <c r="D103" s="74"/>
-      <c r="E103" s="70"/>
-      <c r="F103" s="71"/>
-      <c r="G103" s="70"/>
-      <c r="H103" s="74"/>
-      <c r="I103" s="74"/>
-      <c r="J103" s="70"/>
-      <c r="K103" s="70"/>
-      <c r="L103" s="74"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="64"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="52"/>
+      <c r="I103" s="52"/>
+      <c r="J103" s="55"/>
+      <c r="K103" s="55"/>
+      <c r="L103" s="52"/>
       <c r="M103" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N103" s="74"/>
+      <c r="N103" s="52"/>
     </row>
     <row r="104" spans="2:16" ht="24">
-      <c r="B104" s="74"/>
-      <c r="C104" s="74"/>
-      <c r="D104" s="74"/>
-      <c r="E104" s="70"/>
-      <c r="F104" s="71"/>
-      <c r="G104" s="70"/>
-      <c r="H104" s="74"/>
-      <c r="I104" s="74"/>
-      <c r="J104" s="70"/>
-      <c r="K104" s="70"/>
-      <c r="L104" s="74"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="64"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="52"/>
+      <c r="I104" s="52"/>
+      <c r="J104" s="55"/>
+      <c r="K104" s="55"/>
+      <c r="L104" s="52"/>
       <c r="M104" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="N104" s="74"/>
+      <c r="N104" s="52"/>
     </row>
     <row r="105" spans="2:16" ht="15" thickBot="1">
-      <c r="B105" s="61"/>
-      <c r="C105" s="61"/>
-      <c r="D105" s="61"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="57"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="61"/>
-      <c r="I105" s="61"/>
-      <c r="J105" s="55"/>
-      <c r="K105" s="55"/>
-      <c r="L105" s="61"/>
+      <c r="B105" s="53"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="56"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="56"/>
+      <c r="H105" s="53"/>
+      <c r="I105" s="53"/>
+      <c r="J105" s="56"/>
+      <c r="K105" s="56"/>
+      <c r="L105" s="53"/>
       <c r="M105" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="61"/>
+      <c r="N105" s="53"/>
     </row>
     <row r="106" spans="2:16">
-      <c r="B106" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="64">
+      <c r="B106" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="54">
         <v>24</v>
       </c>
-      <c r="F106" s="65">
+      <c r="F106" s="63">
         <v>26</v>
       </c>
-      <c r="G106" s="64">
+      <c r="G106" s="54">
         <v>26</v>
       </c>
-      <c r="H106" s="66" t="s">
+      <c r="H106" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="78" t="s">
+      <c r="I106" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="J106" s="64" t="s">
+      <c r="J106" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="64" t="s">
+      <c r="K106" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L106" s="72" t="s">
+      <c r="L106" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M106" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="N106" s="72" t="s">
+      <c r="N106" s="51" t="s">
         <v>203</v>
       </c>
       <c r="P106" t="s">
@@ -6899,38 +6902,38 @@
       </c>
     </row>
     <row r="107" spans="2:16">
-      <c r="B107" s="74"/>
-      <c r="C107" s="74"/>
-      <c r="D107" s="74"/>
-      <c r="E107" s="70"/>
-      <c r="F107" s="71"/>
-      <c r="G107" s="70"/>
-      <c r="H107" s="73"/>
-      <c r="I107" s="79"/>
-      <c r="J107" s="70"/>
-      <c r="K107" s="70"/>
-      <c r="L107" s="74"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="52"/>
+      <c r="D107" s="52"/>
+      <c r="E107" s="55"/>
+      <c r="F107" s="64"/>
+      <c r="G107" s="55"/>
+      <c r="H107" s="61"/>
+      <c r="I107" s="70"/>
+      <c r="J107" s="55"/>
+      <c r="K107" s="55"/>
+      <c r="L107" s="52"/>
       <c r="M107" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="N107" s="74"/>
+      <c r="N107" s="52"/>
     </row>
     <row r="108" spans="2:16" ht="15" thickBot="1">
-      <c r="B108" s="61"/>
-      <c r="C108" s="61"/>
-      <c r="D108" s="61"/>
-      <c r="E108" s="55"/>
-      <c r="F108" s="57"/>
-      <c r="G108" s="55"/>
-      <c r="H108" s="63"/>
-      <c r="I108" s="80"/>
-      <c r="J108" s="55"/>
-      <c r="K108" s="55"/>
-      <c r="L108" s="61"/>
+      <c r="B108" s="53"/>
+      <c r="C108" s="53"/>
+      <c r="D108" s="53"/>
+      <c r="E108" s="56"/>
+      <c r="F108" s="65"/>
+      <c r="G108" s="56"/>
+      <c r="H108" s="62"/>
+      <c r="I108" s="71"/>
+      <c r="J108" s="56"/>
+      <c r="K108" s="56"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="N108" s="61"/>
+      <c r="N108" s="53"/>
     </row>
     <row r="109" spans="2:16" ht="24.75" thickBot="1">
       <c r="B109" s="24" t="s">
@@ -6977,43 +6980,43 @@
       </c>
     </row>
     <row r="110" spans="2:16" ht="15" thickTop="1">
-      <c r="B110" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="54">
+      <c r="B110" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="67">
         <v>26</v>
       </c>
-      <c r="F110" s="56">
+      <c r="F110" s="68">
         <v>28</v>
       </c>
-      <c r="G110" s="54">
+      <c r="G110" s="67">
         <v>28</v>
       </c>
-      <c r="H110" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="I110" s="85" t="s">
+      <c r="H110" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="I110" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="J110" s="54" t="s">
+      <c r="J110" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="K110" s="54" t="s">
+      <c r="K110" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="L110" s="60" t="s">
+      <c r="L110" s="66" t="s">
         <v>88</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="N110" s="60" t="s">
+      <c r="N110" s="66" t="s">
         <v>206</v>
       </c>
       <c r="P110" t="s">
@@ -7021,222 +7024,222 @@
       </c>
     </row>
     <row r="111" spans="2:16" ht="24">
-      <c r="B111" s="74"/>
-      <c r="C111" s="74"/>
-      <c r="D111" s="74"/>
-      <c r="E111" s="70"/>
-      <c r="F111" s="71"/>
-      <c r="G111" s="70"/>
-      <c r="H111" s="74"/>
-      <c r="I111" s="79"/>
-      <c r="J111" s="70"/>
-      <c r="K111" s="70"/>
-      <c r="L111" s="74"/>
+      <c r="B111" s="52"/>
+      <c r="C111" s="52"/>
+      <c r="D111" s="52"/>
+      <c r="E111" s="55"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="55"/>
+      <c r="H111" s="52"/>
+      <c r="I111" s="70"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="55"/>
+      <c r="L111" s="52"/>
       <c r="M111" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="N111" s="74"/>
+      <c r="N111" s="52"/>
     </row>
     <row r="112" spans="2:16" ht="24">
-      <c r="B112" s="74"/>
-      <c r="C112" s="74"/>
-      <c r="D112" s="74"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="74"/>
-      <c r="I112" s="79"/>
-      <c r="J112" s="70"/>
-      <c r="K112" s="70"/>
-      <c r="L112" s="74"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="52"/>
+      <c r="D112" s="52"/>
+      <c r="E112" s="55"/>
+      <c r="F112" s="64"/>
+      <c r="G112" s="55"/>
+      <c r="H112" s="52"/>
+      <c r="I112" s="70"/>
+      <c r="J112" s="55"/>
+      <c r="K112" s="55"/>
+      <c r="L112" s="52"/>
       <c r="M112" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="74"/>
+      <c r="N112" s="52"/>
     </row>
     <row r="113" spans="2:14" ht="15" thickBot="1">
-      <c r="B113" s="61"/>
-      <c r="C113" s="61"/>
-      <c r="D113" s="61"/>
-      <c r="E113" s="55"/>
-      <c r="F113" s="57"/>
-      <c r="G113" s="55"/>
-      <c r="H113" s="61"/>
-      <c r="I113" s="80"/>
-      <c r="J113" s="55"/>
-      <c r="K113" s="55"/>
-      <c r="L113" s="61"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="56"/>
+      <c r="F113" s="65"/>
+      <c r="G113" s="56"/>
+      <c r="H113" s="53"/>
+      <c r="I113" s="71"/>
+      <c r="J113" s="56"/>
+      <c r="K113" s="56"/>
+      <c r="L113" s="53"/>
       <c r="M113" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="N113" s="61"/>
+      <c r="N113" s="53"/>
     </row>
     <row r="114" spans="2:14" ht="36">
-      <c r="B114" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="64">
+      <c r="B114" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="54">
         <v>18</v>
       </c>
-      <c r="D114" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E114" s="64">
+      <c r="D114" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E114" s="54">
         <v>27</v>
       </c>
-      <c r="F114" s="65">
+      <c r="F114" s="63">
         <v>29</v>
       </c>
-      <c r="G114" s="64">
+      <c r="G114" s="54">
         <v>29</v>
       </c>
-      <c r="H114" s="66" t="s">
+      <c r="H114" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="I114" s="72" t="s">
+      <c r="I114" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="J114" s="64" t="s">
+      <c r="J114" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K114" s="64" t="s">
+      <c r="K114" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L114" s="72" t="s">
+      <c r="L114" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M114" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="N114" s="72" t="s">
+      <c r="N114" s="51" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="115" spans="2:14" ht="24">
-      <c r="B115" s="74"/>
-      <c r="C115" s="70"/>
-      <c r="D115" s="74"/>
-      <c r="E115" s="70"/>
-      <c r="F115" s="71"/>
-      <c r="G115" s="70"/>
-      <c r="H115" s="73"/>
-      <c r="I115" s="74"/>
-      <c r="J115" s="70"/>
-      <c r="K115" s="70"/>
-      <c r="L115" s="74"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="55"/>
+      <c r="D115" s="52"/>
+      <c r="E115" s="55"/>
+      <c r="F115" s="64"/>
+      <c r="G115" s="55"/>
+      <c r="H115" s="61"/>
+      <c r="I115" s="52"/>
+      <c r="J115" s="55"/>
+      <c r="K115" s="55"/>
+      <c r="L115" s="52"/>
       <c r="M115" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="N115" s="74"/>
+      <c r="N115" s="52"/>
     </row>
     <row r="116" spans="2:14">
-      <c r="B116" s="74"/>
-      <c r="C116" s="70"/>
-      <c r="D116" s="74"/>
-      <c r="E116" s="70"/>
-      <c r="F116" s="71"/>
-      <c r="G116" s="70"/>
-      <c r="H116" s="73"/>
-      <c r="I116" s="74"/>
-      <c r="J116" s="70"/>
-      <c r="K116" s="70"/>
-      <c r="L116" s="74"/>
+      <c r="B116" s="52"/>
+      <c r="C116" s="55"/>
+      <c r="D116" s="52"/>
+      <c r="E116" s="55"/>
+      <c r="F116" s="64"/>
+      <c r="G116" s="55"/>
+      <c r="H116" s="61"/>
+      <c r="I116" s="52"/>
+      <c r="J116" s="55"/>
+      <c r="K116" s="55"/>
+      <c r="L116" s="52"/>
       <c r="M116" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N116" s="74"/>
+      <c r="N116" s="52"/>
     </row>
     <row r="117" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B117" s="61"/>
-      <c r="C117" s="55"/>
-      <c r="D117" s="61"/>
-      <c r="E117" s="55"/>
-      <c r="F117" s="57"/>
-      <c r="G117" s="55"/>
-      <c r="H117" s="63"/>
-      <c r="I117" s="61"/>
-      <c r="J117" s="55"/>
-      <c r="K117" s="55"/>
-      <c r="L117" s="61"/>
+      <c r="B117" s="53"/>
+      <c r="C117" s="56"/>
+      <c r="D117" s="53"/>
+      <c r="E117" s="56"/>
+      <c r="F117" s="65"/>
+      <c r="G117" s="56"/>
+      <c r="H117" s="62"/>
+      <c r="I117" s="53"/>
+      <c r="J117" s="56"/>
+      <c r="K117" s="56"/>
+      <c r="L117" s="53"/>
       <c r="M117" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="N117" s="61"/>
+      <c r="N117" s="53"/>
     </row>
     <row r="118" spans="2:14" ht="36">
-      <c r="B118" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="64">
+      <c r="B118" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="54">
         <v>19</v>
       </c>
-      <c r="D118" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E118" s="64">
+      <c r="D118" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="54">
         <v>28</v>
       </c>
-      <c r="F118" s="65">
+      <c r="F118" s="63">
         <v>30</v>
       </c>
-      <c r="G118" s="64">
+      <c r="G118" s="54">
         <v>30</v>
       </c>
-      <c r="H118" s="66" t="s">
+      <c r="H118" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="72" t="s">
+      <c r="I118" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="J118" s="64" t="s">
+      <c r="J118" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K118" s="64" t="s">
+      <c r="K118" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L118" s="72" t="s">
+      <c r="L118" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M118" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="N118" s="72" t="s">
+      <c r="N118" s="51" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:14" ht="36">
-      <c r="B119" s="74"/>
-      <c r="C119" s="70"/>
-      <c r="D119" s="74"/>
-      <c r="E119" s="70"/>
-      <c r="F119" s="71"/>
-      <c r="G119" s="70"/>
-      <c r="H119" s="73"/>
-      <c r="I119" s="74"/>
-      <c r="J119" s="70"/>
-      <c r="K119" s="70"/>
-      <c r="L119" s="74"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="55"/>
+      <c r="D119" s="52"/>
+      <c r="E119" s="55"/>
+      <c r="F119" s="64"/>
+      <c r="G119" s="55"/>
+      <c r="H119" s="61"/>
+      <c r="I119" s="52"/>
+      <c r="J119" s="55"/>
+      <c r="K119" s="55"/>
+      <c r="L119" s="52"/>
       <c r="M119" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="N119" s="74"/>
+      <c r="N119" s="52"/>
     </row>
     <row r="120" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B120" s="61"/>
-      <c r="C120" s="55"/>
-      <c r="D120" s="61"/>
-      <c r="E120" s="55"/>
-      <c r="F120" s="57"/>
-      <c r="G120" s="55"/>
-      <c r="H120" s="63"/>
-      <c r="I120" s="61"/>
-      <c r="J120" s="55"/>
-      <c r="K120" s="55"/>
-      <c r="L120" s="61"/>
+      <c r="B120" s="53"/>
+      <c r="C120" s="56"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="56"/>
+      <c r="F120" s="65"/>
+      <c r="G120" s="56"/>
+      <c r="H120" s="62"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="56"/>
+      <c r="K120" s="56"/>
+      <c r="L120" s="53"/>
       <c r="M120" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="N120" s="61"/>
+      <c r="N120" s="53"/>
     </row>
     <row r="121" spans="2:14" ht="48.75" thickBot="1">
       <c r="B121" s="17">
@@ -7280,96 +7283,96 @@
       </c>
     </row>
     <row r="122" spans="2:14" ht="24">
-      <c r="B122" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="86" t="s">
-        <v>88</v>
-      </c>
-      <c r="G122" s="64">
+      <c r="B122" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="G122" s="54">
         <v>32</v>
       </c>
-      <c r="H122" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="I122" s="72" t="s">
+      <c r="H122" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="I122" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="J122" s="64" t="s">
+      <c r="J122" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="K122" s="64" t="s">
+      <c r="K122" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="L122" s="72" t="s">
+      <c r="L122" s="51" t="s">
         <v>88</v>
       </c>
       <c r="M122" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N122" s="72" t="s">
+      <c r="N122" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="24">
-      <c r="B123" s="74"/>
-      <c r="C123" s="74"/>
-      <c r="D123" s="74"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="87"/>
-      <c r="G123" s="70"/>
-      <c r="H123" s="74"/>
-      <c r="I123" s="74"/>
-      <c r="J123" s="70"/>
-      <c r="K123" s="70"/>
-      <c r="L123" s="74"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="52"/>
+      <c r="D123" s="52"/>
+      <c r="E123" s="52"/>
+      <c r="F123" s="58"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="52"/>
+      <c r="I123" s="52"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="52"/>
       <c r="M123" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="N123" s="74"/>
+      <c r="N123" s="52"/>
     </row>
     <row r="124" spans="2:14">
-      <c r="B124" s="74"/>
-      <c r="C124" s="74"/>
-      <c r="D124" s="74"/>
-      <c r="E124" s="74"/>
-      <c r="F124" s="87"/>
-      <c r="G124" s="70"/>
-      <c r="H124" s="74"/>
-      <c r="I124" s="74"/>
-      <c r="J124" s="70"/>
-      <c r="K124" s="70"/>
-      <c r="L124" s="74"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="52"/>
+      <c r="D124" s="52"/>
+      <c r="E124" s="52"/>
+      <c r="F124" s="58"/>
+      <c r="G124" s="55"/>
+      <c r="H124" s="52"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="55"/>
+      <c r="K124" s="55"/>
+      <c r="L124" s="52"/>
       <c r="M124" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="74"/>
+      <c r="N124" s="52"/>
     </row>
     <row r="125" spans="2:14" ht="15" thickBot="1">
-      <c r="B125" s="61"/>
-      <c r="C125" s="61"/>
-      <c r="D125" s="61"/>
-      <c r="E125" s="61"/>
-      <c r="F125" s="88"/>
-      <c r="G125" s="55"/>
-      <c r="H125" s="61"/>
-      <c r="I125" s="61"/>
-      <c r="J125" s="55"/>
-      <c r="K125" s="55"/>
-      <c r="L125" s="61"/>
+      <c r="B125" s="53"/>
+      <c r="C125" s="53"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="53"/>
+      <c r="F125" s="59"/>
+      <c r="G125" s="56"/>
+      <c r="H125" s="53"/>
+      <c r="I125" s="53"/>
+      <c r="J125" s="56"/>
+      <c r="K125" s="56"/>
+      <c r="L125" s="53"/>
       <c r="M125" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="61"/>
+      <c r="N125" s="53"/>
     </row>
     <row r="126" spans="2:14" ht="15" thickBot="1">
       <c r="B126" s="24" t="s">
@@ -7455,57 +7458,229 @@
     </row>
   </sheetData>
   <mergeCells count="298">
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="I122:I125"/>
-    <mergeCell ref="J122:J125"/>
-    <mergeCell ref="K122:K125"/>
-    <mergeCell ref="L122:L125"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="G122:G125"/>
-    <mergeCell ref="H118:H120"/>
-    <mergeCell ref="I118:I120"/>
-    <mergeCell ref="J118:J120"/>
-    <mergeCell ref="K118:K120"/>
-    <mergeCell ref="L118:L120"/>
-    <mergeCell ref="N118:N120"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="E118:E120"/>
-    <mergeCell ref="F118:F120"/>
-    <mergeCell ref="G118:G120"/>
-    <mergeCell ref="K114:K117"/>
-    <mergeCell ref="L114:L117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="I114:I117"/>
-    <mergeCell ref="J114:J117"/>
-    <mergeCell ref="K101:K105"/>
-    <mergeCell ref="L101:L105"/>
-    <mergeCell ref="N101:N105"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="J110:J113"/>
-    <mergeCell ref="K110:K113"/>
-    <mergeCell ref="L110:L113"/>
-    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="D17:D23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="E11:E16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="G11:G16"/>
+    <mergeCell ref="H11:H16"/>
+    <mergeCell ref="H17:H23"/>
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="K17:K23"/>
+    <mergeCell ref="L17:L23"/>
+    <mergeCell ref="I11:I16"/>
+    <mergeCell ref="J11:J16"/>
+    <mergeCell ref="K11:K16"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I24:I27"/>
+    <mergeCell ref="J24:J27"/>
+    <mergeCell ref="K24:K27"/>
+    <mergeCell ref="L24:L27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="J28:J31"/>
+    <mergeCell ref="K28:K31"/>
+    <mergeCell ref="L28:L31"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="L32:L38"/>
+    <mergeCell ref="B32:B38"/>
+    <mergeCell ref="C32:C38"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="E32:E38"/>
+    <mergeCell ref="F32:F38"/>
+    <mergeCell ref="G32:G38"/>
+    <mergeCell ref="H32:H38"/>
+    <mergeCell ref="I32:I38"/>
+    <mergeCell ref="J32:J38"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="G48:G53"/>
+    <mergeCell ref="K39:K42"/>
+    <mergeCell ref="L39:L42"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="I48:I53"/>
+    <mergeCell ref="J48:J53"/>
+    <mergeCell ref="K48:K53"/>
+    <mergeCell ref="L48:L53"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="D59:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="F59:F63"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="G59:G63"/>
+    <mergeCell ref="H59:H63"/>
+    <mergeCell ref="I59:I63"/>
+    <mergeCell ref="J59:J63"/>
+    <mergeCell ref="K59:K63"/>
+    <mergeCell ref="L59:L63"/>
+    <mergeCell ref="H54:H58"/>
+    <mergeCell ref="I54:I58"/>
+    <mergeCell ref="J54:J58"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="L54:L58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="K67:K70"/>
+    <mergeCell ref="L67:L70"/>
+    <mergeCell ref="N67:N70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="H71:H74"/>
+    <mergeCell ref="I71:I74"/>
+    <mergeCell ref="J71:J74"/>
+    <mergeCell ref="K71:K74"/>
+    <mergeCell ref="L71:L74"/>
+    <mergeCell ref="N71:N74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="G71:G74"/>
+    <mergeCell ref="N75:N79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="G80:G83"/>
+    <mergeCell ref="H80:H83"/>
+    <mergeCell ref="I80:I83"/>
+    <mergeCell ref="J80:J83"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="H75:H79"/>
+    <mergeCell ref="I75:I79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="K75:K79"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="D75:D79"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="K80:K83"/>
+    <mergeCell ref="L80:L83"/>
+    <mergeCell ref="N80:N83"/>
+    <mergeCell ref="K84:K87"/>
+    <mergeCell ref="L84:L87"/>
+    <mergeCell ref="N84:N87"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="D88:D93"/>
+    <mergeCell ref="E88:E93"/>
+    <mergeCell ref="F88:F93"/>
+    <mergeCell ref="N88:N93"/>
+    <mergeCell ref="G88:G93"/>
+    <mergeCell ref="H88:H93"/>
+    <mergeCell ref="I88:I93"/>
+    <mergeCell ref="J88:J93"/>
+    <mergeCell ref="K88:K93"/>
+    <mergeCell ref="L88:L93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="E84:E87"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="G84:G87"/>
+    <mergeCell ref="H84:H87"/>
+    <mergeCell ref="I84:I87"/>
+    <mergeCell ref="J84:J87"/>
+    <mergeCell ref="B94:B100"/>
+    <mergeCell ref="C94:C100"/>
+    <mergeCell ref="D94:D100"/>
+    <mergeCell ref="E94:E100"/>
+    <mergeCell ref="F94:F100"/>
+    <mergeCell ref="G94:G100"/>
+    <mergeCell ref="H94:H100"/>
+    <mergeCell ref="I94:I100"/>
+    <mergeCell ref="J94:J100"/>
     <mergeCell ref="B106:B108"/>
     <mergeCell ref="C106:C108"/>
     <mergeCell ref="D106:D108"/>
@@ -7530,229 +7705,57 @@
     <mergeCell ref="L106:L108"/>
     <mergeCell ref="I101:I105"/>
     <mergeCell ref="J101:J105"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="C94:C100"/>
-    <mergeCell ref="D94:D100"/>
-    <mergeCell ref="E94:E100"/>
-    <mergeCell ref="F94:F100"/>
-    <mergeCell ref="G94:G100"/>
-    <mergeCell ref="H94:H100"/>
-    <mergeCell ref="I94:I100"/>
-    <mergeCell ref="J94:J100"/>
-    <mergeCell ref="K84:K87"/>
-    <mergeCell ref="L84:L87"/>
-    <mergeCell ref="N84:N87"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="D88:D93"/>
-    <mergeCell ref="E88:E93"/>
-    <mergeCell ref="F88:F93"/>
-    <mergeCell ref="N88:N93"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="H88:H93"/>
-    <mergeCell ref="I88:I93"/>
-    <mergeCell ref="J88:J93"/>
-    <mergeCell ref="K88:K93"/>
-    <mergeCell ref="L88:L93"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E84:E87"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="G84:G87"/>
-    <mergeCell ref="H84:H87"/>
-    <mergeCell ref="I84:I87"/>
-    <mergeCell ref="J84:J87"/>
-    <mergeCell ref="N75:N79"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="G80:G83"/>
-    <mergeCell ref="H80:H83"/>
-    <mergeCell ref="I80:I83"/>
-    <mergeCell ref="J80:J83"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="H75:H79"/>
-    <mergeCell ref="I75:I79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="K75:K79"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="D75:D79"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="K80:K83"/>
-    <mergeCell ref="L80:L83"/>
-    <mergeCell ref="N80:N83"/>
-    <mergeCell ref="H71:H74"/>
-    <mergeCell ref="I71:I74"/>
-    <mergeCell ref="J71:J74"/>
-    <mergeCell ref="K71:K74"/>
-    <mergeCell ref="L71:L74"/>
-    <mergeCell ref="N71:N74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="E71:E74"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="J67:J70"/>
-    <mergeCell ref="K67:K70"/>
-    <mergeCell ref="L67:L70"/>
-    <mergeCell ref="N67:N70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="H59:H63"/>
-    <mergeCell ref="I59:I63"/>
-    <mergeCell ref="J59:J63"/>
-    <mergeCell ref="K59:K63"/>
-    <mergeCell ref="L59:L63"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="J54:J58"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="D59:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="H48:H53"/>
-    <mergeCell ref="I48:I53"/>
-    <mergeCell ref="J48:J53"/>
-    <mergeCell ref="K48:K53"/>
-    <mergeCell ref="L48:L53"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="K43:K47"/>
-    <mergeCell ref="L43:L47"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="G48:G53"/>
-    <mergeCell ref="K39:K42"/>
-    <mergeCell ref="L39:L42"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="D43:D47"/>
-    <mergeCell ref="E43:E47"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="G39:G42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="I39:I42"/>
-    <mergeCell ref="J39:J42"/>
-    <mergeCell ref="K32:K38"/>
-    <mergeCell ref="L32:L38"/>
-    <mergeCell ref="B32:B38"/>
-    <mergeCell ref="C32:C38"/>
-    <mergeCell ref="D32:D38"/>
-    <mergeCell ref="E32:E38"/>
-    <mergeCell ref="F32:F38"/>
-    <mergeCell ref="G32:G38"/>
-    <mergeCell ref="H32:H38"/>
-    <mergeCell ref="I32:I38"/>
-    <mergeCell ref="J32:J38"/>
-    <mergeCell ref="L11:L16"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I24:I27"/>
-    <mergeCell ref="J24:J27"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="L24:L27"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="F24:F27"/>
-    <mergeCell ref="G24:G27"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="H28:H31"/>
-    <mergeCell ref="I28:I31"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="K28:K31"/>
-    <mergeCell ref="L28:L31"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="D17:D23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="E11:E16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="G11:G16"/>
-    <mergeCell ref="H11:H16"/>
-    <mergeCell ref="H17:H23"/>
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="K17:K23"/>
-    <mergeCell ref="L17:L23"/>
-    <mergeCell ref="I11:I16"/>
-    <mergeCell ref="J11:J16"/>
-    <mergeCell ref="K11:K16"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K101:K105"/>
+    <mergeCell ref="L101:L105"/>
+    <mergeCell ref="N101:N105"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="J110:J113"/>
+    <mergeCell ref="K110:K113"/>
+    <mergeCell ref="L110:L113"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="J114:J117"/>
+    <mergeCell ref="K114:K117"/>
+    <mergeCell ref="L114:L117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="H118:H120"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="J118:J120"/>
+    <mergeCell ref="K118:K120"/>
+    <mergeCell ref="L118:L120"/>
+    <mergeCell ref="N118:N120"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="E118:E120"/>
+    <mergeCell ref="F118:F120"/>
+    <mergeCell ref="G118:G120"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="I122:I125"/>
+    <mergeCell ref="J122:J125"/>
+    <mergeCell ref="K122:K125"/>
+    <mergeCell ref="L122:L125"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="G122:G125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8618,6 +8621,415 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="16.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="46.625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="30">
+      <c r="A1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>510</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>516</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5">
+      <c r="A12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G12" s="49" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.5">
+      <c r="A15" t="s">
+        <v>535</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>547</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>550</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="57">
+      <c r="A20" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>523</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>432</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>557</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062DA91B-8FB1-42E1-8F78-2FA3A3E1477E}">
   <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -9293,420 +9705,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="16.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="46.625" style="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" ht="30">
-      <c r="A1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>537</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>508</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>545</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>554</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>514</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>515</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>516</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.5">
-      <c r="A12" t="s">
-        <v>528</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>531</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>533</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.5">
-      <c r="A15" t="s">
-        <v>535</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>542</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>544</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>547</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>550</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="57">
-      <c r="A20" t="s">
-        <v>488</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>523</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>432</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>557</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F4E72C-2ACE-4813-A14A-59C7689800F0}">
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.25" style="89" customWidth="1"/>
+    <col min="1" max="1" width="35.25" style="50" customWidth="1"/>
     <col min="7" max="7" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="50" t="s">
         <v>559</v>
       </c>
     </row>
@@ -9725,7 +9734,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="50" t="s">
         <v>563</v>
       </c>
       <c r="B3">
@@ -9742,7 +9751,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="50" t="s">
         <v>566</v>
       </c>
       <c r="B4">
@@ -9756,7 +9765,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="50" t="s">
         <v>564</v>
       </c>
       <c r="B5" s="5">

--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1976A523-0F15-41D7-85CA-2150A432BFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A013A45-CA1C-4C34-BFF5-C1293A90118D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" tabRatio="783" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="609">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -858,15 +858,6 @@
   </si>
   <si>
     <t>OUT_EN_2</t>
-  </si>
-  <si>
-    <t>OUT_EN_3</t>
-  </si>
-  <si>
-    <t>OUT_EN_4</t>
-  </si>
-  <si>
-    <t>OUT_EN_5</t>
   </si>
   <si>
     <t>OUT_EN_6</t>
@@ -1671,9 +1662,6 @@
     <t>RX TX crossed - rewire</t>
   </si>
   <si>
-    <t>Not going to be re-layed out. Modify Rev A adaptors to use pinout as defined for other serial connections</t>
-  </si>
-  <si>
     <t>Blob links unnecessary</t>
   </si>
   <si>
@@ -1698,9 +1686,6 @@
     <t>Should read Direction and Magnitude</t>
   </si>
   <si>
-    <t>Can't do without redoing programming adaptor</t>
-  </si>
-  <si>
     <t>Fixed by Initial &amp; Date</t>
   </si>
   <si>
@@ -1750,12 +1735,6 @@
   </si>
   <si>
     <t>Add conformal coating mask layers to assembly drawings</t>
-  </si>
-  <si>
-    <t>Status LED brightness</t>
-  </si>
-  <si>
-    <t>Reduce brightness ??</t>
   </si>
   <si>
     <t>Current profile of ignitors</t>
@@ -1805,6 +1784,150 @@
   </si>
   <si>
     <t>ACB 1 Jan 2026</t>
+  </si>
+  <si>
+    <t>RGB LED</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Capacitance for firing</t>
+  </si>
+  <si>
+    <t>Firing current (A)</t>
+  </si>
+  <si>
+    <t>Firing Duration (mS)</t>
+  </si>
+  <si>
+    <t>Voltage dip (V)</t>
+  </si>
+  <si>
+    <t>Capacitance required (uF)</t>
+  </si>
+  <si>
+    <t>I=CdV/dt</t>
+  </si>
+  <si>
+    <t>C=Idt/dV</t>
+  </si>
+  <si>
+    <t>Capacitance required (F)</t>
+  </si>
+  <si>
+    <t>Not going to add that much capacitance - is better done by having secondary battery</t>
+  </si>
+  <si>
+    <t>uC bulk capacitance</t>
+  </si>
+  <si>
+    <t>uC current (A)</t>
+  </si>
+  <si>
+    <t>Capacitance needed to source O/P current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitance needed on 3V3 line to prevent uC brown out during firing </t>
+  </si>
+  <si>
+    <t>ACB 10 Jan 2026</t>
+  </si>
+  <si>
+    <t>As above</t>
+  </si>
+  <si>
+    <t>NOT GOING TO CHANGE NOW</t>
+  </si>
+  <si>
+    <t>Increase C4 to 100uF</t>
+  </si>
+  <si>
+    <t>Check Net Class directives on SCM</t>
+  </si>
+  <si>
+    <t>Concern about bulk capacitance</t>
+  </si>
+  <si>
+    <t>Had been corrupted. Needs to be re-entered</t>
+  </si>
+  <si>
+    <t>ACB 15 Dec 2026</t>
+  </si>
+  <si>
+    <t>Status LED too bright</t>
+  </si>
+  <si>
+    <t>Reduce current in all RGB LEDs</t>
+  </si>
+  <si>
+    <t>Sort BOM - new parts</t>
+  </si>
+  <si>
+    <t>CAN adaptor 9V I/P</t>
+  </si>
+  <si>
+    <t>Needs connector rather than test points</t>
+  </si>
+  <si>
+    <t>Add part solutions</t>
+  </si>
+  <si>
+    <t>2A for 4mS. FETs ok, but need to check battery voltage dip during firing. Would be alieviated by using both batteries on primary and secondary (ie 4 batteries)</t>
+  </si>
+  <si>
+    <t>CAMERA_ENABLE</t>
+  </si>
+  <si>
+    <t>ACB 11 Jan 2026</t>
+  </si>
+  <si>
+    <t>Ground box doesn't have ability to switch this</t>
+  </si>
+  <si>
+    <t>Easier to just add note on schematic to program Option Bits</t>
+  </si>
+  <si>
+    <t>Firing current limiting</t>
+  </si>
+  <si>
+    <t>Ignitor resistance (ohm)</t>
+  </si>
+  <si>
+    <t>Ignitor firing current (A)</t>
+  </si>
+  <si>
+    <t>Battery voltage (V)</t>
+  </si>
+  <si>
+    <t>Series R needed (ohm)</t>
+  </si>
+  <si>
+    <t>Total resistance needed</t>
+  </si>
+  <si>
+    <t>Resistance to add in series with ignitor</t>
+  </si>
+  <si>
+    <t>Total circuit resistance to draw ignitor current</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Add resistance to ignitor lead to reduce current surge from battery</t>
+  </si>
+  <si>
+    <t>ACB 19 Jan 2026</t>
+  </si>
+  <si>
+    <t>Dates</t>
+  </si>
+  <si>
+    <t>Silkscreen pin 1 dots</t>
   </si>
 </sst>
 </file>
@@ -1909,7 +2032,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1952,14 +2075,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2098,12 +2215,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2125,7 +2322,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2233,89 +2429,92 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2327,33 +2526,40 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3080,6 +3286,320 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
             <a:t>High repeatability</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{586C9989-4E2C-11D1-9E8A-4A5E6D691D02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6334125" y="10096500"/>
+          <a:ext cx="7620000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A762F30E-9B67-48D9-AAFB-0BD78758AC69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1885950" y="10277475"/>
+          <a:ext cx="4105275" cy="3371850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Vector PCB O/P voltage during firing of e-match using easymini flight computer</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1"/>
+            <a:t>Yellow</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t> = battery voltage drop 200mV/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>Purple = ignitor current 1A/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>Therefore seeing ~800mV drop during firing</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABA0DDB4-DEB2-1585-6E4C-50C281E0E303}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6334125" y="15240000"/>
+          <a:ext cx="7620000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1638300</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FFE106F-7E89-4A04-B6F4-07CF84FE4D50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1638300" y="15240000"/>
+          <a:ext cx="4105275" cy="3371850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t>Vector PCB 3V3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" baseline="0"/>
+            <a:t> regulator O/P</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800"/>
+            <a:t> voltage during firing of e-match using easymini</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" baseline="0"/>
+            <a:t> flight computer</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1"/>
+            <a:t>Yellow</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t> = battery voltage drop 100mV/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>Purple = ignitor current 1A/div</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1" baseline="0"/>
+            <a:t>Therefore seeing ~200mV drop during firing</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1800" b="1"/>
         </a:p>
@@ -3838,19 +4358,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>277</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="G1" s="43" t="s">
-        <v>280</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -3861,10 +4381,10 @@
         <v>19</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
@@ -3872,7 +4392,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D3" s="7">
         <v>3.7</v>
@@ -3881,21 +4401,21 @@
         <v>10</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="57">
       <c r="B4" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F4" s="7">
         <v>30</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3903,7 +4423,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3911,7 +4431,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3925,7 +4445,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3933,10 +4453,10 @@
         <v>17</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3944,18 +4464,18 @@
         <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F9" s="7">
         <v>3</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D10" s="7">
         <v>2</v>
@@ -3963,7 +4483,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D11" s="7">
         <v>2</v>
@@ -3971,7 +4491,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -3979,7 +4499,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -3990,32 +4510,32 @@
         <v>50</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D14" s="7">
         <v>10</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>333</v>
+        <v>293</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D15" s="7">
         <v>4000</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H15" s="45"/>
+        <v>278</v>
+      </c>
+      <c r="H15" s="44"/>
     </row>
     <row r="17" spans="2:9" ht="15">
       <c r="B17" s="2" t="s">
@@ -4024,16 +4544,16 @@
     </row>
     <row r="18" spans="2:9" ht="42.75">
       <c r="B18" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" t="s">
         <v>317</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I18" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="28.5">
@@ -4041,10 +4561,10 @@
         <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="28.5">
@@ -4052,10 +4572,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="28.5">
@@ -4063,10 +4583,10 @@
         <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -4081,206 +4601,206 @@
     </row>
     <row r="24" spans="2:9" ht="28.5">
       <c r="B24" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="28.5">
       <c r="B25" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="57">
       <c r="B26" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="28.5">
       <c r="B27" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="28.5">
       <c r="B28" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="28.5">
       <c r="B29" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="28.5">
       <c r="B30" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="71.25">
       <c r="B31" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="28.5">
       <c r="B32" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="28.5">
       <c r="B33" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="28.5">
       <c r="B35" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>274</v>
+        <v>349</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="28.5">
       <c r="B36" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="28.5">
       <c r="B37" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="28.5">
       <c r="B39" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15">
       <c r="B41" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="43" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="44" t="s">
+    <row r="44" spans="2:8">
+      <c r="B44" s="43" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="43" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="44" t="s">
+    <row r="46" spans="2:8">
+      <c r="B46" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="43" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="44" t="s">
-        <v>348</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="44" t="s">
-        <v>316</v>
-      </c>
-    </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="44"/>
+      <c r="B48" s="43"/>
     </row>
     <row r="49" spans="2:3">
-      <c r="B49" s="44"/>
+      <c r="B49" s="43"/>
     </row>
     <row r="50" spans="2:3">
-      <c r="B50" s="44"/>
+      <c r="B50" s="43"/>
     </row>
     <row r="51" spans="2:3">
-      <c r="B51" s="44"/>
+      <c r="B51" s="43"/>
     </row>
     <row r="52" spans="2:3" ht="15">
       <c r="B52" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="28.5">
@@ -4288,7 +4808,7 @@
         <v>26</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4299,101 +4819,388 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFAF250-9E30-4C8F-8A0D-6D92E94AA6E7}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:2" ht="15">
+      <c r="A1" s="49" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B1" s="50"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B2" s="52">
         <v>2</v>
       </c>
-      <c r="D3">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="52">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="51"/>
+      <c r="B5" s="53"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="54">
+        <f>(B3-B2)/(B4/1000)</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1">
+      <c r="A7" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="56">
+        <f>(B3-B2)*B4/1000</f>
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1"/>
+    <row r="9" spans="1:2" ht="15">
+      <c r="A9" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="50"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="52">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="52">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="53"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1">
+      <c r="A14" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="56">
+        <f>B12*B11/(B10+B11)</f>
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1"/>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>562</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>563</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="B18" s="59">
+        <v>2.1</v>
+      </c>
+      <c r="C18" s="59">
+        <v>3.1</v>
+      </c>
+      <c r="D18" s="52">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="59">
+        <v>3.3</v>
+      </c>
+      <c r="C19" s="59">
+        <v>3.3</v>
+      </c>
+      <c r="D19" s="52">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="59">
+        <v>5</v>
+      </c>
+      <c r="C20" s="59">
+        <v>5</v>
+      </c>
+      <c r="D20" s="52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="51"/>
+      <c r="D21" s="53"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="8">
+        <f>(B19-B18)/(B20/1000)</f>
+        <v>239.99999999999994</v>
+      </c>
+      <c r="C22" s="8">
+        <f>(C19-C18)/(C20/1000)</f>
+        <v>39.999999999999943</v>
+      </c>
+      <c r="D22" s="54">
+        <f>(D19-D18)/(D20/1000)</f>
+        <v>39.999999999999943</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1">
+      <c r="A23" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="60">
+        <f>(B19-B18)*B20/1000</f>
+        <v>5.9999999999999984E-3</v>
+      </c>
+      <c r="C23" s="60">
+        <f>(C19-C18)*C20/1000</f>
+        <v>9.9999999999999872E-4</v>
+      </c>
+      <c r="D23" s="56">
+        <f>(D19-D18)*D20/1000</f>
+        <v>9.9999999999999872E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1"/>
+    <row r="25" spans="1:5" ht="15">
+      <c r="A25" s="49" t="s">
+        <v>564</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="D25" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="51" t="s">
+        <v>565</v>
+      </c>
+      <c r="B26" s="52">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="9">
-        <v>7.4</v>
-      </c>
-      <c r="D4">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="8">
-        <f>(B4-B3)/(B5/1000)</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="8">
-        <f>(B4-B3)*B5/1000</f>
-        <v>5.3999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="9">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="8">
-        <f>B14*B13/(B12+B13)</f>
-        <v>1.85</v>
+    <row r="27" spans="1:5">
+      <c r="A27" s="51" t="s">
+        <v>566</v>
+      </c>
+      <c r="B27" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="51" t="s">
+        <v>567</v>
+      </c>
+      <c r="B28" s="52">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="51"/>
+      <c r="B29" s="53"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="51" t="s">
+        <v>571</v>
+      </c>
+      <c r="B30" s="54">
+        <f>B26*B27*0.001/B28</f>
+        <v>0.08</v>
+      </c>
+      <c r="D30" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1">
+      <c r="A31" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="B31" s="100">
+        <f>B30*1000000</f>
+        <v>80000</v>
+      </c>
+      <c r="D31" t="s">
+        <v>569</v>
+      </c>
+      <c r="E31" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1"/>
+    <row r="33" spans="1:4" ht="15">
+      <c r="A33" s="49" t="s">
+        <v>573</v>
+      </c>
+      <c r="B33" s="50"/>
+      <c r="D33" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="51" t="s">
+        <v>574</v>
+      </c>
+      <c r="B34" s="52">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="51" t="s">
+        <v>566</v>
+      </c>
+      <c r="B35" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="51" t="s">
+        <v>567</v>
+      </c>
+      <c r="B36" s="52">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="51"/>
+      <c r="B37" s="53"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="51" t="s">
+        <v>571</v>
+      </c>
+      <c r="B38" s="54">
+        <f>B34*B35*0.001/B36</f>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" thickBot="1">
+      <c r="A39" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="B39" s="56">
+        <f>B38*1000000</f>
+        <v>2000</v>
+      </c>
+      <c r="D39" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" thickBot="1"/>
+    <row r="42" spans="1:4" ht="15">
+      <c r="A42" s="49" t="s">
+        <v>596</v>
+      </c>
+      <c r="B42" s="50"/>
+      <c r="D42" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="51" t="s">
+        <v>597</v>
+      </c>
+      <c r="B43" s="52">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="B44" s="52">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="51" t="s">
+        <v>599</v>
+      </c>
+      <c r="B45" s="52">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="51" t="s">
+        <v>601</v>
+      </c>
+      <c r="B46" s="54">
+        <f>B45/B44</f>
+        <v>9.25</v>
+      </c>
+      <c r="D46" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" thickBot="1">
+      <c r="A47" s="55" t="s">
+        <v>600</v>
+      </c>
+      <c r="B47" s="56">
+        <f>B46-B43</f>
+        <v>7.65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="50" spans="11:11">
+      <c r="K50" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -4406,68 +5213,68 @@
   <dimension ref="B2:S127"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="6" max="6" width="9" style="30"/>
+    <col min="6" max="6" width="9" style="29"/>
     <col min="16" max="16" width="14.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="15" thickBot="1"/>
     <row r="3" spans="2:16" ht="15" thickBot="1">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="88" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="84" t="s">
+      <c r="J3" s="79" t="s">
         <v>232</v>
       </c>
-      <c r="K3" s="84" t="s">
+      <c r="K3" s="79" t="s">
         <v>233</v>
       </c>
-      <c r="L3" s="86" t="s">
+      <c r="L3" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="81" t="s">
+      <c r="M3" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="83"/>
+      <c r="N3" s="64"/>
     </row>
     <row r="4" spans="2:16" ht="96.75" customHeight="1" thickBot="1">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="89"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="11" t="s">
+      <c r="I4" s="70"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -4475,546 +5282,546 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15" thickTop="1">
-      <c r="B5" s="67">
+      <c r="B5" s="65">
         <v>2</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="65">
         <v>1</v>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="65">
         <v>2</v>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="65">
         <v>2</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="67">
         <v>2</v>
       </c>
-      <c r="G5" s="67">
+      <c r="G5" s="65">
         <v>2</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="K5" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="66" t="s">
+      <c r="L5" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="71" t="s">
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="15" thickBot="1">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="15" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="54">
+      <c r="B7" s="75">
         <v>3</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="75">
         <v>2</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="75">
         <v>3</v>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="75">
         <v>3</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="76">
         <v>3</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="75">
         <v>3</v>
       </c>
-      <c r="H7" s="60" t="s">
+      <c r="H7" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="54" t="s">
+      <c r="J7" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="51" t="s">
+      <c r="L7" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="83" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="16" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1">
-      <c r="B9" s="17">
+      <c r="B9" s="16">
         <v>4</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>3</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>4</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>4</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="31">
         <v>4</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <v>4</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="19">
         <v>-2</v>
       </c>
-      <c r="M9" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N9" s="19" t="s">
+      <c r="M9" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N9" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1">
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>10</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>4</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>5</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>5</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>5</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <v>5</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K10" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="20" t="s">
+      <c r="K10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="M10" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N10" s="19" t="s">
+      <c r="M10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="24">
-      <c r="B11" s="54">
+      <c r="B11" s="75">
         <v>5</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="75">
         <v>5</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="75">
         <v>6</v>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="75">
         <v>6</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="76">
         <v>6</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="75">
         <v>6</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="78" t="s">
+      <c r="I11" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="54" t="s">
+      <c r="J11" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="60" t="s">
+      <c r="K11" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="29" t="s">
+      <c r="L11" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="13" t="s">
         <v>109</v>
       </c>
       <c r="P11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="24">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="14" t="s">
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="N12" s="29" t="s">
+      <c r="N12" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="24">
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="14" t="s">
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="36">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="14" t="s">
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="N14" s="14" t="s">
+      <c r="N14" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="24">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="29" t="s">
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="21" t="s">
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="N16" s="18"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="2:16" ht="24">
-      <c r="B17" s="54">
+      <c r="B17" s="75">
         <v>6</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="75">
         <v>6</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="75">
         <v>7</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="75">
         <v>7</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="76">
         <v>7</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="75">
         <v>7</v>
       </c>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="54" t="s">
+      <c r="J17" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="54" t="s">
+      <c r="K17" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="23" t="s">
+      <c r="L17" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="N17" s="24" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="24">
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="23" t="s">
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="N18" s="35" t="s">
+      <c r="N18" s="34" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="14" t="s">
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="N19" s="26"/>
+      <c r="N19" s="25"/>
     </row>
     <row r="20" spans="2:16" ht="24">
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="23" t="s">
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="N20" s="26"/>
+      <c r="N20" s="25"/>
     </row>
     <row r="21" spans="2:16" ht="24">
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="13" t="s">
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="N21" s="26"/>
+      <c r="N21" s="25"/>
     </row>
     <row r="22" spans="2:16" ht="24">
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="14" t="s">
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="N22" s="26"/>
+      <c r="N22" s="25"/>
     </row>
     <row r="23" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="40" t="s">
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="N23" s="24"/>
+      <c r="N23" s="23"/>
     </row>
     <row r="24" spans="2:16" ht="36">
-      <c r="B24" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="54">
+      <c r="B24" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="75">
         <v>8</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="75">
         <v>8</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="76">
         <v>8</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="75">
         <v>8</v>
       </c>
-      <c r="H24" s="60" t="s">
+      <c r="H24" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="J24" s="54" t="s">
+      <c r="J24" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="60" t="s">
+      <c r="K24" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="L24" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" s="14" t="s">
+      <c r="L24" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="N24" s="14" t="s">
+      <c r="N24" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="24">
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="29" t="s">
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="N25" s="38" t="s">
+      <c r="N25" s="37" t="s">
         <v>129</v>
       </c>
       <c r="P25" t="s">
@@ -5022,213 +5829,213 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="24">
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="14" t="s">
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="N26" s="12" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="19" t="s">
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="N27" s="18" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="24">
-      <c r="B28" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="54">
+      <c r="B28" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="75">
         <v>9</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="75">
         <v>9</v>
       </c>
-      <c r="F28" s="63">
+      <c r="F28" s="76">
         <v>9</v>
       </c>
-      <c r="G28" s="54">
+      <c r="G28" s="75">
         <v>9</v>
       </c>
-      <c r="H28" s="60" t="s">
+      <c r="H28" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="54" t="s">
+      <c r="J28" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K28" s="54" t="s">
+      <c r="K28" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L28" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M28" s="14" t="s">
+      <c r="L28" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M28" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="N28" s="25" t="s">
+      <c r="N28" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="14" t="s">
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="N29" s="35" t="s">
+      <c r="N29" s="34" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="24">
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="29" t="s">
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="N30" s="26"/>
+      <c r="N30" s="25"/>
     </row>
     <row r="31" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="40" t="s">
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="N31" s="24"/>
+      <c r="N31" s="23"/>
     </row>
     <row r="32" spans="2:16" ht="24">
-      <c r="B32" s="54">
+      <c r="B32" s="75">
         <v>7</v>
       </c>
-      <c r="C32" s="54">
+      <c r="C32" s="75">
         <v>7</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="75">
         <v>10</v>
       </c>
-      <c r="E32" s="54">
+      <c r="E32" s="75">
         <v>10</v>
       </c>
-      <c r="F32" s="63">
+      <c r="F32" s="76">
         <v>10</v>
       </c>
-      <c r="G32" s="54">
+      <c r="G32" s="75">
         <v>10</v>
       </c>
-      <c r="H32" s="60" t="s">
+      <c r="H32" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="83" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="54" t="s">
+      <c r="J32" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="60" t="s">
+      <c r="K32" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="L32" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M32" s="14" t="s">
+      <c r="L32" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="N32" s="14" t="s">
+      <c r="N32" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="24">
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="14" t="s">
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="36">
-      <c r="B34" s="55"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="55"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="14" t="s">
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
+      <c r="M34" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="N34" s="38" t="s">
+      <c r="N34" s="37" t="s">
         <v>143</v>
       </c>
       <c r="P34" t="s">
@@ -5236,149 +6043,149 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="24">
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="23" t="s">
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="N35" s="22"/>
+      <c r="N35" s="21"/>
     </row>
     <row r="36" spans="2:16">
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="14" t="s">
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="85"/>
+      <c r="M36" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="N36" s="22"/>
+      <c r="N36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="24">
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="37" t="s">
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="N37" s="22"/>
+      <c r="N37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="21" t="s">
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="74"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="N38" s="18"/>
+      <c r="N38" s="17"/>
     </row>
     <row r="39" spans="2:16" ht="24.75" thickTop="1">
-      <c r="B39" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="67">
+      <c r="B39" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="65">
         <v>8</v>
       </c>
-      <c r="D39" s="67">
+      <c r="D39" s="65">
         <v>11</v>
       </c>
-      <c r="E39" s="67">
+      <c r="E39" s="65">
         <v>11</v>
       </c>
-      <c r="F39" s="68">
+      <c r="F39" s="67">
         <v>11</v>
       </c>
-      <c r="G39" s="67">
+      <c r="G39" s="65">
         <v>11</v>
       </c>
-      <c r="H39" s="76" t="s">
+      <c r="H39" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="66" t="s">
+      <c r="I39" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="J39" s="67" t="s">
+      <c r="J39" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="76" t="s">
+      <c r="K39" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="M39" s="14" t="s">
+      <c r="L39" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N39" s="14" t="s">
+      <c r="N39" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="24">
-      <c r="B40" s="52"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="14" t="s">
+      <c r="B40" s="85"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="N40" s="14" t="s">
+      <c r="N40" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="41" spans="2:16">
-      <c r="B41" s="52"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="14" t="s">
+      <c r="B41" s="85"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="N41" s="38" t="s">
+      <c r="N41" s="37" t="s">
         <v>148</v>
       </c>
       <c r="P41" t="s">
@@ -5386,303 +6193,303 @@
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1">
-      <c r="B42" s="53"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="19" t="s">
+      <c r="B42" s="72"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="66"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="N42" s="18"/>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" spans="2:16">
-      <c r="B43" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="54">
+      <c r="B43" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="75">
         <v>9</v>
       </c>
-      <c r="D43" s="54">
+      <c r="D43" s="75">
         <v>12</v>
       </c>
-      <c r="E43" s="54">
+      <c r="E43" s="75">
         <v>12</v>
       </c>
-      <c r="F43" s="63">
+      <c r="F43" s="76">
         <v>12</v>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="75">
         <v>12</v>
       </c>
-      <c r="H43" s="60" t="s">
+      <c r="H43" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="I43" s="51" t="s">
+      <c r="I43" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="J43" s="54" t="s">
+      <c r="J43" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K43" s="54" t="s">
+      <c r="K43" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L43" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M43" s="14" t="s">
+      <c r="L43" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="N43" s="75" t="s">
+      <c r="N43" s="89" t="s">
         <v>154</v>
       </c>
       <c r="P43" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="2:16" ht="24">
-      <c r="B44" s="52"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="55"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="14" t="s">
+      <c r="B44" s="85"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="82"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="85"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="85"/>
+      <c r="M44" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="N44" s="70"/>
+      <c r="N44" s="90"/>
     </row>
     <row r="45" spans="2:16" ht="24">
-      <c r="B45" s="52"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="14" t="s">
+      <c r="B45" s="85"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="85"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="85"/>
+      <c r="M45" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="70"/>
+      <c r="N45" s="90"/>
     </row>
     <row r="46" spans="2:16" ht="24">
-      <c r="B46" s="52"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="55"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="14" t="s">
+      <c r="B46" s="85"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="85"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="85"/>
+      <c r="M46" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N46" s="70"/>
+      <c r="N46" s="90"/>
     </row>
     <row r="47" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B47" s="53"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="19" t="s">
+      <c r="B47" s="72"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="72"/>
+      <c r="M47" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="N47" s="71"/>
+      <c r="N47" s="91"/>
     </row>
     <row r="48" spans="2:16" ht="14.25" customHeight="1">
-      <c r="B48" s="54">
+      <c r="B48" s="75">
         <v>8</v>
       </c>
-      <c r="C48" s="54">
+      <c r="C48" s="75">
         <v>10</v>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="75">
         <v>13</v>
       </c>
-      <c r="E48" s="54">
+      <c r="E48" s="75">
         <v>13</v>
       </c>
-      <c r="F48" s="63">
+      <c r="F48" s="76">
         <v>13</v>
       </c>
-      <c r="G48" s="54">
+      <c r="G48" s="75">
         <v>13</v>
       </c>
-      <c r="H48" s="60" t="s">
+      <c r="H48" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="51" t="s">
+      <c r="I48" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="54" t="s">
+      <c r="J48" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="54" t="s">
+      <c r="K48" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L48" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M48" s="14" t="s">
+      <c r="L48" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M48" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="N48" s="51" t="s">
+      <c r="N48" s="83" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="24">
-      <c r="B49" s="55"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="14" t="s">
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="85"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="85"/>
+      <c r="M49" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="N49" s="52"/>
+      <c r="N49" s="85"/>
     </row>
     <row r="50" spans="2:16" ht="24">
-      <c r="B50" s="55"/>
-      <c r="C50" s="55"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="55"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="55"/>
-      <c r="L50" s="52"/>
-      <c r="M50" s="14" t="s">
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="85"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="85"/>
+      <c r="M50" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="N50" s="41" t="s">
+      <c r="N50" s="40" t="s">
         <v>242</v>
       </c>
       <c r="P50" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="24">
-      <c r="B51" s="55"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="55"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="55"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="55"/>
-      <c r="K51" s="55"/>
-      <c r="L51" s="52"/>
-      <c r="M51" s="14" t="s">
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="85"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="85"/>
+      <c r="M51" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="N51" s="26"/>
+      <c r="N51" s="25"/>
     </row>
     <row r="52" spans="2:16" ht="24">
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="64"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="14" t="s">
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="85"/>
+      <c r="M52" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N52" s="26"/>
+      <c r="N52" s="25"/>
     </row>
     <row r="53" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="62"/>
-      <c r="I53" s="53"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="21" t="s">
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="66"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="72"/>
+      <c r="J53" s="66"/>
+      <c r="K53" s="66"/>
+      <c r="L53" s="72"/>
+      <c r="M53" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="N53" s="24"/>
+      <c r="N53" s="23"/>
     </row>
     <row r="54" spans="2:16" ht="24">
-      <c r="B54" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="54">
+      <c r="B54" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="75">
         <v>14</v>
       </c>
-      <c r="F54" s="63">
+      <c r="F54" s="76">
         <v>14</v>
       </c>
-      <c r="G54" s="54">
+      <c r="G54" s="75">
         <v>14</v>
       </c>
-      <c r="H54" s="60" t="s">
+      <c r="H54" s="77" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="75" t="s">
+      <c r="I54" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="J54" s="54" t="s">
+      <c r="J54" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="54" t="s">
+      <c r="K54" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M54" s="14" t="s">
+      <c r="L54" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M54" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N54" s="29" t="s">
+      <c r="N54" s="28" t="s">
         <v>163</v>
       </c>
       <c r="P54" t="s">
@@ -5690,113 +6497,113 @@
       </c>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="55"/>
-      <c r="K55" s="55"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="14" t="s">
+      <c r="B55" s="85"/>
+      <c r="C55" s="85"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="85"/>
+      <c r="M55" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="N55" s="14" t="s">
+      <c r="N55" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="56" spans="2:16">
-      <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="55"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="55"/>
-      <c r="K56" s="55"/>
-      <c r="L56" s="52"/>
-      <c r="M56" s="14" t="s">
+      <c r="B56" s="85"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="84"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="85"/>
+      <c r="M56" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="N56" s="22"/>
+      <c r="N56" s="21"/>
     </row>
     <row r="57" spans="2:16" ht="24">
-      <c r="B57" s="52"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="E57" s="55"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="55"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="55"/>
-      <c r="K57" s="55"/>
-      <c r="L57" s="52"/>
-      <c r="M57" s="13" t="s">
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="84"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="85"/>
+      <c r="M57" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="N57" s="22"/>
+      <c r="N57" s="21"/>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1">
-      <c r="B58" s="53"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="62"/>
-      <c r="I58" s="71"/>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
-      <c r="L58" s="53"/>
-      <c r="M58" s="19" t="s">
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="66"/>
+      <c r="K58" s="66"/>
+      <c r="L58" s="72"/>
+      <c r="M58" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="N58" s="18"/>
+      <c r="N58" s="17"/>
     </row>
     <row r="59" spans="2:16" ht="24">
-      <c r="B59" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="54">
+      <c r="B59" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="75">
         <v>11</v>
       </c>
-      <c r="D59" s="54">
+      <c r="D59" s="75">
         <v>14</v>
       </c>
-      <c r="E59" s="54">
+      <c r="E59" s="75">
         <v>15</v>
       </c>
-      <c r="F59" s="63">
+      <c r="F59" s="76">
         <v>15</v>
       </c>
-      <c r="G59" s="54">
+      <c r="G59" s="75">
         <v>15</v>
       </c>
-      <c r="H59" s="60" t="s">
+      <c r="H59" s="77" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="75" t="s">
+      <c r="I59" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="54" t="s">
+      <c r="J59" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K59" s="54" t="s">
+      <c r="K59" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L59" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M59" s="14" t="s">
+      <c r="L59" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M59" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="N59" s="29" t="s">
+      <c r="N59" s="28" t="s">
         <v>169</v>
       </c>
       <c r="P59" t="s">
@@ -5804,1686 +6611,1902 @@
       </c>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" s="52"/>
-      <c r="C60" s="55"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="55"/>
-      <c r="K60" s="55"/>
-      <c r="L60" s="52"/>
-      <c r="M60" s="14" t="s">
+      <c r="B60" s="85"/>
+      <c r="C60" s="81"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="84"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="81"/>
+      <c r="L60" s="85"/>
+      <c r="M60" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="N60" s="14" t="s">
+      <c r="N60" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="24">
-      <c r="B61" s="52"/>
-      <c r="C61" s="55"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="64"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="70"/>
-      <c r="J61" s="55"/>
-      <c r="K61" s="55"/>
-      <c r="L61" s="52"/>
-      <c r="M61" s="14" t="s">
+      <c r="B61" s="85"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="82"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="84"/>
+      <c r="I61" s="90"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="85"/>
+      <c r="M61" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="N61" s="22"/>
+      <c r="N61" s="21"/>
     </row>
     <row r="62" spans="2:16" ht="24">
-      <c r="B62" s="52"/>
-      <c r="C62" s="55"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="64"/>
-      <c r="G62" s="55"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="70"/>
-      <c r="J62" s="55"/>
-      <c r="K62" s="55"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="13" t="s">
+      <c r="B62" s="85"/>
+      <c r="C62" s="81"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="81"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="81"/>
+      <c r="H62" s="84"/>
+      <c r="I62" s="90"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="81"/>
+      <c r="L62" s="85"/>
+      <c r="M62" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="N62" s="22"/>
+      <c r="N62" s="21"/>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1">
-      <c r="B63" s="53"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="62"/>
-      <c r="I63" s="71"/>
-      <c r="J63" s="56"/>
-      <c r="K63" s="56"/>
-      <c r="L63" s="53"/>
-      <c r="M63" s="19" t="s">
+      <c r="B63" s="72"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="66"/>
+      <c r="E63" s="66"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="74"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="66"/>
+      <c r="K63" s="66"/>
+      <c r="L63" s="72"/>
+      <c r="M63" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="N63" s="18"/>
+      <c r="N63" s="17"/>
     </row>
     <row r="64" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B64" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F64" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G64" s="15">
+      <c r="B64" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G64" s="14">
         <v>16</v>
       </c>
-      <c r="H64" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I64" s="19" t="s">
+      <c r="H64" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I64" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="J64" s="15" t="s">
+      <c r="J64" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L64" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M64" s="19" t="s">
+      <c r="L64" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="M64" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="N64" s="19" t="s">
+      <c r="N64" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="65" spans="2:16" ht="15" thickBot="1">
-      <c r="B65" s="17">
+      <c r="B65" s="16">
         <v>9</v>
       </c>
-      <c r="C65" s="15">
+      <c r="C65" s="14">
         <v>12</v>
       </c>
-      <c r="D65" s="15">
+      <c r="D65" s="14">
         <v>15</v>
       </c>
-      <c r="E65" s="15">
+      <c r="E65" s="14">
         <v>16</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="31">
         <v>16</v>
       </c>
-      <c r="G65" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H65" s="16" t="s">
+      <c r="G65" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H65" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="I65" s="19" t="s">
+      <c r="I65" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K65" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L65" s="20">
+      <c r="K65" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L65" s="19">
         <v>-5</v>
       </c>
-      <c r="M65" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N65" s="19" t="s">
+      <c r="M65" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N65" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="66" spans="2:16" ht="15" thickBot="1">
-      <c r="B66" s="17">
+      <c r="B66" s="16">
         <v>10</v>
       </c>
-      <c r="C66" s="15">
+      <c r="C66" s="14">
         <v>13</v>
       </c>
-      <c r="D66" s="15">
+      <c r="D66" s="14">
         <v>16</v>
       </c>
-      <c r="E66" s="15">
+      <c r="E66" s="14">
         <v>17</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="31">
         <v>17</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="14">
         <v>17</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="I66" s="19" t="s">
+      <c r="I66" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K66" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L66" s="20">
+      <c r="K66" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L66" s="19">
         <v>-6</v>
       </c>
-      <c r="M66" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N66" s="19" t="s">
+      <c r="M66" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N66" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:16" ht="36">
-      <c r="B67" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="54">
+      <c r="B67" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" s="75">
         <v>18</v>
       </c>
-      <c r="F67" s="63">
+      <c r="F67" s="76">
         <v>18</v>
       </c>
-      <c r="G67" s="54">
+      <c r="G67" s="75">
         <v>18</v>
       </c>
-      <c r="H67" s="60" t="s">
+      <c r="H67" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="I67" s="75" t="s">
+      <c r="I67" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="54" t="s">
+      <c r="J67" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="54" t="s">
+      <c r="K67" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M67" s="13" t="s">
+      <c r="L67" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M67" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="N67" s="51" t="s">
+      <c r="N67" s="83" t="s">
         <v>88</v>
       </c>
       <c r="P67" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="2:16" ht="24">
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="64"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="70"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="55"/>
-      <c r="L68" s="52"/>
-      <c r="M68" s="14" t="s">
+      <c r="B68" s="85"/>
+      <c r="C68" s="85"/>
+      <c r="D68" s="85"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="84"/>
+      <c r="I68" s="90"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="81"/>
+      <c r="L68" s="85"/>
+      <c r="M68" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N68" s="52"/>
+      <c r="N68" s="85"/>
     </row>
     <row r="69" spans="2:16" ht="24">
-      <c r="B69" s="52"/>
-      <c r="C69" s="52"/>
-      <c r="D69" s="52"/>
-      <c r="E69" s="55"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="55"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="70"/>
-      <c r="J69" s="55"/>
-      <c r="K69" s="55"/>
-      <c r="L69" s="52"/>
-      <c r="M69" s="14" t="s">
+      <c r="B69" s="85"/>
+      <c r="C69" s="85"/>
+      <c r="D69" s="85"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="81"/>
+      <c r="H69" s="84"/>
+      <c r="I69" s="90"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="81"/>
+      <c r="L69" s="85"/>
+      <c r="M69" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="52"/>
+      <c r="N69" s="85"/>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1">
-      <c r="B70" s="53"/>
-      <c r="C70" s="53"/>
-      <c r="D70" s="53"/>
-      <c r="E70" s="56"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="56"/>
-      <c r="H70" s="62"/>
-      <c r="I70" s="71"/>
-      <c r="J70" s="56"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="53"/>
-      <c r="M70" s="19" t="s">
+      <c r="B70" s="72"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="91"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="72"/>
+      <c r="M70" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="N70" s="53"/>
+      <c r="N70" s="72"/>
     </row>
     <row r="71" spans="2:16" ht="24">
-      <c r="B71" s="54">
+      <c r="B71" s="75">
         <v>11</v>
       </c>
-      <c r="C71" s="54">
+      <c r="C71" s="75">
         <v>14</v>
       </c>
-      <c r="D71" s="54">
+      <c r="D71" s="75">
         <v>17</v>
       </c>
-      <c r="E71" s="54">
+      <c r="E71" s="75">
         <v>19</v>
       </c>
-      <c r="F71" s="63">
+      <c r="F71" s="76">
         <v>19</v>
       </c>
-      <c r="G71" s="54">
+      <c r="G71" s="75">
         <v>19</v>
       </c>
-      <c r="H71" s="60" t="s">
+      <c r="H71" s="77" t="s">
         <v>179</v>
       </c>
-      <c r="I71" s="51" t="s">
+      <c r="I71" s="83" t="s">
         <v>180</v>
       </c>
-      <c r="J71" s="54" t="s">
+      <c r="J71" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K71" s="54" t="s">
+      <c r="K71" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="L71" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M71" s="12" t="s">
+      <c r="L71" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M71" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="N71" s="51" t="s">
+      <c r="N71" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="24">
-      <c r="B72" s="55"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="55"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="L72" s="52"/>
-      <c r="M72" s="14" t="s">
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="82"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="84"/>
+      <c r="I72" s="85"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="85"/>
+      <c r="M72" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="N72" s="52"/>
+      <c r="N72" s="85"/>
     </row>
     <row r="73" spans="2:16" ht="24">
-      <c r="B73" s="55"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="55"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="52"/>
-      <c r="J73" s="55"/>
-      <c r="K73" s="55"/>
-      <c r="L73" s="52"/>
-      <c r="M73" s="38" t="s">
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="81"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="84"/>
+      <c r="I73" s="85"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="85"/>
+      <c r="M73" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="N73" s="52"/>
+      <c r="N73" s="85"/>
     </row>
     <row r="74" spans="2:16" ht="48.75" thickBot="1">
-      <c r="B74" s="56"/>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-      <c r="F74" s="65"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="62"/>
-      <c r="I74" s="53"/>
-      <c r="J74" s="56"/>
-      <c r="K74" s="56"/>
-      <c r="L74" s="53"/>
-      <c r="M74" s="19" t="s">
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="66"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="66"/>
+      <c r="H74" s="74"/>
+      <c r="I74" s="72"/>
+      <c r="J74" s="66"/>
+      <c r="K74" s="66"/>
+      <c r="L74" s="72"/>
+      <c r="M74" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="N74" s="53"/>
+      <c r="N74" s="72"/>
     </row>
     <row r="75" spans="2:16" ht="36.75" thickTop="1">
-      <c r="B75" s="67">
+      <c r="B75" s="65">
         <v>12</v>
       </c>
-      <c r="C75" s="67">
+      <c r="C75" s="65">
         <v>15</v>
       </c>
-      <c r="D75" s="67">
+      <c r="D75" s="65">
         <v>18</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="65">
         <v>20</v>
       </c>
-      <c r="F75" s="68">
+      <c r="F75" s="67">
         <v>20</v>
       </c>
-      <c r="G75" s="67">
+      <c r="G75" s="65">
         <v>20</v>
       </c>
-      <c r="H75" s="76" t="s">
+      <c r="H75" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="I75" s="66" t="s">
+      <c r="I75" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="J75" s="67" t="s">
+      <c r="J75" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="67" t="s">
+      <c r="K75" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="L75" s="77">
+      <c r="L75" s="92">
         <v>-7</v>
       </c>
-      <c r="M75" s="14" t="s">
+      <c r="M75" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="N75" s="66" t="s">
+      <c r="N75" s="71" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="24">
-      <c r="B76" s="55"/>
-      <c r="C76" s="55"/>
-      <c r="D76" s="55"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="55"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="52"/>
-      <c r="J76" s="55"/>
-      <c r="K76" s="55"/>
-      <c r="L76" s="73"/>
-      <c r="M76" s="14" t="s">
+      <c r="B76" s="81"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="81"/>
+      <c r="E76" s="81"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="84"/>
+      <c r="I76" s="85"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="81"/>
+      <c r="L76" s="93"/>
+      <c r="M76" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="52"/>
+      <c r="N76" s="85"/>
     </row>
     <row r="77" spans="2:16" ht="24">
-      <c r="B77" s="55"/>
-      <c r="C77" s="55"/>
-      <c r="D77" s="55"/>
-      <c r="E77" s="55"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="55"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="55"/>
-      <c r="K77" s="55"/>
-      <c r="L77" s="73"/>
-      <c r="M77" s="38" t="s">
+      <c r="B77" s="81"/>
+      <c r="C77" s="81"/>
+      <c r="D77" s="81"/>
+      <c r="E77" s="81"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="81"/>
+      <c r="H77" s="84"/>
+      <c r="I77" s="85"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="81"/>
+      <c r="L77" s="93"/>
+      <c r="M77" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="N77" s="52"/>
+      <c r="N77" s="85"/>
     </row>
     <row r="78" spans="2:16">
-      <c r="B78" s="55"/>
-      <c r="C78" s="55"/>
-      <c r="D78" s="55"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="55"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="52"/>
-      <c r="J78" s="55"/>
-      <c r="K78" s="55"/>
-      <c r="L78" s="73"/>
-      <c r="M78" s="14" t="s">
+      <c r="B78" s="81"/>
+      <c r="C78" s="81"/>
+      <c r="D78" s="81"/>
+      <c r="E78" s="81"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="81"/>
+      <c r="H78" s="84"/>
+      <c r="I78" s="85"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="81"/>
+      <c r="L78" s="93"/>
+      <c r="M78" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="N78" s="52"/>
+      <c r="N78" s="85"/>
     </row>
     <row r="79" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B79" s="56"/>
-      <c r="C79" s="56"/>
-      <c r="D79" s="56"/>
-      <c r="E79" s="56"/>
-      <c r="F79" s="65"/>
-      <c r="G79" s="56"/>
-      <c r="H79" s="62"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="56"/>
-      <c r="K79" s="56"/>
-      <c r="L79" s="74"/>
-      <c r="M79" s="19" t="s">
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="68"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="74"/>
+      <c r="I79" s="72"/>
+      <c r="J79" s="66"/>
+      <c r="K79" s="66"/>
+      <c r="L79" s="94"/>
+      <c r="M79" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="N79" s="53"/>
+      <c r="N79" s="72"/>
     </row>
     <row r="80" spans="2:16">
-      <c r="B80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="F80" s="63">
+      <c r="B80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="76">
         <v>21</v>
       </c>
-      <c r="G80" s="54">
+      <c r="G80" s="75">
         <v>21</v>
       </c>
-      <c r="H80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80" s="51" t="s">
+      <c r="H80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="83" t="s">
         <v>189</v>
       </c>
-      <c r="J80" s="54" t="s">
+      <c r="J80" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K80" s="54" t="s">
+      <c r="K80" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L80" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M80" s="14" t="s">
+      <c r="L80" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M80" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="N80" s="51" t="s">
+      <c r="N80" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:19" ht="48">
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="55"/>
-      <c r="H81" s="52"/>
-      <c r="I81" s="52"/>
-      <c r="J81" s="55"/>
-      <c r="K81" s="55"/>
-      <c r="L81" s="52"/>
-      <c r="M81" s="14" t="s">
+      <c r="B81" s="85"/>
+      <c r="C81" s="85"/>
+      <c r="D81" s="85"/>
+      <c r="E81" s="85"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="85"/>
+      <c r="I81" s="85"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="81"/>
+      <c r="L81" s="85"/>
+      <c r="M81" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="N81" s="52"/>
+      <c r="N81" s="85"/>
     </row>
     <row r="82" spans="2:19" ht="24">
-      <c r="B82" s="52"/>
-      <c r="C82" s="52"/>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="55"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="55"/>
-      <c r="K82" s="55"/>
-      <c r="L82" s="52"/>
-      <c r="M82" s="14" t="s">
+      <c r="B82" s="85"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
+      <c r="E82" s="85"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="85"/>
+      <c r="I82" s="85"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="81"/>
+      <c r="L82" s="85"/>
+      <c r="M82" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="N82" s="52"/>
+      <c r="N82" s="85"/>
     </row>
     <row r="83" spans="2:19" ht="48.75" thickBot="1">
-      <c r="B83" s="53"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="53"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="56"/>
-      <c r="H83" s="53"/>
-      <c r="I83" s="53"/>
-      <c r="J83" s="56"/>
-      <c r="K83" s="56"/>
-      <c r="L83" s="53"/>
-      <c r="M83" s="19" t="s">
+      <c r="B83" s="72"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="66"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="66"/>
+      <c r="K83" s="66"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="N83" s="53"/>
+      <c r="N83" s="72"/>
     </row>
     <row r="84" spans="2:19">
-      <c r="B84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="63">
+      <c r="B84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="76">
         <v>22</v>
       </c>
-      <c r="G84" s="54">
+      <c r="G84" s="75">
         <v>22</v>
       </c>
-      <c r="H84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84" s="51" t="s">
+      <c r="H84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="J84" s="54" t="s">
+      <c r="J84" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="54" t="s">
+      <c r="K84" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L84" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M84" s="14" t="s">
+      <c r="L84" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M84" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="N84" s="51" t="s">
+      <c r="N84" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:19" ht="24">
-      <c r="B85" s="52"/>
-      <c r="C85" s="52"/>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="55"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="52"/>
-      <c r="J85" s="55"/>
-      <c r="K85" s="55"/>
-      <c r="L85" s="52"/>
-      <c r="M85" s="14" t="s">
+      <c r="B85" s="85"/>
+      <c r="C85" s="85"/>
+      <c r="D85" s="85"/>
+      <c r="E85" s="85"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="81"/>
+      <c r="H85" s="85"/>
+      <c r="I85" s="85"/>
+      <c r="J85" s="81"/>
+      <c r="K85" s="81"/>
+      <c r="L85" s="85"/>
+      <c r="M85" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N85" s="52"/>
+      <c r="N85" s="85"/>
     </row>
     <row r="86" spans="2:19" ht="24">
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="64"/>
-      <c r="G86" s="55"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="55"/>
-      <c r="K86" s="55"/>
-      <c r="L86" s="52"/>
-      <c r="M86" s="13" t="s">
+      <c r="B86" s="85"/>
+      <c r="C86" s="85"/>
+      <c r="D86" s="85"/>
+      <c r="E86" s="85"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="81"/>
+      <c r="H86" s="85"/>
+      <c r="I86" s="85"/>
+      <c r="J86" s="81"/>
+      <c r="K86" s="81"/>
+      <c r="L86" s="85"/>
+      <c r="M86" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="N86" s="52"/>
+      <c r="N86" s="85"/>
       <c r="S86" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B87" s="53"/>
-      <c r="C87" s="53"/>
-      <c r="D87" s="53"/>
-      <c r="E87" s="53"/>
-      <c r="F87" s="65"/>
-      <c r="G87" s="56"/>
-      <c r="H87" s="53"/>
-      <c r="I87" s="53"/>
-      <c r="J87" s="56"/>
-      <c r="K87" s="56"/>
-      <c r="L87" s="53"/>
-      <c r="M87" s="19" t="s">
+      <c r="B87" s="72"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="66"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="66"/>
+      <c r="K87" s="66"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="N87" s="53"/>
+      <c r="N87" s="72"/>
     </row>
     <row r="88" spans="2:19">
-      <c r="B88" s="54">
+      <c r="B88" s="75">
         <v>13</v>
       </c>
-      <c r="C88" s="54">
+      <c r="C88" s="75">
         <v>16</v>
       </c>
-      <c r="D88" s="54">
+      <c r="D88" s="75">
         <v>19</v>
       </c>
-      <c r="E88" s="54">
+      <c r="E88" s="75">
         <v>21</v>
       </c>
-      <c r="F88" s="63">
+      <c r="F88" s="76">
         <v>23</v>
       </c>
-      <c r="G88" s="54">
+      <c r="G88" s="75">
         <v>23</v>
       </c>
-      <c r="H88" s="60" t="s">
+      <c r="H88" s="77" t="s">
         <v>192</v>
       </c>
-      <c r="I88" s="51" t="s">
+      <c r="I88" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="J88" s="54" t="s">
+      <c r="J88" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K88" s="54" t="s">
+      <c r="K88" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="L88" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M88" s="38" t="s">
+      <c r="L88" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M88" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="N88" s="51" t="s">
+      <c r="N88" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="2:19" ht="24">
-      <c r="B89" s="55"/>
-      <c r="C89" s="55"/>
-      <c r="D89" s="55"/>
-      <c r="E89" s="55"/>
-      <c r="F89" s="64"/>
-      <c r="G89" s="55"/>
-      <c r="H89" s="61"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="55"/>
-      <c r="K89" s="55"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="14" t="s">
+      <c r="B89" s="81"/>
+      <c r="C89" s="81"/>
+      <c r="D89" s="81"/>
+      <c r="E89" s="81"/>
+      <c r="F89" s="82"/>
+      <c r="G89" s="81"/>
+      <c r="H89" s="84"/>
+      <c r="I89" s="85"/>
+      <c r="J89" s="81"/>
+      <c r="K89" s="81"/>
+      <c r="L89" s="85"/>
+      <c r="M89" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="N89" s="52"/>
+      <c r="N89" s="85"/>
     </row>
     <row r="90" spans="2:19">
-      <c r="B90" s="55"/>
-      <c r="C90" s="55"/>
-      <c r="D90" s="55"/>
-      <c r="E90" s="55"/>
-      <c r="F90" s="64"/>
-      <c r="G90" s="55"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="55"/>
-      <c r="K90" s="55"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="14" t="s">
+      <c r="B90" s="81"/>
+      <c r="C90" s="81"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="81"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="81"/>
+      <c r="H90" s="84"/>
+      <c r="I90" s="85"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="81"/>
+      <c r="L90" s="85"/>
+      <c r="M90" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="N90" s="52"/>
+      <c r="N90" s="85"/>
     </row>
     <row r="91" spans="2:19">
-      <c r="B91" s="55"/>
-      <c r="C91" s="55"/>
-      <c r="D91" s="55"/>
-      <c r="E91" s="55"/>
-      <c r="F91" s="64"/>
-      <c r="G91" s="55"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="55"/>
-      <c r="K91" s="55"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="14" t="s">
+      <c r="B91" s="81"/>
+      <c r="C91" s="81"/>
+      <c r="D91" s="81"/>
+      <c r="E91" s="81"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="81"/>
+      <c r="H91" s="84"/>
+      <c r="I91" s="85"/>
+      <c r="J91" s="81"/>
+      <c r="K91" s="81"/>
+      <c r="L91" s="85"/>
+      <c r="M91" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N91" s="52"/>
+      <c r="N91" s="85"/>
     </row>
     <row r="92" spans="2:19" ht="24">
-      <c r="B92" s="55"/>
-      <c r="C92" s="55"/>
-      <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="64"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="61"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="55"/>
-      <c r="K92" s="55"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="37" t="s">
+      <c r="B92" s="81"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
+      <c r="E92" s="81"/>
+      <c r="F92" s="82"/>
+      <c r="G92" s="81"/>
+      <c r="H92" s="84"/>
+      <c r="I92" s="85"/>
+      <c r="J92" s="81"/>
+      <c r="K92" s="81"/>
+      <c r="L92" s="85"/>
+      <c r="M92" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="N92" s="52"/>
+      <c r="N92" s="85"/>
     </row>
     <row r="93" spans="2:19" ht="24.75" thickBot="1">
-      <c r="B93" s="56"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="62"/>
-      <c r="I93" s="53"/>
-      <c r="J93" s="56"/>
-      <c r="K93" s="56"/>
-      <c r="L93" s="53"/>
-      <c r="M93" s="19" t="s">
+      <c r="B93" s="66"/>
+      <c r="C93" s="66"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="66"/>
+      <c r="H93" s="74"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="66"/>
+      <c r="K93" s="66"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="N93" s="53"/>
+      <c r="N93" s="72"/>
     </row>
     <row r="94" spans="2:19">
-      <c r="B94" s="54">
+      <c r="B94" s="75">
         <v>14</v>
       </c>
-      <c r="C94" s="54">
+      <c r="C94" s="75">
         <v>17</v>
       </c>
-      <c r="D94" s="54">
+      <c r="D94" s="75">
         <v>20</v>
       </c>
-      <c r="E94" s="54">
+      <c r="E94" s="75">
         <v>22</v>
       </c>
-      <c r="F94" s="63">
+      <c r="F94" s="76">
         <v>24</v>
       </c>
-      <c r="G94" s="54">
+      <c r="G94" s="75">
         <v>24</v>
       </c>
-      <c r="H94" s="60" t="s">
+      <c r="H94" s="77" t="s">
         <v>196</v>
       </c>
-      <c r="I94" s="51" t="s">
+      <c r="I94" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="J94" s="54" t="s">
+      <c r="J94" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K94" s="54" t="s">
+      <c r="K94" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L94" s="72">
+      <c r="L94" s="95">
         <v>-7</v>
       </c>
-      <c r="M94" s="38" t="s">
+      <c r="M94" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="N94" s="51" t="s">
+      <c r="N94" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:19" ht="24">
-      <c r="B95" s="55"/>
-      <c r="C95" s="55"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="64"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="55"/>
-      <c r="K95" s="55"/>
-      <c r="L95" s="73"/>
-      <c r="M95" s="23" t="s">
+      <c r="B95" s="81"/>
+      <c r="C95" s="81"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
+      <c r="F95" s="82"/>
+      <c r="G95" s="81"/>
+      <c r="H95" s="84"/>
+      <c r="I95" s="85"/>
+      <c r="J95" s="81"/>
+      <c r="K95" s="81"/>
+      <c r="L95" s="93"/>
+      <c r="M95" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="N95" s="52"/>
+      <c r="N95" s="85"/>
     </row>
     <row r="96" spans="2:19" ht="24">
-      <c r="B96" s="55"/>
-      <c r="C96" s="55"/>
-      <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="64"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="61"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="55"/>
-      <c r="K96" s="55"/>
-      <c r="L96" s="73"/>
-      <c r="M96" s="14" t="s">
+      <c r="B96" s="81"/>
+      <c r="C96" s="81"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="81"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="81"/>
+      <c r="H96" s="84"/>
+      <c r="I96" s="85"/>
+      <c r="J96" s="81"/>
+      <c r="K96" s="81"/>
+      <c r="L96" s="93"/>
+      <c r="M96" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="N96" s="52"/>
+      <c r="N96" s="85"/>
     </row>
     <row r="97" spans="2:16" ht="24">
-      <c r="B97" s="55"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="61"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="55"/>
-      <c r="K97" s="55"/>
-      <c r="L97" s="73"/>
-      <c r="M97" s="36" t="s">
+      <c r="B97" s="81"/>
+      <c r="C97" s="81"/>
+      <c r="D97" s="81"/>
+      <c r="E97" s="81"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="81"/>
+      <c r="H97" s="84"/>
+      <c r="I97" s="85"/>
+      <c r="J97" s="81"/>
+      <c r="K97" s="81"/>
+      <c r="L97" s="93"/>
+      <c r="M97" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="N97" s="52"/>
+      <c r="N97" s="85"/>
     </row>
     <row r="98" spans="2:16">
-      <c r="B98" s="55"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="64"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="55"/>
-      <c r="K98" s="55"/>
-      <c r="L98" s="73"/>
-      <c r="M98" s="14" t="s">
+      <c r="B98" s="81"/>
+      <c r="C98" s="81"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="81"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="81"/>
+      <c r="H98" s="84"/>
+      <c r="I98" s="85"/>
+      <c r="J98" s="81"/>
+      <c r="K98" s="81"/>
+      <c r="L98" s="93"/>
+      <c r="M98" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="N98" s="52"/>
+      <c r="N98" s="85"/>
     </row>
     <row r="99" spans="2:16" ht="24">
-      <c r="B99" s="55"/>
-      <c r="C99" s="55"/>
-      <c r="D99" s="55"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="64"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="55"/>
-      <c r="K99" s="55"/>
-      <c r="L99" s="73"/>
-      <c r="M99" s="29" t="s">
+      <c r="B99" s="81"/>
+      <c r="C99" s="81"/>
+      <c r="D99" s="81"/>
+      <c r="E99" s="81"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="81"/>
+      <c r="H99" s="84"/>
+      <c r="I99" s="85"/>
+      <c r="J99" s="81"/>
+      <c r="K99" s="81"/>
+      <c r="L99" s="93"/>
+      <c r="M99" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="N99" s="52"/>
+      <c r="N99" s="85"/>
     </row>
     <row r="100" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B100" s="56"/>
-      <c r="C100" s="56"/>
-      <c r="D100" s="56"/>
-      <c r="E100" s="56"/>
-      <c r="F100" s="65"/>
-      <c r="G100" s="56"/>
-      <c r="H100" s="62"/>
-      <c r="I100" s="53"/>
-      <c r="J100" s="56"/>
-      <c r="K100" s="56"/>
-      <c r="L100" s="74"/>
-      <c r="M100" s="21" t="s">
+      <c r="B100" s="66"/>
+      <c r="C100" s="66"/>
+      <c r="D100" s="66"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="66"/>
+      <c r="H100" s="74"/>
+      <c r="I100" s="72"/>
+      <c r="J100" s="66"/>
+      <c r="K100" s="66"/>
+      <c r="L100" s="94"/>
+      <c r="M100" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="N100" s="53"/>
+      <c r="N100" s="72"/>
     </row>
     <row r="101" spans="2:16">
-      <c r="B101" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D101" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E101" s="54">
+      <c r="B101" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="75">
         <v>23</v>
       </c>
-      <c r="F101" s="63">
+      <c r="F101" s="76">
         <v>25</v>
       </c>
-      <c r="G101" s="54">
+      <c r="G101" s="75">
         <v>25</v>
       </c>
-      <c r="H101" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I101" s="51" t="s">
+      <c r="H101" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="I101" s="83" t="s">
         <v>199</v>
       </c>
-      <c r="J101" s="54" t="s">
+      <c r="J101" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K101" s="54" t="s">
+      <c r="K101" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L101" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M101" s="14" t="s">
+      <c r="L101" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M101" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="N101" s="51" t="s">
+      <c r="N101" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="2:16">
-      <c r="B102" s="52"/>
-      <c r="C102" s="52"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="64"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="52"/>
-      <c r="I102" s="52"/>
-      <c r="J102" s="55"/>
-      <c r="K102" s="55"/>
-      <c r="L102" s="52"/>
-      <c r="M102" s="14" t="s">
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="81"/>
+      <c r="F102" s="82"/>
+      <c r="G102" s="81"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="81"/>
+      <c r="K102" s="81"/>
+      <c r="L102" s="85"/>
+      <c r="M102" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="N102" s="52"/>
+      <c r="N102" s="85"/>
     </row>
     <row r="103" spans="2:16" ht="24">
-      <c r="B103" s="52"/>
-      <c r="C103" s="52"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="64"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="52"/>
-      <c r="I103" s="52"/>
-      <c r="J103" s="55"/>
-      <c r="K103" s="55"/>
-      <c r="L103" s="52"/>
-      <c r="M103" s="14" t="s">
+      <c r="B103" s="85"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="82"/>
+      <c r="G103" s="81"/>
+      <c r="H103" s="85"/>
+      <c r="I103" s="85"/>
+      <c r="J103" s="81"/>
+      <c r="K103" s="81"/>
+      <c r="L103" s="85"/>
+      <c r="M103" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N103" s="52"/>
+      <c r="N103" s="85"/>
     </row>
     <row r="104" spans="2:16" ht="24">
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="64"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="52"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="55"/>
-      <c r="K104" s="55"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="29" t="s">
+      <c r="B104" s="85"/>
+      <c r="C104" s="85"/>
+      <c r="D104" s="85"/>
+      <c r="E104" s="81"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="81"/>
+      <c r="H104" s="85"/>
+      <c r="I104" s="85"/>
+      <c r="J104" s="81"/>
+      <c r="K104" s="81"/>
+      <c r="L104" s="85"/>
+      <c r="M104" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="N104" s="52"/>
+      <c r="N104" s="85"/>
     </row>
     <row r="105" spans="2:16" ht="15" thickBot="1">
-      <c r="B105" s="53"/>
-      <c r="C105" s="53"/>
-      <c r="D105" s="53"/>
-      <c r="E105" s="56"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="56"/>
-      <c r="H105" s="53"/>
-      <c r="I105" s="53"/>
-      <c r="J105" s="56"/>
-      <c r="K105" s="56"/>
-      <c r="L105" s="53"/>
-      <c r="M105" s="19" t="s">
+      <c r="B105" s="72"/>
+      <c r="C105" s="72"/>
+      <c r="D105" s="72"/>
+      <c r="E105" s="66"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="66"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="66"/>
+      <c r="K105" s="66"/>
+      <c r="L105" s="72"/>
+      <c r="M105" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="N105" s="53"/>
+      <c r="N105" s="72"/>
     </row>
     <row r="106" spans="2:16">
-      <c r="B106" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C106" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="54">
+      <c r="B106" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C106" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="75">
         <v>24</v>
       </c>
-      <c r="F106" s="63">
+      <c r="F106" s="76">
         <v>26</v>
       </c>
-      <c r="G106" s="54">
+      <c r="G106" s="75">
         <v>26</v>
       </c>
-      <c r="H106" s="60" t="s">
+      <c r="H106" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="75" t="s">
+      <c r="I106" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="J106" s="54" t="s">
+      <c r="J106" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K106" s="54" t="s">
+      <c r="K106" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="L106" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M106" s="14" t="s">
+      <c r="L106" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M106" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N106" s="51" t="s">
+      <c r="N106" s="83" t="s">
         <v>203</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>592</v>
       </c>
     </row>
     <row r="107" spans="2:16">
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
-      <c r="D107" s="52"/>
-      <c r="E107" s="55"/>
-      <c r="F107" s="64"/>
-      <c r="G107" s="55"/>
-      <c r="H107" s="61"/>
-      <c r="I107" s="70"/>
-      <c r="J107" s="55"/>
-      <c r="K107" s="55"/>
-      <c r="L107" s="52"/>
-      <c r="M107" s="14" t="s">
+      <c r="B107" s="85"/>
+      <c r="C107" s="85"/>
+      <c r="D107" s="85"/>
+      <c r="E107" s="81"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="81"/>
+      <c r="H107" s="84"/>
+      <c r="I107" s="90"/>
+      <c r="J107" s="81"/>
+      <c r="K107" s="81"/>
+      <c r="L107" s="85"/>
+      <c r="M107" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="N107" s="52"/>
+      <c r="N107" s="85"/>
     </row>
     <row r="108" spans="2:16" ht="15" thickBot="1">
-      <c r="B108" s="53"/>
-      <c r="C108" s="53"/>
-      <c r="D108" s="53"/>
-      <c r="E108" s="56"/>
-      <c r="F108" s="65"/>
-      <c r="G108" s="56"/>
-      <c r="H108" s="62"/>
-      <c r="I108" s="71"/>
-      <c r="J108" s="56"/>
-      <c r="K108" s="56"/>
-      <c r="L108" s="53"/>
-      <c r="M108" s="19" t="s">
+      <c r="B108" s="72"/>
+      <c r="C108" s="72"/>
+      <c r="D108" s="72"/>
+      <c r="E108" s="66"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="66"/>
+      <c r="H108" s="74"/>
+      <c r="I108" s="91"/>
+      <c r="J108" s="66"/>
+      <c r="K108" s="66"/>
+      <c r="L108" s="72"/>
+      <c r="M108" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="N108" s="53"/>
+      <c r="N108" s="72"/>
     </row>
     <row r="109" spans="2:16" ht="24.75" thickBot="1">
-      <c r="B109" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D109" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E109" s="15">
+      <c r="B109" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E109" s="14">
         <v>25</v>
       </c>
-      <c r="F109" s="32">
+      <c r="F109" s="31">
         <v>27</v>
       </c>
-      <c r="G109" s="15">
+      <c r="G109" s="14">
         <v>27</v>
       </c>
-      <c r="H109" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I109" s="40" t="s">
+      <c r="H109" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I109" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="J109" s="15" t="s">
+      <c r="J109" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="K109" s="15" t="s">
+      <c r="K109" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L109" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M109" s="19" t="s">
+      <c r="L109" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="M109" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="N109" s="19" t="s">
+      <c r="N109" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="P109" t="s">
-        <v>267</v>
-      </c>
     </row>
     <row r="110" spans="2:16" ht="15" thickTop="1">
-      <c r="B110" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="67">
+      <c r="B110" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C110" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="65">
         <v>26</v>
       </c>
-      <c r="F110" s="68">
+      <c r="F110" s="67">
         <v>28</v>
       </c>
-      <c r="G110" s="67">
+      <c r="G110" s="65">
         <v>28</v>
       </c>
-      <c r="H110" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="I110" s="69" t="s">
+      <c r="H110" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="I110" s="96" t="s">
         <v>207</v>
       </c>
-      <c r="J110" s="67" t="s">
+      <c r="J110" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="K110" s="67" t="s">
+      <c r="K110" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="L110" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="M110" s="14" t="s">
+      <c r="L110" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="M110" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="N110" s="66" t="s">
+      <c r="N110" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="P110" t="s">
-        <v>268</v>
-      </c>
     </row>
     <row r="111" spans="2:16" ht="24">
-      <c r="B111" s="52"/>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="55"/>
-      <c r="H111" s="52"/>
-      <c r="I111" s="70"/>
-      <c r="J111" s="55"/>
-      <c r="K111" s="55"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="14" t="s">
+      <c r="B111" s="85"/>
+      <c r="C111" s="85"/>
+      <c r="D111" s="85"/>
+      <c r="E111" s="81"/>
+      <c r="F111" s="82"/>
+      <c r="G111" s="81"/>
+      <c r="H111" s="85"/>
+      <c r="I111" s="90"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="81"/>
+      <c r="L111" s="85"/>
+      <c r="M111" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="N111" s="52"/>
+      <c r="N111" s="85"/>
     </row>
     <row r="112" spans="2:16" ht="24">
-      <c r="B112" s="52"/>
-      <c r="C112" s="52"/>
-      <c r="D112" s="52"/>
-      <c r="E112" s="55"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="55"/>
-      <c r="H112" s="52"/>
-      <c r="I112" s="70"/>
-      <c r="J112" s="55"/>
-      <c r="K112" s="55"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="14" t="s">
+      <c r="B112" s="85"/>
+      <c r="C112" s="85"/>
+      <c r="D112" s="85"/>
+      <c r="E112" s="81"/>
+      <c r="F112" s="82"/>
+      <c r="G112" s="81"/>
+      <c r="H112" s="85"/>
+      <c r="I112" s="90"/>
+      <c r="J112" s="81"/>
+      <c r="K112" s="81"/>
+      <c r="L112" s="85"/>
+      <c r="M112" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="52"/>
+      <c r="N112" s="85"/>
     </row>
     <row r="113" spans="2:14" ht="15" thickBot="1">
-      <c r="B113" s="53"/>
-      <c r="C113" s="53"/>
-      <c r="D113" s="53"/>
-      <c r="E113" s="56"/>
-      <c r="F113" s="65"/>
-      <c r="G113" s="56"/>
-      <c r="H113" s="53"/>
-      <c r="I113" s="71"/>
-      <c r="J113" s="56"/>
-      <c r="K113" s="56"/>
-      <c r="L113" s="53"/>
-      <c r="M113" s="19" t="s">
+      <c r="B113" s="72"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="72"/>
+      <c r="E113" s="66"/>
+      <c r="F113" s="68"/>
+      <c r="G113" s="66"/>
+      <c r="H113" s="72"/>
+      <c r="I113" s="91"/>
+      <c r="J113" s="66"/>
+      <c r="K113" s="66"/>
+      <c r="L113" s="72"/>
+      <c r="M113" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N113" s="53"/>
+      <c r="N113" s="72"/>
     </row>
     <row r="114" spans="2:14" ht="36">
-      <c r="B114" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" s="54">
+      <c r="B114" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="75">
         <v>18</v>
       </c>
-      <c r="D114" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E114" s="54">
+      <c r="D114" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E114" s="75">
         <v>27</v>
       </c>
-      <c r="F114" s="63">
+      <c r="F114" s="76">
         <v>29</v>
       </c>
-      <c r="G114" s="54">
+      <c r="G114" s="75">
         <v>29</v>
       </c>
-      <c r="H114" s="60" t="s">
+      <c r="H114" s="77" t="s">
         <v>209</v>
       </c>
-      <c r="I114" s="51" t="s">
+      <c r="I114" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="J114" s="54" t="s">
+      <c r="J114" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K114" s="54" t="s">
+      <c r="K114" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="L114" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M114" s="29" t="s">
+      <c r="L114" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M114" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="N114" s="51" t="s">
+      <c r="N114" s="83" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="115" spans="2:14" ht="24">
-      <c r="B115" s="52"/>
-      <c r="C115" s="55"/>
-      <c r="D115" s="52"/>
-      <c r="E115" s="55"/>
-      <c r="F115" s="64"/>
-      <c r="G115" s="55"/>
-      <c r="H115" s="61"/>
-      <c r="I115" s="52"/>
-      <c r="J115" s="55"/>
-      <c r="K115" s="55"/>
-      <c r="L115" s="52"/>
-      <c r="M115" s="14" t="s">
+      <c r="B115" s="85"/>
+      <c r="C115" s="81"/>
+      <c r="D115" s="85"/>
+      <c r="E115" s="81"/>
+      <c r="F115" s="82"/>
+      <c r="G115" s="81"/>
+      <c r="H115" s="84"/>
+      <c r="I115" s="85"/>
+      <c r="J115" s="81"/>
+      <c r="K115" s="81"/>
+      <c r="L115" s="85"/>
+      <c r="M115" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="N115" s="52"/>
+      <c r="N115" s="85"/>
     </row>
     <row r="116" spans="2:14">
-      <c r="B116" s="52"/>
-      <c r="C116" s="55"/>
-      <c r="D116" s="52"/>
-      <c r="E116" s="55"/>
-      <c r="F116" s="64"/>
-      <c r="G116" s="55"/>
-      <c r="H116" s="61"/>
-      <c r="I116" s="52"/>
-      <c r="J116" s="55"/>
-      <c r="K116" s="55"/>
-      <c r="L116" s="52"/>
-      <c r="M116" s="14" t="s">
+      <c r="B116" s="85"/>
+      <c r="C116" s="81"/>
+      <c r="D116" s="85"/>
+      <c r="E116" s="81"/>
+      <c r="F116" s="82"/>
+      <c r="G116" s="81"/>
+      <c r="H116" s="84"/>
+      <c r="I116" s="85"/>
+      <c r="J116" s="81"/>
+      <c r="K116" s="81"/>
+      <c r="L116" s="85"/>
+      <c r="M116" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="N116" s="52"/>
+      <c r="N116" s="85"/>
     </row>
     <row r="117" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B117" s="53"/>
-      <c r="C117" s="56"/>
-      <c r="D117" s="53"/>
-      <c r="E117" s="56"/>
-      <c r="F117" s="65"/>
-      <c r="G117" s="56"/>
-      <c r="H117" s="62"/>
-      <c r="I117" s="53"/>
-      <c r="J117" s="56"/>
-      <c r="K117" s="56"/>
-      <c r="L117" s="53"/>
-      <c r="M117" s="34" t="s">
+      <c r="B117" s="72"/>
+      <c r="C117" s="66"/>
+      <c r="D117" s="72"/>
+      <c r="E117" s="66"/>
+      <c r="F117" s="68"/>
+      <c r="G117" s="66"/>
+      <c r="H117" s="74"/>
+      <c r="I117" s="72"/>
+      <c r="J117" s="66"/>
+      <c r="K117" s="66"/>
+      <c r="L117" s="72"/>
+      <c r="M117" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="N117" s="53"/>
+      <c r="N117" s="72"/>
     </row>
     <row r="118" spans="2:14" ht="36">
-      <c r="B118" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" s="54">
+      <c r="B118" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="75">
         <v>19</v>
       </c>
-      <c r="D118" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E118" s="54">
+      <c r="D118" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="75">
         <v>28</v>
       </c>
-      <c r="F118" s="63">
+      <c r="F118" s="76">
         <v>30</v>
       </c>
-      <c r="G118" s="54">
+      <c r="G118" s="75">
         <v>30</v>
       </c>
-      <c r="H118" s="60" t="s">
+      <c r="H118" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="51" t="s">
+      <c r="I118" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="J118" s="54" t="s">
+      <c r="J118" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K118" s="54" t="s">
+      <c r="K118" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="L118" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M118" s="29" t="s">
+      <c r="L118" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M118" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="N118" s="51" t="s">
+      <c r="N118" s="83" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="119" spans="2:14" ht="36">
-      <c r="B119" s="52"/>
-      <c r="C119" s="55"/>
-      <c r="D119" s="52"/>
-      <c r="E119" s="55"/>
-      <c r="F119" s="64"/>
-      <c r="G119" s="55"/>
-      <c r="H119" s="61"/>
-      <c r="I119" s="52"/>
-      <c r="J119" s="55"/>
-      <c r="K119" s="55"/>
-      <c r="L119" s="52"/>
-      <c r="M119" s="14" t="s">
+      <c r="B119" s="85"/>
+      <c r="C119" s="81"/>
+      <c r="D119" s="85"/>
+      <c r="E119" s="81"/>
+      <c r="F119" s="82"/>
+      <c r="G119" s="81"/>
+      <c r="H119" s="84"/>
+      <c r="I119" s="85"/>
+      <c r="J119" s="81"/>
+      <c r="K119" s="81"/>
+      <c r="L119" s="85"/>
+      <c r="M119" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="N119" s="52"/>
+      <c r="N119" s="85"/>
     </row>
     <row r="120" spans="2:14" ht="24.75" thickBot="1">
-      <c r="B120" s="53"/>
-      <c r="C120" s="56"/>
-      <c r="D120" s="53"/>
-      <c r="E120" s="56"/>
-      <c r="F120" s="65"/>
-      <c r="G120" s="56"/>
-      <c r="H120" s="62"/>
-      <c r="I120" s="53"/>
-      <c r="J120" s="56"/>
-      <c r="K120" s="56"/>
-      <c r="L120" s="53"/>
-      <c r="M120" s="34" t="s">
+      <c r="B120" s="72"/>
+      <c r="C120" s="66"/>
+      <c r="D120" s="72"/>
+      <c r="E120" s="66"/>
+      <c r="F120" s="68"/>
+      <c r="G120" s="66"/>
+      <c r="H120" s="74"/>
+      <c r="I120" s="72"/>
+      <c r="J120" s="66"/>
+      <c r="K120" s="66"/>
+      <c r="L120" s="72"/>
+      <c r="M120" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="N120" s="53"/>
+      <c r="N120" s="72"/>
     </row>
     <row r="121" spans="2:14" ht="48.75" thickBot="1">
-      <c r="B121" s="17">
+      <c r="B121" s="16">
         <v>1</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="14">
         <v>20</v>
       </c>
-      <c r="D121" s="15">
+      <c r="D121" s="14">
         <v>1</v>
       </c>
-      <c r="E121" s="15">
+      <c r="E121" s="14">
         <v>1</v>
       </c>
-      <c r="F121" s="32">
+      <c r="F121" s="31">
         <v>31</v>
       </c>
-      <c r="G121" s="15">
+      <c r="G121" s="14">
         <v>31</v>
       </c>
-      <c r="H121" s="16" t="s">
+      <c r="H121" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="I121" s="39" t="s">
+      <c r="I121" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="J121" s="19" t="s">
+      <c r="J121" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="K121" s="15" t="s">
+      <c r="K121" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="L121" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M121" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N121" s="40" t="s">
+      <c r="L121" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="M121" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N121" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="122" spans="2:14" ht="24">
-      <c r="B122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="G122" s="54">
+      <c r="B122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="G122" s="75">
         <v>32</v>
       </c>
-      <c r="H122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I122" s="51" t="s">
+      <c r="H122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="I122" s="83" t="s">
         <v>222</v>
       </c>
-      <c r="J122" s="54" t="s">
+      <c r="J122" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="K122" s="54" t="s">
+      <c r="K122" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="L122" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M122" s="14" t="s">
+      <c r="L122" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="M122" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="N122" s="51" t="s">
+      <c r="N122" s="83" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="24">
-      <c r="B123" s="52"/>
-      <c r="C123" s="52"/>
-      <c r="D123" s="52"/>
-      <c r="E123" s="52"/>
-      <c r="F123" s="58"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="52"/>
-      <c r="I123" s="52"/>
-      <c r="J123" s="55"/>
-      <c r="K123" s="55"/>
-      <c r="L123" s="52"/>
-      <c r="M123" s="14" t="s">
+      <c r="B123" s="85"/>
+      <c r="C123" s="85"/>
+      <c r="D123" s="85"/>
+      <c r="E123" s="85"/>
+      <c r="F123" s="98"/>
+      <c r="G123" s="81"/>
+      <c r="H123" s="85"/>
+      <c r="I123" s="85"/>
+      <c r="J123" s="81"/>
+      <c r="K123" s="81"/>
+      <c r="L123" s="85"/>
+      <c r="M123" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="N123" s="52"/>
+      <c r="N123" s="85"/>
     </row>
     <row r="124" spans="2:14">
-      <c r="B124" s="52"/>
-      <c r="C124" s="52"/>
-      <c r="D124" s="52"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="58"/>
-      <c r="G124" s="55"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="55"/>
-      <c r="K124" s="55"/>
-      <c r="L124" s="52"/>
-      <c r="M124" s="14" t="s">
+      <c r="B124" s="85"/>
+      <c r="C124" s="85"/>
+      <c r="D124" s="85"/>
+      <c r="E124" s="85"/>
+      <c r="F124" s="98"/>
+      <c r="G124" s="81"/>
+      <c r="H124" s="85"/>
+      <c r="I124" s="85"/>
+      <c r="J124" s="81"/>
+      <c r="K124" s="81"/>
+      <c r="L124" s="85"/>
+      <c r="M124" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="N124" s="52"/>
+      <c r="N124" s="85"/>
     </row>
     <row r="125" spans="2:14" ht="15" thickBot="1">
-      <c r="B125" s="53"/>
-      <c r="C125" s="53"/>
-      <c r="D125" s="53"/>
-      <c r="E125" s="53"/>
-      <c r="F125" s="59"/>
-      <c r="G125" s="56"/>
-      <c r="H125" s="53"/>
-      <c r="I125" s="53"/>
-      <c r="J125" s="56"/>
-      <c r="K125" s="56"/>
-      <c r="L125" s="53"/>
-      <c r="M125" s="19" t="s">
+      <c r="B125" s="72"/>
+      <c r="C125" s="72"/>
+      <c r="D125" s="72"/>
+      <c r="E125" s="72"/>
+      <c r="F125" s="99"/>
+      <c r="G125" s="66"/>
+      <c r="H125" s="72"/>
+      <c r="I125" s="72"/>
+      <c r="J125" s="66"/>
+      <c r="K125" s="66"/>
+      <c r="L125" s="72"/>
+      <c r="M125" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="N125" s="53"/>
+      <c r="N125" s="72"/>
     </row>
     <row r="126" spans="2:14" ht="15" thickBot="1">
-      <c r="B126" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F126" s="32">
+      <c r="B126" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F126" s="31">
         <v>32</v>
       </c>
-      <c r="G126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I126" s="19" t="s">
+      <c r="G126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I126" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="J126" s="15" t="s">
+      <c r="J126" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L126" s="20">
+      <c r="K126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L126" s="19">
         <v>-5</v>
       </c>
-      <c r="M126" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N126" s="19" t="s">
+      <c r="M126" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N126" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="127" spans="2:14" ht="15" thickBot="1">
-      <c r="B127" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F127" s="32">
+      <c r="B127" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F127" s="31">
         <v>1</v>
       </c>
-      <c r="G127" s="15">
+      <c r="G127" s="14">
         <v>1</v>
       </c>
-      <c r="H127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I127" s="19" t="s">
+      <c r="H127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I127" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="J127" s="15" t="s">
+      <c r="J127" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L127" s="20">
+      <c r="K127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L127" s="19">
         <v>-6</v>
       </c>
-      <c r="M127" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N127" s="19" t="s">
+      <c r="M127" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="N127" s="18" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="298">
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="I122:I125"/>
+    <mergeCell ref="J122:J125"/>
+    <mergeCell ref="K122:K125"/>
+    <mergeCell ref="L122:L125"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="H118:H120"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="J118:J120"/>
+    <mergeCell ref="K118:K120"/>
+    <mergeCell ref="L118:L120"/>
+    <mergeCell ref="N118:N120"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="E118:E120"/>
+    <mergeCell ref="F118:F120"/>
+    <mergeCell ref="G118:G120"/>
+    <mergeCell ref="K114:K117"/>
+    <mergeCell ref="L114:L117"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="J114:J117"/>
+    <mergeCell ref="K101:K105"/>
+    <mergeCell ref="L101:L105"/>
+    <mergeCell ref="N101:N105"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="J110:J113"/>
+    <mergeCell ref="K110:K113"/>
+    <mergeCell ref="L110:L113"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="D106:D108"/>
+    <mergeCell ref="E106:E108"/>
+    <mergeCell ref="F106:F108"/>
+    <mergeCell ref="K94:K100"/>
+    <mergeCell ref="L94:L100"/>
+    <mergeCell ref="N94:N100"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="C101:C105"/>
+    <mergeCell ref="D101:D105"/>
+    <mergeCell ref="E101:E105"/>
+    <mergeCell ref="F101:F105"/>
+    <mergeCell ref="G101:G105"/>
+    <mergeCell ref="H101:H105"/>
+    <mergeCell ref="N106:N108"/>
+    <mergeCell ref="G106:G108"/>
+    <mergeCell ref="H106:H108"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="K106:K108"/>
+    <mergeCell ref="L106:L108"/>
+    <mergeCell ref="I101:I105"/>
+    <mergeCell ref="J101:J105"/>
+    <mergeCell ref="B94:B100"/>
+    <mergeCell ref="C94:C100"/>
+    <mergeCell ref="D94:D100"/>
+    <mergeCell ref="E94:E100"/>
+    <mergeCell ref="F94:F100"/>
+    <mergeCell ref="G94:G100"/>
+    <mergeCell ref="H94:H100"/>
+    <mergeCell ref="I94:I100"/>
+    <mergeCell ref="J94:J100"/>
+    <mergeCell ref="K84:K87"/>
+    <mergeCell ref="L84:L87"/>
+    <mergeCell ref="N84:N87"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="D88:D93"/>
+    <mergeCell ref="E88:E93"/>
+    <mergeCell ref="F88:F93"/>
+    <mergeCell ref="N88:N93"/>
+    <mergeCell ref="G88:G93"/>
+    <mergeCell ref="H88:H93"/>
+    <mergeCell ref="I88:I93"/>
+    <mergeCell ref="J88:J93"/>
+    <mergeCell ref="K88:K93"/>
+    <mergeCell ref="L88:L93"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="E84:E87"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="G84:G87"/>
+    <mergeCell ref="H84:H87"/>
+    <mergeCell ref="I84:I87"/>
+    <mergeCell ref="J84:J87"/>
+    <mergeCell ref="N75:N79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="G80:G83"/>
+    <mergeCell ref="H80:H83"/>
+    <mergeCell ref="I80:I83"/>
+    <mergeCell ref="J80:J83"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="H75:H79"/>
+    <mergeCell ref="I75:I79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="K75:K79"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="D75:D79"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="K80:K83"/>
+    <mergeCell ref="L80:L83"/>
+    <mergeCell ref="N80:N83"/>
+    <mergeCell ref="H71:H74"/>
+    <mergeCell ref="I71:I74"/>
+    <mergeCell ref="J71:J74"/>
+    <mergeCell ref="K71:K74"/>
+    <mergeCell ref="L71:L74"/>
+    <mergeCell ref="N71:N74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="G71:G74"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="K67:K70"/>
+    <mergeCell ref="L67:L70"/>
+    <mergeCell ref="N67:N70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="G59:G63"/>
+    <mergeCell ref="H59:H63"/>
+    <mergeCell ref="I59:I63"/>
+    <mergeCell ref="J59:J63"/>
+    <mergeCell ref="K59:K63"/>
+    <mergeCell ref="L59:L63"/>
+    <mergeCell ref="H54:H58"/>
+    <mergeCell ref="I54:I58"/>
+    <mergeCell ref="J54:J58"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="L54:L58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="D59:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="F59:F63"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="I48:I53"/>
+    <mergeCell ref="J48:J53"/>
+    <mergeCell ref="K48:K53"/>
+    <mergeCell ref="L48:L53"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="G48:G53"/>
+    <mergeCell ref="K39:K42"/>
+    <mergeCell ref="L39:L42"/>
+    <mergeCell ref="B43:B47"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="D43:D47"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="L32:L38"/>
+    <mergeCell ref="B32:B38"/>
+    <mergeCell ref="C32:C38"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="E32:E38"/>
+    <mergeCell ref="F32:F38"/>
+    <mergeCell ref="G32:G38"/>
+    <mergeCell ref="H32:H38"/>
+    <mergeCell ref="I32:I38"/>
+    <mergeCell ref="J32:J38"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="I24:I27"/>
+    <mergeCell ref="J24:J27"/>
+    <mergeCell ref="K24:K27"/>
+    <mergeCell ref="L24:L27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="J28:J31"/>
+    <mergeCell ref="K28:K31"/>
+    <mergeCell ref="L28:L31"/>
+    <mergeCell ref="B17:B23"/>
     <mergeCell ref="C17:C23"/>
     <mergeCell ref="D17:D23"/>
     <mergeCell ref="E17:E23"/>
@@ -7508,254 +8531,32 @@
     <mergeCell ref="J11:J16"/>
     <mergeCell ref="K11:K16"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="L11:L16"/>
-    <mergeCell ref="H24:H27"/>
-    <mergeCell ref="I24:I27"/>
-    <mergeCell ref="J24:J27"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="L24:L27"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="F24:F27"/>
-    <mergeCell ref="G24:G27"/>
-    <mergeCell ref="G28:G31"/>
-    <mergeCell ref="H28:H31"/>
-    <mergeCell ref="I28:I31"/>
-    <mergeCell ref="J28:J31"/>
-    <mergeCell ref="K28:K31"/>
-    <mergeCell ref="L28:L31"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="J39:J42"/>
-    <mergeCell ref="K32:K38"/>
-    <mergeCell ref="L32:L38"/>
-    <mergeCell ref="B32:B38"/>
-    <mergeCell ref="C32:C38"/>
-    <mergeCell ref="D32:D38"/>
-    <mergeCell ref="E32:E38"/>
-    <mergeCell ref="F32:F38"/>
-    <mergeCell ref="G32:G38"/>
-    <mergeCell ref="H32:H38"/>
-    <mergeCell ref="I32:I38"/>
-    <mergeCell ref="J32:J38"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="G48:G53"/>
-    <mergeCell ref="K39:K42"/>
-    <mergeCell ref="L39:L42"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="D43:D47"/>
-    <mergeCell ref="E43:E47"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="G39:G42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="I39:I42"/>
-    <mergeCell ref="H48:H53"/>
-    <mergeCell ref="I48:I53"/>
-    <mergeCell ref="J48:J53"/>
-    <mergeCell ref="K48:K53"/>
-    <mergeCell ref="L48:L53"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="K43:K47"/>
-    <mergeCell ref="L43:L47"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="D59:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="H59:H63"/>
-    <mergeCell ref="I59:I63"/>
-    <mergeCell ref="J59:J63"/>
-    <mergeCell ref="K59:K63"/>
-    <mergeCell ref="L59:L63"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="J54:J58"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="J67:J70"/>
-    <mergeCell ref="K67:K70"/>
-    <mergeCell ref="L67:L70"/>
-    <mergeCell ref="N67:N70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="H71:H74"/>
-    <mergeCell ref="I71:I74"/>
-    <mergeCell ref="J71:J74"/>
-    <mergeCell ref="K71:K74"/>
-    <mergeCell ref="L71:L74"/>
-    <mergeCell ref="N71:N74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="E71:E74"/>
-    <mergeCell ref="F71:F74"/>
-    <mergeCell ref="G71:G74"/>
-    <mergeCell ref="N75:N79"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="G80:G83"/>
-    <mergeCell ref="H80:H83"/>
-    <mergeCell ref="I80:I83"/>
-    <mergeCell ref="J80:J83"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="H75:H79"/>
-    <mergeCell ref="I75:I79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="K75:K79"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="D75:D79"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="K80:K83"/>
-    <mergeCell ref="L80:L83"/>
-    <mergeCell ref="N80:N83"/>
-    <mergeCell ref="K84:K87"/>
-    <mergeCell ref="L84:L87"/>
-    <mergeCell ref="N84:N87"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="D88:D93"/>
-    <mergeCell ref="E88:E93"/>
-    <mergeCell ref="F88:F93"/>
-    <mergeCell ref="N88:N93"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="H88:H93"/>
-    <mergeCell ref="I88:I93"/>
-    <mergeCell ref="J88:J93"/>
-    <mergeCell ref="K88:K93"/>
-    <mergeCell ref="L88:L93"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E84:E87"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="G84:G87"/>
-    <mergeCell ref="H84:H87"/>
-    <mergeCell ref="I84:I87"/>
-    <mergeCell ref="J84:J87"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="C94:C100"/>
-    <mergeCell ref="D94:D100"/>
-    <mergeCell ref="E94:E100"/>
-    <mergeCell ref="F94:F100"/>
-    <mergeCell ref="G94:G100"/>
-    <mergeCell ref="H94:H100"/>
-    <mergeCell ref="I94:I100"/>
-    <mergeCell ref="J94:J100"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="D106:D108"/>
-    <mergeCell ref="E106:E108"/>
-    <mergeCell ref="F106:F108"/>
-    <mergeCell ref="K94:K100"/>
-    <mergeCell ref="L94:L100"/>
-    <mergeCell ref="N94:N100"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="C101:C105"/>
-    <mergeCell ref="D101:D105"/>
-    <mergeCell ref="E101:E105"/>
-    <mergeCell ref="F101:F105"/>
-    <mergeCell ref="G101:G105"/>
-    <mergeCell ref="H101:H105"/>
-    <mergeCell ref="N106:N108"/>
-    <mergeCell ref="G106:G108"/>
-    <mergeCell ref="H106:H108"/>
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="J106:J108"/>
-    <mergeCell ref="K106:K108"/>
-    <mergeCell ref="L106:L108"/>
-    <mergeCell ref="I101:I105"/>
-    <mergeCell ref="J101:J105"/>
-    <mergeCell ref="K101:K105"/>
-    <mergeCell ref="L101:L105"/>
-    <mergeCell ref="N101:N105"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="J110:J113"/>
-    <mergeCell ref="K110:K113"/>
-    <mergeCell ref="L110:L113"/>
-    <mergeCell ref="N110:N113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="I114:I117"/>
-    <mergeCell ref="J114:J117"/>
-    <mergeCell ref="K114:K117"/>
-    <mergeCell ref="L114:L117"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="H118:H120"/>
-    <mergeCell ref="I118:I120"/>
-    <mergeCell ref="J118:J120"/>
-    <mergeCell ref="K118:K120"/>
-    <mergeCell ref="L118:L120"/>
-    <mergeCell ref="N118:N120"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="E118:E120"/>
-    <mergeCell ref="F118:F120"/>
-    <mergeCell ref="G118:G120"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="I122:I125"/>
-    <mergeCell ref="J122:J125"/>
-    <mergeCell ref="K122:K125"/>
-    <mergeCell ref="L122:L125"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7804,8 +8605,8 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="42" t="s">
-        <v>273</v>
+      <c r="A3" s="41" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -7959,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -7975,7 +8776,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
@@ -7992,13 +8793,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -8011,10 +8812,10 @@
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>10</v>
@@ -8153,7 +8954,7 @@
     </row>
     <row r="18" spans="4:5" ht="28.5">
       <c r="D18" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -8176,7 +8977,7 @@
     </row>
     <row r="22" spans="4:5" ht="28.5">
       <c r="D22" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -8184,17 +8985,17 @@
     </row>
     <row r="25" spans="4:5">
       <c r="D25" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="4:5">
       <c r="D26" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="4:5">
       <c r="D27" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -8279,7 +9080,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8287,7 +9088,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -8311,7 +9112,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30">
@@ -8319,7 +9120,7 @@
         <v>243</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8377,7 +9178,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>32</v>
@@ -8385,15 +9186,15 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>32</v>
@@ -8401,7 +9202,7 @@
     </row>
     <row r="24" spans="1:2" ht="30">
       <c r="A24" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>32</v>
@@ -8409,7 +9210,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>32</v>
@@ -8417,15 +9218,15 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>32</v>
@@ -8433,7 +9234,7 @@
     </row>
     <row r="28" spans="1:2" ht="30">
       <c r="A28" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>32</v>
@@ -8441,7 +9242,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>32</v>
@@ -8449,7 +9250,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>32</v>
@@ -8457,7 +9258,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>32</v>
@@ -8465,7 +9266,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>32</v>
@@ -8473,7 +9274,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>32</v>
@@ -8481,7 +9282,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>32</v>
@@ -8489,7 +9290,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>32</v>
@@ -8497,7 +9298,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>32</v>
@@ -8505,7 +9306,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>32</v>
@@ -8513,7 +9314,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>32</v>
@@ -8521,7 +9322,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>32</v>
@@ -8529,15 +9330,15 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="30">
       <c r="A41" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>32</v>
@@ -8545,7 +9346,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>32</v>
@@ -8553,15 +9354,15 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="30">
       <c r="A44" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>32</v>
@@ -8569,7 +9370,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>32</v>
@@ -8577,7 +9378,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>32</v>
@@ -8585,7 +9386,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>32</v>
@@ -8593,7 +9394,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>32</v>
@@ -8601,7 +9402,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>32</v>
@@ -8609,7 +9410,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>32</v>
@@ -8622,10 +9423,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
     <col min="2" max="2" width="57.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
@@ -8640,19 +9441,19 @@
         <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>7</v>
@@ -8663,364 +9464,495 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
+        <v>527</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.5">
+      <c r="E11" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>530</v>
+        <v>516</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.5">
+        <v>516</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>535</v>
+        <v>429</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
+        <v>585</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>582</v>
+      </c>
+      <c r="B17" t="s">
+        <v>580</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>581</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>588</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
+      <c r="A25" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42.75">
+      <c r="A26" t="s">
+        <v>537</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>539</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
         <v>542</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="57">
+      <c r="A29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
         <v>520</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>544</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+      <c r="B30" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="28.5">
+      <c r="A31" t="s">
+        <v>531</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>513</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>550</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="57">
-      <c r="A20" t="s">
-        <v>488</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>523</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>432</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>557</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>519</v>
+      <c r="C32" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -9041,18 +9973,18 @@
     <col min="6" max="6" width="20.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="57.5" customWidth="1"/>
     <col min="8" max="8" width="55.75" customWidth="1"/>
-    <col min="9" max="9" width="9.875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.875" style="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A1" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>402</v>
-      </c>
       <c r="C1" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>247</v>
@@ -9064,616 +9996,616 @@
         <v>252</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>397</v>
+        <v>402</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>394</v>
       </c>
       <c r="H2" t="s">
-        <v>401</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>370</v>
+        <v>398</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D3">
         <v>39012025</v>
       </c>
       <c r="E3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F3">
         <v>2101989</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>503</v>
+      <c r="G3" s="47" t="s">
+        <v>500</v>
       </c>
       <c r="H3" t="s">
-        <v>468</v>
-      </c>
-      <c r="I3" s="47" t="s">
+        <v>465</v>
+      </c>
+      <c r="I3" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25">
       <c r="A4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F4">
         <v>1717550</v>
       </c>
-      <c r="G4" s="48" t="s">
-        <v>505</v>
+      <c r="G4" s="47" t="s">
+        <v>502</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F5">
         <v>630470</v>
       </c>
-      <c r="G5" s="48" t="s">
-        <v>498</v>
+      <c r="G5" s="47" t="s">
+        <v>495</v>
       </c>
       <c r="H5" t="s">
-        <v>470</v>
-      </c>
-      <c r="I5" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="I5" s="45" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F6">
         <v>630500</v>
       </c>
-      <c r="G6" s="48" t="s">
-        <v>499</v>
-      </c>
-      <c r="I6" s="46" t="s">
+      <c r="G6" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="I6" s="45" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F7">
         <v>1830730</v>
       </c>
-      <c r="G7" s="48" t="s">
-        <v>500</v>
+      <c r="G7" s="47" t="s">
+        <v>497</v>
       </c>
       <c r="H7" t="s">
-        <v>465</v>
-      </c>
-      <c r="I7" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="I7" s="45" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25">
       <c r="A8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D8" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F8">
         <v>1830725</v>
       </c>
-      <c r="G8" s="48" t="s">
-        <v>507</v>
+      <c r="G8" s="47" t="s">
+        <v>504</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25">
       <c r="A9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F9">
         <v>1830729</v>
       </c>
-      <c r="G9" s="48" t="s">
-        <v>502</v>
+      <c r="G9" s="47" t="s">
+        <v>499</v>
       </c>
       <c r="H9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25">
       <c r="A10" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B10">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D10" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E10" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F10">
         <v>1830725</v>
       </c>
-      <c r="G10" s="48" t="s">
-        <v>507</v>
+      <c r="G10" s="47" t="s">
+        <v>504</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D14" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E14" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F14">
         <v>1892523</v>
       </c>
-      <c r="G14" s="48" t="s">
-        <v>494</v>
+      <c r="G14" s="47" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D15" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F15" t="s">
-        <v>484</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>485</v>
+        <v>481</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
+        <v>475</v>
+      </c>
+      <c r="D16" t="s">
         <v>478</v>
       </c>
-      <c r="D16" t="s">
-        <v>481</v>
-      </c>
       <c r="E16" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>482</v>
+        <v>478</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E17" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F17">
         <v>2352005</v>
       </c>
-      <c r="G17" s="48" t="s">
-        <v>495</v>
+      <c r="G17" s="47" t="s">
+        <v>492</v>
       </c>
       <c r="H17" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D19" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E19" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F19">
         <v>2535699</v>
       </c>
-      <c r="G19" s="48" t="s">
-        <v>497</v>
-      </c>
-      <c r="I19" s="46" t="s">
+      <c r="G19" s="47" t="s">
+        <v>494</v>
+      </c>
+      <c r="I19" s="45" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C22" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D22" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E22" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F22">
         <v>9599568</v>
       </c>
-      <c r="G22" s="48" t="s">
-        <v>446</v>
+      <c r="G22" s="47" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H23" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s">
+        <v>442</v>
+      </c>
+      <c r="D24" t="s">
         <v>445</v>
       </c>
-      <c r="D24" t="s">
-        <v>448</v>
-      </c>
       <c r="E24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F24">
         <v>860414</v>
       </c>
-      <c r="G24" s="48" t="s">
-        <v>428</v>
+      <c r="G24" s="47" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C25" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D25" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E25" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F25">
         <v>4668791</v>
       </c>
-      <c r="G25" s="48" t="s">
-        <v>449</v>
+      <c r="G25" s="47" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C28" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E28" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F28">
         <v>2501338</v>
       </c>
-      <c r="G28" s="48" t="s">
-        <v>431</v>
+      <c r="G28" s="47" t="s">
+        <v>428</v>
       </c>
       <c r="H28" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C29" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D29" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E29" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F29">
         <v>3026838</v>
       </c>
-      <c r="G29" s="48" t="s">
-        <v>433</v>
+      <c r="G29" s="47" t="s">
+        <v>430</v>
       </c>
       <c r="H29" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
+        <v>432</v>
+      </c>
+      <c r="C30" t="s">
         <v>435</v>
       </c>
-      <c r="C30" t="s">
-        <v>438</v>
-      </c>
       <c r="D30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E30" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30">
         <v>537056</v>
       </c>
-      <c r="G30" s="48" t="s">
-        <v>436</v>
+      <c r="G30" s="47" t="s">
+        <v>433</v>
       </c>
       <c r="H30" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H31" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="5" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>424</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>458</v>
+        <v>421</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>455</v>
       </c>
       <c r="D37" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E37" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F37">
         <v>1014356</v>
       </c>
-      <c r="G37" s="48" t="s">
-        <v>455</v>
+      <c r="G37" s="47" t="s">
+        <v>452</v>
       </c>
       <c r="H37" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E38" t="s">
-        <v>491</v>
-      </c>
-      <c r="G38" s="48" t="s">
-        <v>490</v>
+        <v>488</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>487</v>
       </c>
       <c r="H38" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -9710,32 +10642,32 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.25" style="50" customWidth="1"/>
+    <col min="1" max="1" width="35.25" style="48" customWidth="1"/>
     <col min="7" max="7" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="50" t="s">
-        <v>559</v>
+      <c r="A1" s="48" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="5" customFormat="1">
       <c r="B2" s="5" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="50" t="s">
-        <v>563</v>
+      <c r="A3" s="48" t="s">
+        <v>556</v>
       </c>
       <c r="B3">
         <v>2.2799999999999998</v>
@@ -9747,12 +10679,12 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="50" t="s">
-        <v>566</v>
+      <c r="A4" s="48" t="s">
+        <v>559</v>
       </c>
       <c r="B4">
         <v>0.75</v>
@@ -9765,8 +10697,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="50" t="s">
-        <v>564</v>
+      <c r="A5" s="48" t="s">
+        <v>557</v>
       </c>
       <c r="B5" s="5">
         <f>B3-B4</f>
@@ -9783,12 +10715,12 @@
     </row>
     <row r="19" spans="6:6">
       <c r="F19" s="5" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34" spans="6:6">
       <c r="F34" s="5" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/Karman Delta Arm/Rocket arming system.xlsx
+++ b/Karman Delta Arm/Rocket arming system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\GitHub\AltiumGithub\Karman Delta Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A013A45-CA1C-4C34-BFF5-C1293A90118D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D508B82F-D9B1-4458-B342-199AEDC7DB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" tabRatio="783" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
+    <workbookView xWindow="0" yWindow="1980" windowWidth="21600" windowHeight="12645" tabRatio="783" activeTab="5" xr2:uid="{C397F53C-48EF-47A2-AFE9-4806826F5736}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="608">
   <si>
     <t>Failure Mode</t>
   </si>
@@ -1925,9 +1925,6 @@
   </si>
   <si>
     <t>Dates</t>
-  </si>
-  <si>
-    <t>Silkscreen pin 1 dots</t>
   </si>
 </sst>
 </file>
@@ -9423,7 +9420,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03095054-2AE4-4924-A1C8-63632743E825}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -9724,10 +9721,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>429</v>
+        <v>585</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>517</v>
@@ -9735,16 +9732,22 @@
       <c r="D15" s="1" t="s">
         <v>516</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>585</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
+      </c>
+      <c r="B16" t="s">
+        <v>580</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>517</v>
+        <v>584</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>516</v>
@@ -9758,10 +9761,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>582</v>
-      </c>
-      <c r="B17" t="s">
-        <v>580</v>
+        <v>581</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>583</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>584</v>
@@ -9778,10 +9781,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>584</v>
@@ -9790,7 +9793,7 @@
         <v>516</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>536</v>
@@ -9798,10 +9801,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>584</v>
@@ -9809,48 +9812,60 @@
       <c r="D19" s="1" t="s">
         <v>516</v>
       </c>
+      <c r="E19" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>588</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>536</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15">
-      <c r="A25" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" s="5" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="42.75">
+    <row r="25" spans="1:7" ht="42.75">
+      <c r="A25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>517</v>
@@ -9859,15 +9874,15 @@
         <v>516</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>517</v>
@@ -9875,16 +9890,13 @@
       <c r="D27" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+    </row>
+    <row r="28" spans="1:7" ht="57">
       <c r="A28" t="s">
-        <v>542</v>
+        <v>485</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>517</v>
@@ -9893,12 +9905,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="57">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>517</v>
@@ -9907,12 +9919,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" ht="28.5">
       <c r="A30" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>517</v>
@@ -9920,13 +9932,16 @@
       <c r="D30" s="1" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.5">
+      <c r="G30" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>517</v>
@@ -9935,23 +9950,6 @@
         <v>516</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>513</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="G32" s="1" t="s">
         <v>594</v>
       </c>
     </row>
